--- a/data/face-common-vars-v2.xlsx
+++ b/data/face-common-vars-v2.xlsx
@@ -38,7 +38,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="68">
+  <fills count="67">
     <fill>
       <patternFill/>
     </fill>
@@ -407,12 +407,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4F770"/>
-        <bgColor rgb="FFF8CBAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -484,7 +478,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -738,9 +732,6 @@
     <xf numFmtId="0" fontId="0" fillId="61" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="62" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="57" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -814,20 +805,20 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="62" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="62" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="62" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="63" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="63" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="66" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -836,11 +827,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="66" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="65" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="67" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="66" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1246,12 +1237,12 @@
   <cols>
     <col width="24.1640625" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="3"/>
-    <col width="28" customWidth="1" style="120" min="4" max="4"/>
+    <col width="28" customWidth="1" style="119" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="6"/>
-    <col width="25" customWidth="1" style="120" min="7" max="7"/>
+    <col width="25" customWidth="1" style="119" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="22.83203125" customWidth="1" style="120" min="10" max="10"/>
+    <col width="22.83203125" customWidth="1" style="119" min="10" max="10"/>
     <col width="22.83203125" customWidth="1" min="11" max="11"/>
     <col width="108" customWidth="1" min="12" max="12"/>
     <col width="75" customWidth="1" min="13" max="14"/>
@@ -1283,7 +1274,7 @@
           <t>SZ column in CSV</t>
         </is>
       </c>
-      <c r="D1" s="99" t="inlineStr">
+      <c r="D1" s="98" t="inlineStr">
         <is>
           <t>DR column in CSV</t>
         </is>
@@ -1298,7 +1289,7 @@
           <t>Variable SZ</t>
         </is>
       </c>
-      <c r="G1" s="99" t="inlineStr">
+      <c r="G1" s="98" t="inlineStr">
         <is>
           <t>Variable DR</t>
         </is>
@@ -1313,12 +1304,12 @@
           <t>Codage</t>
         </is>
       </c>
-      <c r="J1" s="99" t="inlineStr">
+      <c r="J1" s="98" t="inlineStr">
         <is>
           <t>Sanity min check</t>
         </is>
       </c>
-      <c r="K1" s="99" t="inlineStr">
+      <c r="K1" s="98" t="inlineStr">
         <is>
           <t>Sanity max check</t>
         </is>
@@ -1410,7 +1401,7 @@
           <t>usubjid_patients</t>
         </is>
       </c>
-      <c r="D2" s="100" t="inlineStr">
+      <c r="D2" s="99" t="inlineStr">
         <is>
           <t>usubjid_patients</t>
         </is>
@@ -1425,7 +1416,7 @@
           <t>USUBJID</t>
         </is>
       </c>
-      <c r="G2" s="100" t="inlineStr">
+      <c r="G2" s="99" t="inlineStr">
         <is>
           <t>USUBJID</t>
         </is>
@@ -1436,7 +1427,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n"/>
-      <c r="J2" s="100" t="n"/>
+      <c r="J2" s="99" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -1517,7 +1508,7 @@
           <t>fondacode</t>
         </is>
       </c>
-      <c r="D3" s="100" t="inlineStr">
+      <c r="D3" s="99" t="inlineStr">
         <is>
           <t>fondacode</t>
         </is>
@@ -1532,7 +1523,7 @@
           <t>SUBJID</t>
         </is>
       </c>
-      <c r="G3" s="100" t="inlineStr">
+      <c r="G3" s="99" t="inlineStr">
         <is>
           <t>SUBJID</t>
         </is>
@@ -1543,7 +1534,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n"/>
-      <c r="J3" s="100" t="n"/>
+      <c r="J3" s="99" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -1620,7 +1611,7 @@
           <t>sex</t>
         </is>
       </c>
-      <c r="D4" s="100" t="inlineStr">
+      <c r="D4" s="99" t="inlineStr">
         <is>
           <t>sex</t>
         </is>
@@ -1635,7 +1626,7 @@
           <t>SEX</t>
         </is>
       </c>
-      <c r="G4" s="100" t="inlineStr">
+      <c r="G4" s="99" t="inlineStr">
         <is>
           <t>SEX</t>
         </is>
@@ -1650,7 +1641,7 @@
           <t>F: Female; M: Male</t>
         </is>
       </c>
-      <c r="J4" s="100" t="n"/>
+      <c r="J4" s="99" t="n"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -1739,7 +1730,7 @@
           <t>siteid</t>
         </is>
       </c>
-      <c r="D5" s="101" t="inlineStr">
+      <c r="D5" s="100" t="inlineStr">
         <is>
           <t>siteid</t>
         </is>
@@ -1754,7 +1745,7 @@
           <t>SITEID</t>
         </is>
       </c>
-      <c r="G5" s="101" t="inlineStr">
+      <c r="G5" s="100" t="inlineStr">
         <is>
           <t>SITEID</t>
         </is>
@@ -1766,10 +1757,10 @@
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>1:Bordeaux; 2:Créteil; 3:Montpellier; 4:Grenoble; 5: Nancy; 6:Marseille; 7:Lariboisière; 8:Versailles; 9: Monaco; 10: Clermont-Ferrand; 12: Colombes; 16: Besançon</t>
-        </is>
-      </c>
-      <c r="J5" s="101" t="n"/>
+          <t>Numéro de centre = code réseau FONDAMENTAL (= 1-2 premiers chiffres du fondacode). MÊME schéma de numérotation dans les 3 cohortes. Décoder via data/site_lookup.csv. NB: raw siteid mal-étiqueté pour SZ code 16 (=19 Toulouse) -&gt; préférer fondacode.</t>
+        </is>
+      </c>
+      <c r="J5" s="100" t="n"/>
       <c r="K5" s="10" t="n"/>
       <c r="L5" s="10" t="inlineStr">
         <is>
@@ -1778,12 +1769,12 @@
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>⚠ CONFIRMED disjoint numbering: BP has SITEID 1-24 (15 distinct sites), SZ has SITEID 1-23 (12 distinct sites), DR has SITEID 1-20 (13 distinct sites). Mean and median values differ substantially across pathologies (BP mean=5.4, SZ=7.4, DR=10.3) because the same integer maps to different cities.</t>
+          <t>Cross-cohort comparable VIA fondacode head, NOT raw siteid. Raw siteid matches fondacode 99.2%% (BP) / 99.9%% (SZ) / 100%% (DR); the mismatches are data-entry errors. Recode to city using data/site_lookup.csv (site_code -&gt; city). DR sites 17,18 need city labels.</t>
         </is>
       </c>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>Build a per-pathology lookup table {pathology, SITEID_int} → city_name. Use city_name (not raw SITEID) as the clustering covariate. Treat as categorical stratifier. Verify cities across pathologies overlap correctly before pooling within-city.</t>
+          <t>Derive canonical site from fondacode leading digits; map to city via data/site_lookup.csv. Use as ComBat batch / site confound.</t>
         </is>
       </c>
       <c r="O5" s="10" t="inlineStr">
@@ -1854,7 +1845,7 @@
           <t>arm</t>
         </is>
       </c>
-      <c r="D6" s="100" t="inlineStr">
+      <c r="D6" s="99" t="inlineStr">
         <is>
           <t>arm</t>
         </is>
@@ -1869,7 +1860,7 @@
           <t>ARM</t>
         </is>
       </c>
-      <c r="G6" s="100" t="inlineStr">
+      <c r="G6" s="99" t="inlineStr">
         <is>
           <t>ARM</t>
         </is>
@@ -1880,7 +1871,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n"/>
-      <c r="J6" s="100" t="n"/>
+      <c r="J6" s="99" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1953,7 +1944,7 @@
           <t>brthdtc</t>
         </is>
       </c>
-      <c r="D7" s="100" t="inlineStr">
+      <c r="D7" s="99" t="inlineStr">
         <is>
           <t>brthdtc</t>
         </is>
@@ -1968,7 +1959,7 @@
           <t>BRTHDTC</t>
         </is>
       </c>
-      <c r="G7" s="100" t="inlineStr">
+      <c r="G7" s="99" t="inlineStr">
         <is>
           <t>BRTHDTC</t>
         </is>
@@ -1979,7 +1970,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n"/>
-      <c r="J7" s="100" t="n"/>
+      <c r="J7" s="99" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -2052,7 +2043,7 @@
           <t>age</t>
         </is>
       </c>
-      <c r="D8" s="100" t="inlineStr">
+      <c r="D8" s="99" t="inlineStr">
         <is>
           <t>age</t>
         </is>
@@ -2067,7 +2058,7 @@
           <t>AGE</t>
         </is>
       </c>
-      <c r="G8" s="100" t="inlineStr">
+      <c r="G8" s="99" t="inlineStr">
         <is>
           <t>AGE</t>
         </is>
@@ -2078,7 +2069,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n"/>
-      <c r="J8" s="100" t="n"/>
+      <c r="J8" s="99" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -2151,7 +2142,7 @@
           <t>visitnum</t>
         </is>
       </c>
-      <c r="D9" s="101" t="inlineStr">
+      <c r="D9" s="100" t="inlineStr">
         <is>
           <t>visitnum</t>
         </is>
@@ -2166,7 +2157,7 @@
           <t>VISITNUM</t>
         </is>
       </c>
-      <c r="G9" s="101" t="inlineStr">
+      <c r="G9" s="100" t="inlineStr">
         <is>
           <t>VISITNUM</t>
         </is>
@@ -2181,7 +2172,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J9" s="101" t="n"/>
+      <c r="J9" s="100" t="n"/>
       <c r="K9" s="10" t="n"/>
       <c r="L9" s="10" t="inlineStr">
         <is>
@@ -2254,7 +2245,7 @@
           <t>visit</t>
         </is>
       </c>
-      <c r="D10" s="102" t="inlineStr">
+      <c r="D10" s="101" t="inlineStr">
         <is>
           <t>visit</t>
         </is>
@@ -2269,7 +2260,7 @@
           <t xml:space="preserve">VISIT </t>
         </is>
       </c>
-      <c r="G10" s="102" t="inlineStr">
+      <c r="G10" s="101" t="inlineStr">
         <is>
           <t xml:space="preserve">VISIT </t>
         </is>
@@ -2280,7 +2271,7 @@
         </is>
       </c>
       <c r="I10" s="7" t="n"/>
-      <c r="J10" s="102" t="n"/>
+      <c r="J10" s="101" t="n"/>
       <c r="K10" s="7" t="n"/>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -2349,7 +2340,7 @@
         </is>
       </c>
       <c r="C11" s="15" t="n"/>
-      <c r="D11" s="103" t="inlineStr">
+      <c r="D11" s="102" t="inlineStr">
         <is>
           <t>prism</t>
         </is>
@@ -2360,7 +2351,7 @@
         </is>
       </c>
       <c r="F11" s="15" t="n"/>
-      <c r="G11" s="103" t="inlineStr">
+      <c r="G11" s="102" t="inlineStr">
         <is>
           <t>PRISM</t>
         </is>
@@ -2371,7 +2362,7 @@
         </is>
       </c>
       <c r="I11" s="15" t="n"/>
-      <c r="J11" s="103" t="n">
+      <c r="J11" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="15" t="n">
@@ -2436,7 +2427,7 @@
         </is>
       </c>
       <c r="C12" s="15" t="n"/>
-      <c r="D12" s="103" t="inlineStr">
+      <c r="D12" s="102" t="inlineStr">
         <is>
           <t>staya</t>
         </is>
@@ -2447,7 +2438,7 @@
         </is>
       </c>
       <c r="F12" s="15" t="n"/>
-      <c r="G12" s="103" t="inlineStr">
+      <c r="G12" s="102" t="inlineStr">
         <is>
           <t xml:space="preserve">STAYA </t>
         </is>
@@ -2458,7 +2449,7 @@
         </is>
       </c>
       <c r="I12" s="15" t="n"/>
-      <c r="J12" s="103" t="n">
+      <c r="J12" s="102" t="n">
         <v>20</v>
       </c>
       <c r="K12" s="15" t="n">
@@ -2527,7 +2518,7 @@
           <t>mars_</t>
         </is>
       </c>
-      <c r="D13" s="103" t="inlineStr">
+      <c r="D13" s="102" t="inlineStr">
         <is>
           <t>mars_</t>
         </is>
@@ -2542,7 +2533,7 @@
           <t>MARS_</t>
         </is>
       </c>
-      <c r="G13" s="103" t="inlineStr">
+      <c r="G13" s="102" t="inlineStr">
         <is>
           <t>MARS_</t>
         </is>
@@ -2553,7 +2544,7 @@
         </is>
       </c>
       <c r="I13" s="15" t="n"/>
-      <c r="J13" s="103" t="n">
+      <c r="J13" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="15" t="n">
@@ -2622,7 +2613,7 @@
         </is>
       </c>
       <c r="C14" s="15" t="n"/>
-      <c r="D14" s="103" t="inlineStr">
+      <c r="D14" s="102" t="inlineStr">
         <is>
           <t>altman_</t>
         </is>
@@ -2633,7 +2624,7 @@
         </is>
       </c>
       <c r="F14" s="15" t="n"/>
-      <c r="G14" s="103" t="inlineStr">
+      <c r="G14" s="102" t="inlineStr">
         <is>
           <t>ALTMAN_</t>
         </is>
@@ -2644,7 +2635,7 @@
         </is>
       </c>
       <c r="I14" s="15" t="n"/>
-      <c r="J14" s="103" t="n">
+      <c r="J14" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="15" t="n">
@@ -2709,7 +2700,7 @@
         </is>
       </c>
       <c r="C15" s="15" t="n"/>
-      <c r="D15" s="103" t="inlineStr">
+      <c r="D15" s="102" t="inlineStr">
         <is>
           <t>qids_</t>
         </is>
@@ -2720,7 +2711,7 @@
         </is>
       </c>
       <c r="F15" s="15" t="n"/>
-      <c r="G15" s="103" t="inlineStr">
+      <c r="G15" s="102" t="inlineStr">
         <is>
           <t>QIDS_</t>
         </is>
@@ -2731,7 +2722,7 @@
         </is>
       </c>
       <c r="I15" s="15" t="n"/>
-      <c r="J15" s="103" t="n">
+      <c r="J15" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="15" t="n">
@@ -2800,7 +2791,7 @@
           <t>psqi_</t>
         </is>
       </c>
-      <c r="D16" s="103" t="inlineStr">
+      <c r="D16" s="102" t="inlineStr">
         <is>
           <t>psqi_</t>
         </is>
@@ -2815,7 +2806,7 @@
           <t>PSQI_</t>
         </is>
       </c>
-      <c r="G16" s="103" t="inlineStr">
+      <c r="G16" s="102" t="inlineStr">
         <is>
           <t>PSQI_</t>
         </is>
@@ -2826,7 +2817,7 @@
         </is>
       </c>
       <c r="I16" s="15" t="n"/>
-      <c r="J16" s="103" t="n">
+      <c r="J16" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="15" t="n">
@@ -2899,7 +2890,7 @@
           <t>psqi11</t>
         </is>
       </c>
-      <c r="D17" s="103" t="inlineStr">
+      <c r="D17" s="102" t="inlineStr">
         <is>
           <t>psqi11</t>
         </is>
@@ -2914,7 +2905,7 @@
           <t>PSQI11</t>
         </is>
       </c>
-      <c r="G17" s="103" t="inlineStr">
+      <c r="G17" s="102" t="inlineStr">
         <is>
           <t>PSQI11</t>
         </is>
@@ -2925,7 +2916,7 @@
         </is>
       </c>
       <c r="I17" s="15" t="n"/>
-      <c r="J17" s="103" t="n">
+      <c r="J17" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="15" t="n">
@@ -2998,7 +2989,7 @@
           <t>psqi12</t>
         </is>
       </c>
-      <c r="D18" s="103" t="inlineStr">
+      <c r="D18" s="102" t="inlineStr">
         <is>
           <t>psqi12</t>
         </is>
@@ -3013,7 +3004,7 @@
           <t>PSQI12</t>
         </is>
       </c>
-      <c r="G18" s="103" t="inlineStr">
+      <c r="G18" s="102" t="inlineStr">
         <is>
           <t>PSQI12</t>
         </is>
@@ -3024,7 +3015,7 @@
         </is>
       </c>
       <c r="I18" s="15" t="n"/>
-      <c r="J18" s="103" t="n">
+      <c r="J18" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="15" t="n">
@@ -3097,7 +3088,7 @@
           <t>psqi13</t>
         </is>
       </c>
-      <c r="D19" s="103" t="inlineStr">
+      <c r="D19" s="102" t="inlineStr">
         <is>
           <t>psqi13</t>
         </is>
@@ -3112,7 +3103,7 @@
           <t>PSQI13</t>
         </is>
       </c>
-      <c r="G19" s="103" t="inlineStr">
+      <c r="G19" s="102" t="inlineStr">
         <is>
           <t>PSQI13</t>
         </is>
@@ -3123,7 +3114,7 @@
         </is>
       </c>
       <c r="I19" s="15" t="n"/>
-      <c r="J19" s="103" t="n">
+      <c r="J19" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="15" t="n">
@@ -3196,7 +3187,7 @@
           <t>psqi14</t>
         </is>
       </c>
-      <c r="D20" s="103" t="inlineStr">
+      <c r="D20" s="102" t="inlineStr">
         <is>
           <t>psqi14</t>
         </is>
@@ -3211,7 +3202,7 @@
           <t>PSQI14</t>
         </is>
       </c>
-      <c r="G20" s="103" t="inlineStr">
+      <c r="G20" s="102" t="inlineStr">
         <is>
           <t>PSQI14</t>
         </is>
@@ -3222,7 +3213,7 @@
         </is>
       </c>
       <c r="I20" s="15" t="n"/>
-      <c r="J20" s="103" t="n">
+      <c r="J20" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="15" t="n">
@@ -3295,7 +3286,7 @@
           <t>psqi15</t>
         </is>
       </c>
-      <c r="D21" s="103" t="inlineStr">
+      <c r="D21" s="102" t="inlineStr">
         <is>
           <t>psqi15</t>
         </is>
@@ -3310,7 +3301,7 @@
           <t>PSQI15</t>
         </is>
       </c>
-      <c r="G21" s="103" t="inlineStr">
+      <c r="G21" s="102" t="inlineStr">
         <is>
           <t>PSQI15</t>
         </is>
@@ -3321,7 +3312,7 @@
         </is>
       </c>
       <c r="I21" s="15" t="n"/>
-      <c r="J21" s="103" t="n">
+      <c r="J21" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="15" t="n">
@@ -3394,7 +3385,7 @@
           <t>psqi16</t>
         </is>
       </c>
-      <c r="D22" s="103" t="inlineStr">
+      <c r="D22" s="102" t="inlineStr">
         <is>
           <t>psqi16</t>
         </is>
@@ -3409,7 +3400,7 @@
           <t>PSQI16</t>
         </is>
       </c>
-      <c r="G22" s="103" t="inlineStr">
+      <c r="G22" s="102" t="inlineStr">
         <is>
           <t>PSQI16</t>
         </is>
@@ -3420,7 +3411,7 @@
         </is>
       </c>
       <c r="I22" s="15" t="n"/>
-      <c r="J22" s="103" t="n">
+      <c r="J22" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="15" t="n">
@@ -3493,7 +3484,7 @@
           <t>psqi17</t>
         </is>
       </c>
-      <c r="D23" s="103" t="inlineStr">
+      <c r="D23" s="102" t="inlineStr">
         <is>
           <t>psqi17</t>
         </is>
@@ -3508,7 +3499,7 @@
           <t>PSQI17</t>
         </is>
       </c>
-      <c r="G23" s="103" t="inlineStr">
+      <c r="G23" s="102" t="inlineStr">
         <is>
           <t>PSQI17</t>
         </is>
@@ -3519,7 +3510,7 @@
         </is>
       </c>
       <c r="I23" s="15" t="n"/>
-      <c r="J23" s="103" t="n">
+      <c r="J23" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K23" s="15" t="n">
@@ -3588,7 +3579,7 @@
         </is>
       </c>
       <c r="C24" s="15" t="n"/>
-      <c r="D24" s="103" t="inlineStr">
+      <c r="D24" s="102" t="inlineStr">
         <is>
           <t>ess</t>
         </is>
@@ -3599,7 +3590,7 @@
         </is>
       </c>
       <c r="F24" s="15" t="n"/>
-      <c r="G24" s="103" t="inlineStr">
+      <c r="G24" s="102" t="inlineStr">
         <is>
           <t xml:space="preserve">ESS </t>
         </is>
@@ -3610,7 +3601,7 @@
         </is>
       </c>
       <c r="I24" s="15" t="n"/>
-      <c r="J24" s="103" t="n">
+      <c r="J24" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="15" t="n">
@@ -3679,7 +3670,7 @@
           <t>eq5d0206</t>
         </is>
       </c>
-      <c r="D25" s="103" t="inlineStr">
+      <c r="D25" s="102" t="inlineStr">
         <is>
           <t>eq5d06</t>
         </is>
@@ -3694,7 +3685,7 @@
           <t>EQ5D0206</t>
         </is>
       </c>
-      <c r="G25" s="103" t="inlineStr">
+      <c r="G25" s="102" t="inlineStr">
         <is>
           <t>EQ5D06</t>
         </is>
@@ -3705,7 +3696,7 @@
         </is>
       </c>
       <c r="I25" s="15" t="n"/>
-      <c r="J25" s="103" t="n">
+      <c r="J25" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="15" t="n">
@@ -3782,7 +3773,7 @@
           <t>eq5d_</t>
         </is>
       </c>
-      <c r="D26" s="103" t="n"/>
+      <c r="D26" s="102" t="n"/>
       <c r="E26" s="15" t="inlineStr">
         <is>
           <t>EQ5D_</t>
@@ -3793,14 +3784,14 @@
           <t>EQ5D_</t>
         </is>
       </c>
-      <c r="G26" s="103" t="n"/>
+      <c r="G26" s="102" t="n"/>
       <c r="H26" s="15" t="inlineStr">
         <is>
           <t>Score à l'EQ-5D</t>
         </is>
       </c>
       <c r="I26" s="15" t="n"/>
-      <c r="J26" s="103" t="n">
+      <c r="J26" s="102" t="n">
         <v>-0.53</v>
       </c>
       <c r="K26" s="15" t="n">
@@ -3869,7 +3860,7 @@
           <t>fagers</t>
         </is>
       </c>
-      <c r="D27" s="103" t="inlineStr">
+      <c r="D27" s="102" t="inlineStr">
         <is>
           <t>fagers</t>
         </is>
@@ -3884,7 +3875,7 @@
           <t xml:space="preserve">FAGERS </t>
         </is>
       </c>
-      <c r="G27" s="103" t="inlineStr">
+      <c r="G27" s="102" t="inlineStr">
         <is>
           <t>FAGERS</t>
         </is>
@@ -3895,7 +3886,7 @@
         </is>
       </c>
       <c r="I27" s="15" t="n"/>
-      <c r="J27" s="103" t="n">
+      <c r="J27" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K27" s="15" t="n">
@@ -3976,7 +3967,7 @@
           <t>ctq29</t>
         </is>
       </c>
-      <c r="D28" s="103" t="inlineStr">
+      <c r="D28" s="102" t="inlineStr">
         <is>
           <t>ctq29</t>
         </is>
@@ -3991,7 +3982,7 @@
           <t>CTQ29</t>
         </is>
       </c>
-      <c r="G28" s="103" t="inlineStr">
+      <c r="G28" s="102" t="inlineStr">
         <is>
           <t>CTQ29</t>
         </is>
@@ -4002,7 +3993,7 @@
         </is>
       </c>
       <c r="I28" s="15" t="n"/>
-      <c r="J28" s="103" t="n">
+      <c r="J28" s="102" t="n">
         <v>5</v>
       </c>
       <c r="K28" s="15" t="n">
@@ -4075,7 +4066,7 @@
           <t>ctq31</t>
         </is>
       </c>
-      <c r="D29" s="103" t="inlineStr">
+      <c r="D29" s="102" t="inlineStr">
         <is>
           <t>ctq31</t>
         </is>
@@ -4090,7 +4081,7 @@
           <t>CTQ31</t>
         </is>
       </c>
-      <c r="G29" s="103" t="inlineStr">
+      <c r="G29" s="102" t="inlineStr">
         <is>
           <t>CTQ31</t>
         </is>
@@ -4101,7 +4092,7 @@
         </is>
       </c>
       <c r="I29" s="15" t="n"/>
-      <c r="J29" s="103" t="n">
+      <c r="J29" s="102" t="n">
         <v>5</v>
       </c>
       <c r="K29" s="15" t="n">
@@ -4174,7 +4165,7 @@
           <t>ctq33</t>
         </is>
       </c>
-      <c r="D30" s="103" t="inlineStr">
+      <c r="D30" s="102" t="inlineStr">
         <is>
           <t>ctq33</t>
         </is>
@@ -4189,7 +4180,7 @@
           <t>CTQ33</t>
         </is>
       </c>
-      <c r="G30" s="103" t="inlineStr">
+      <c r="G30" s="102" t="inlineStr">
         <is>
           <t>CTQ33</t>
         </is>
@@ -4200,7 +4191,7 @@
         </is>
       </c>
       <c r="I30" s="15" t="n"/>
-      <c r="J30" s="103" t="n">
+      <c r="J30" s="102" t="n">
         <v>5</v>
       </c>
       <c r="K30" s="15" t="n">
@@ -4273,7 +4264,7 @@
           <t>ctq35</t>
         </is>
       </c>
-      <c r="D31" s="103" t="inlineStr">
+      <c r="D31" s="102" t="inlineStr">
         <is>
           <t>ctq35</t>
         </is>
@@ -4288,7 +4279,7 @@
           <t>CTQ35</t>
         </is>
       </c>
-      <c r="G31" s="103" t="inlineStr">
+      <c r="G31" s="102" t="inlineStr">
         <is>
           <t>CTQ35</t>
         </is>
@@ -4299,7 +4290,7 @@
         </is>
       </c>
       <c r="I31" s="15" t="n"/>
-      <c r="J31" s="103" t="n">
+      <c r="J31" s="102" t="n">
         <v>5</v>
       </c>
       <c r="K31" s="15" t="n">
@@ -4372,7 +4363,7 @@
           <t>ctq37</t>
         </is>
       </c>
-      <c r="D32" s="103" t="inlineStr">
+      <c r="D32" s="102" t="inlineStr">
         <is>
           <t>ctq37</t>
         </is>
@@ -4387,7 +4378,7 @@
           <t>CTQ37</t>
         </is>
       </c>
-      <c r="G32" s="103" t="inlineStr">
+      <c r="G32" s="102" t="inlineStr">
         <is>
           <t>CTQ37</t>
         </is>
@@ -4398,7 +4389,7 @@
         </is>
       </c>
       <c r="I32" s="15" t="n"/>
-      <c r="J32" s="103" t="n">
+      <c r="J32" s="102" t="n">
         <v>5</v>
       </c>
       <c r="K32" s="15" t="n">
@@ -4471,7 +4462,7 @@
           <t>ctq39</t>
         </is>
       </c>
-      <c r="D33" s="103" t="inlineStr">
+      <c r="D33" s="102" t="inlineStr">
         <is>
           <t>ctq39</t>
         </is>
@@ -4486,7 +4477,7 @@
           <t>CTQ39</t>
         </is>
       </c>
-      <c r="G33" s="103" t="inlineStr">
+      <c r="G33" s="102" t="inlineStr">
         <is>
           <t>CTQ39</t>
         </is>
@@ -4497,7 +4488,7 @@
         </is>
       </c>
       <c r="I33" s="15" t="n"/>
-      <c r="J33" s="103" t="n">
+      <c r="J33" s="102" t="n">
         <v>25</v>
       </c>
       <c r="K33" s="15" t="n">
@@ -4570,7 +4561,7 @@
           <t>ctq40</t>
         </is>
       </c>
-      <c r="D34" s="103" t="inlineStr">
+      <c r="D34" s="102" t="inlineStr">
         <is>
           <t>ctq40</t>
         </is>
@@ -4585,7 +4576,7 @@
           <t>CTQ40</t>
         </is>
       </c>
-      <c r="G34" s="103" t="inlineStr">
+      <c r="G34" s="102" t="inlineStr">
         <is>
           <t>CTQ40</t>
         </is>
@@ -4596,7 +4587,7 @@
         </is>
       </c>
       <c r="I34" s="15" t="n"/>
-      <c r="J34" s="103" t="n">
+      <c r="J34" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="15" t="n">
@@ -4669,7 +4660,7 @@
           <t>ctq41</t>
         </is>
       </c>
-      <c r="D35" s="103" t="n"/>
+      <c r="D35" s="102" t="n"/>
       <c r="E35" s="15" t="inlineStr">
         <is>
           <t>CTQ41</t>
@@ -4680,7 +4671,7 @@
           <t>CTQ41</t>
         </is>
       </c>
-      <c r="G35" s="103" t="n"/>
+      <c r="G35" s="102" t="n"/>
       <c r="H35" s="15" t="inlineStr">
         <is>
           <t>Risque de déni sur le questionnaire</t>
@@ -4691,7 +4682,7 @@
           <t>1: Oui; 0: Non</t>
         </is>
       </c>
-      <c r="J35" s="103" t="n">
+      <c r="J35" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K35" s="15" t="n">
@@ -4749,7 +4740,7 @@
       </c>
     </row>
     <row r="36" ht="21" customFormat="1" customHeight="1" s="17">
-      <c r="A36" s="125" t="inlineStr">
+      <c r="A36" s="124" t="inlineStr">
         <is>
           <t>AUTO-QUESTIONNAIRES</t>
         </is>
@@ -4760,7 +4751,7 @@
         </is>
       </c>
       <c r="C36" s="10" t="n"/>
-      <c r="D36" s="101" t="inlineStr">
+      <c r="D36" s="100" t="inlineStr">
         <is>
           <t>bis10</t>
         </is>
@@ -4771,7 +4762,7 @@
         </is>
       </c>
       <c r="F36" s="10" t="n"/>
-      <c r="G36" s="101" t="inlineStr">
+      <c r="G36" s="100" t="inlineStr">
         <is>
           <t>BIS10</t>
         </is>
@@ -4782,7 +4773,7 @@
         </is>
       </c>
       <c r="I36" s="10" t="n"/>
-      <c r="J36" s="101" t="n"/>
+      <c r="J36" s="100" t="n"/>
       <c r="K36" s="10" t="n"/>
       <c r="L36" s="10" t="inlineStr">
         <is>
@@ -4823,7 +4814,7 @@
           <t>mmHg</t>
         </is>
       </c>
-      <c r="W36" s="126" t="inlineStr">
+      <c r="W36" s="125" t="inlineStr">
         <is>
           <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
         </is>
@@ -4855,7 +4846,7 @@
           <t>wurstot</t>
         </is>
       </c>
-      <c r="D37" s="103" t="n"/>
+      <c r="D37" s="102" t="n"/>
       <c r="E37" s="15" t="inlineStr">
         <is>
           <t>WURS</t>
@@ -4866,14 +4857,14 @@
           <t>WURSTOT</t>
         </is>
       </c>
-      <c r="G37" s="103" t="n"/>
+      <c r="G37" s="102" t="n"/>
       <c r="H37" s="15" t="inlineStr">
         <is>
           <t>Score à l'echelle WURS</t>
         </is>
       </c>
       <c r="I37" s="15" t="n"/>
-      <c r="J37" s="103" t="n">
+      <c r="J37" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="15" t="n">
@@ -4938,7 +4929,7 @@
         </is>
       </c>
       <c r="C38" s="15" t="n"/>
-      <c r="D38" s="103" t="inlineStr">
+      <c r="D38" s="102" t="inlineStr">
         <is>
           <t>csm_</t>
         </is>
@@ -4949,7 +4940,7 @@
         </is>
       </c>
       <c r="F38" s="15" t="n"/>
-      <c r="G38" s="103" t="inlineStr">
+      <c r="G38" s="102" t="inlineStr">
         <is>
           <t>CSM_</t>
         </is>
@@ -4960,7 +4951,7 @@
         </is>
       </c>
       <c r="I38" s="15" t="n"/>
-      <c r="J38" s="103" t="n">
+      <c r="J38" s="102" t="n">
         <v>13</v>
       </c>
       <c r="K38" s="15" t="n">
@@ -5025,7 +5016,7 @@
         </is>
       </c>
       <c r="C39" s="22" t="n"/>
-      <c r="D39" s="104" t="inlineStr">
+      <c r="D39" s="103" t="inlineStr">
         <is>
           <t>mdq_</t>
         </is>
@@ -5036,7 +5027,7 @@
         </is>
       </c>
       <c r="F39" s="22" t="n"/>
-      <c r="G39" s="104" t="inlineStr">
+      <c r="G39" s="103" t="inlineStr">
         <is>
           <t>MDQ_</t>
         </is>
@@ -5047,7 +5038,7 @@
         </is>
       </c>
       <c r="I39" s="22" t="n"/>
-      <c r="J39" s="104" t="n">
+      <c r="J39" s="103" t="n">
         <v>0</v>
       </c>
       <c r="K39" s="22" t="n">
@@ -5116,7 +5107,7 @@
           <t>cgi0101</t>
         </is>
       </c>
-      <c r="D40" s="105" t="inlineStr">
+      <c r="D40" s="104" t="inlineStr">
         <is>
           <t>cgi01</t>
         </is>
@@ -5131,7 +5122,7 @@
           <t>CGI0101</t>
         </is>
       </c>
-      <c r="G40" s="105" t="inlineStr">
+      <c r="G40" s="104" t="inlineStr">
         <is>
           <t>CGI01</t>
         </is>
@@ -5146,7 +5137,7 @@
           <t>0: Non évalué; 1: Normal, pas du tout malade ... 7: Parmi les plus malades</t>
         </is>
       </c>
-      <c r="J40" s="105" t="n">
+      <c r="J40" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K40" s="31" t="n">
@@ -5239,7 +5230,7 @@
           <t>cgi0102</t>
         </is>
       </c>
-      <c r="D41" s="105" t="n"/>
+      <c r="D41" s="104" t="n"/>
       <c r="E41" s="31" t="inlineStr">
         <is>
           <t>CGI02</t>
@@ -5250,7 +5241,7 @@
           <t>CGI0102</t>
         </is>
       </c>
-      <c r="G41" s="105" t="n"/>
+      <c r="G41" s="104" t="n"/>
       <c r="H41" s="31" t="inlineStr">
         <is>
           <t>Amélioration globale (CGI amélioration)</t>
@@ -5261,7 +5252,7 @@
           <t>0: Non évalué; 1: Très fortement amélioré ... 7: Très fortement aggravé</t>
         </is>
       </c>
-      <c r="J41" s="105" t="n">
+      <c r="J41" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="31" t="n">
@@ -5346,7 +5337,7 @@
           <t>cgi0103a</t>
         </is>
       </c>
-      <c r="D42" s="105" t="n"/>
+      <c r="D42" s="104" t="n"/>
       <c r="E42" s="31" t="inlineStr">
         <is>
           <t>CGI03A</t>
@@ -5357,7 +5348,7 @@
           <t>CGI0103A</t>
         </is>
       </c>
-      <c r="G42" s="105" t="n"/>
+      <c r="G42" s="104" t="n"/>
       <c r="H42" s="31" t="inlineStr">
         <is>
           <t>Effet thérapeutique (CGI)</t>
@@ -5368,7 +5359,7 @@
           <t>0: Non évalué; 1: Important; 2: Modéré; 3: Minime; 4: Nul ou aggravation</t>
         </is>
       </c>
-      <c r="J42" s="105" t="n">
+      <c r="J42" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="31" t="n">
@@ -5453,7 +5444,7 @@
           <t>cgi0103b</t>
         </is>
       </c>
-      <c r="D43" s="105" t="n"/>
+      <c r="D43" s="104" t="n"/>
       <c r="E43" s="31" t="inlineStr">
         <is>
           <t>CGI03B</t>
@@ -5464,7 +5455,7 @@
           <t>CGI0103B</t>
         </is>
       </c>
-      <c r="G43" s="105" t="n"/>
+      <c r="G43" s="104" t="n"/>
       <c r="H43" s="31" t="inlineStr">
         <is>
           <t>Effets secondaires (CGI)</t>
@@ -5475,7 +5466,7 @@
           <t>0: Non évalué; 1: Aucun; 2: N'interfèrent pas; 3: Interfèrent; 4: Dépassent l'effet</t>
         </is>
       </c>
-      <c r="J43" s="105" t="n">
+      <c r="J43" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="31" t="n">
@@ -5560,7 +5551,7 @@
           <t>cgi0103</t>
         </is>
       </c>
-      <c r="D44" s="105" t="n"/>
+      <c r="D44" s="104" t="n"/>
       <c r="E44" s="31" t="inlineStr">
         <is>
           <t>CGI03</t>
@@ -5571,7 +5562,7 @@
           <t>CGI0103</t>
         </is>
       </c>
-      <c r="G44" s="105" t="n"/>
+      <c r="G44" s="104" t="n"/>
       <c r="H44" s="31" t="inlineStr">
         <is>
           <t>Score de l'index thérapeutique CGI</t>
@@ -5582,7 +5573,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J44" s="105" t="n">
+      <c r="J44" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="31" t="n">
@@ -5655,7 +5646,7 @@
           <t>egf</t>
         </is>
       </c>
-      <c r="D45" s="105" t="inlineStr">
+      <c r="D45" s="104" t="inlineStr">
         <is>
           <t>egf_</t>
         </is>
@@ -5670,7 +5661,7 @@
           <t>EGF</t>
         </is>
       </c>
-      <c r="G45" s="105" t="inlineStr">
+      <c r="G45" s="104" t="inlineStr">
         <is>
           <t>EGF_</t>
         </is>
@@ -5685,7 +5676,7 @@
           <t>NUM (0–100)</t>
         </is>
       </c>
-      <c r="J45" s="105" t="n">
+      <c r="J45" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="31" t="n">
@@ -5770,7 +5761,7 @@
         </is>
       </c>
       <c r="C46" s="31" t="n"/>
-      <c r="D46" s="105" t="inlineStr">
+      <c r="D46" s="104" t="inlineStr">
         <is>
           <t>madrs_</t>
         </is>
@@ -5781,7 +5772,7 @@
         </is>
       </c>
       <c r="F46" s="31" t="n"/>
-      <c r="G46" s="105" t="inlineStr">
+      <c r="G46" s="104" t="inlineStr">
         <is>
           <t>MADRS_</t>
         </is>
@@ -5796,7 +5787,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J46" s="105" t="n">
+      <c r="J46" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K46" s="31" t="n">
@@ -5869,7 +5860,7 @@
           <t>ymrs_</t>
         </is>
       </c>
-      <c r="D47" s="105" t="inlineStr">
+      <c r="D47" s="104" t="inlineStr">
         <is>
           <t>ymrs_</t>
         </is>
@@ -5884,7 +5875,7 @@
           <t>YMRS_</t>
         </is>
       </c>
-      <c r="G47" s="105" t="inlineStr">
+      <c r="G47" s="104" t="inlineStr">
         <is>
           <t>YMRS_</t>
         </is>
@@ -5899,7 +5890,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J47" s="105" t="n">
+      <c r="J47" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="31" t="n">
@@ -5972,7 +5963,7 @@
         </is>
       </c>
       <c r="C48" s="31" t="n"/>
-      <c r="D48" s="105" t="inlineStr">
+      <c r="D48" s="104" t="inlineStr">
         <is>
           <t>fast25</t>
         </is>
@@ -5983,7 +5974,7 @@
         </is>
       </c>
       <c r="F48" s="31" t="n"/>
-      <c r="G48" s="105" t="inlineStr">
+      <c r="G48" s="104" t="inlineStr">
         <is>
           <t>FAST25</t>
         </is>
@@ -5998,7 +5989,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J48" s="105" t="n">
+      <c r="J48" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="31" t="n">
@@ -6067,7 +6058,7 @@
         </is>
       </c>
       <c r="C49" s="31" t="n"/>
-      <c r="D49" s="105" t="inlineStr">
+      <c r="D49" s="104" t="inlineStr">
         <is>
           <t>fast26</t>
         </is>
@@ -6078,7 +6069,7 @@
         </is>
       </c>
       <c r="F49" s="31" t="n"/>
-      <c r="G49" s="105" t="inlineStr">
+      <c r="G49" s="104" t="inlineStr">
         <is>
           <t>FAST26</t>
         </is>
@@ -6093,7 +6084,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J49" s="105" t="n">
+      <c r="J49" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K49" s="31" t="n">
@@ -6162,7 +6153,7 @@
         </is>
       </c>
       <c r="C50" s="31" t="n"/>
-      <c r="D50" s="105" t="inlineStr">
+      <c r="D50" s="104" t="inlineStr">
         <is>
           <t>fast27</t>
         </is>
@@ -6173,7 +6164,7 @@
         </is>
       </c>
       <c r="F50" s="31" t="n"/>
-      <c r="G50" s="105" t="inlineStr">
+      <c r="G50" s="104" t="inlineStr">
         <is>
           <t>FAST27</t>
         </is>
@@ -6188,7 +6179,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J50" s="105" t="n">
+      <c r="J50" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K50" s="31" t="n">
@@ -6257,7 +6248,7 @@
         </is>
       </c>
       <c r="C51" s="31" t="n"/>
-      <c r="D51" s="105" t="inlineStr">
+      <c r="D51" s="104" t="inlineStr">
         <is>
           <t>fast28</t>
         </is>
@@ -6268,7 +6259,7 @@
         </is>
       </c>
       <c r="F51" s="31" t="n"/>
-      <c r="G51" s="105" t="inlineStr">
+      <c r="G51" s="104" t="inlineStr">
         <is>
           <t>FAST28</t>
         </is>
@@ -6283,7 +6274,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J51" s="105" t="n">
+      <c r="J51" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K51" s="31" t="n">
@@ -6352,7 +6343,7 @@
         </is>
       </c>
       <c r="C52" s="31" t="n"/>
-      <c r="D52" s="105" t="inlineStr">
+      <c r="D52" s="104" t="inlineStr">
         <is>
           <t>fast29</t>
         </is>
@@ -6363,7 +6354,7 @@
         </is>
       </c>
       <c r="F52" s="31" t="n"/>
-      <c r="G52" s="105" t="inlineStr">
+      <c r="G52" s="104" t="inlineStr">
         <is>
           <t>FAST29</t>
         </is>
@@ -6378,7 +6369,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J52" s="105" t="n">
+      <c r="J52" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K52" s="31" t="n">
@@ -6447,7 +6438,7 @@
         </is>
       </c>
       <c r="C53" s="31" t="n"/>
-      <c r="D53" s="105" t="inlineStr">
+      <c r="D53" s="104" t="inlineStr">
         <is>
           <t>fast30</t>
         </is>
@@ -6458,7 +6449,7 @@
         </is>
       </c>
       <c r="F53" s="31" t="n"/>
-      <c r="G53" s="105" t="inlineStr">
+      <c r="G53" s="104" t="inlineStr">
         <is>
           <t>FAST30</t>
         </is>
@@ -6473,7 +6464,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J53" s="105" t="n">
+      <c r="J53" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K53" s="31" t="n">
@@ -6542,7 +6533,7 @@
         </is>
       </c>
       <c r="C54" s="38" t="n"/>
-      <c r="D54" s="106" t="inlineStr">
+      <c r="D54" s="105" t="inlineStr">
         <is>
           <t>fast_</t>
         </is>
@@ -6553,7 +6544,7 @@
         </is>
       </c>
       <c r="F54" s="38" t="n"/>
-      <c r="G54" s="106" t="inlineStr">
+      <c r="G54" s="105" t="inlineStr">
         <is>
           <t>FAST_</t>
         </is>
@@ -6568,7 +6559,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J54" s="106" t="n">
+      <c r="J54" s="105" t="n">
         <v>0</v>
       </c>
       <c r="K54" s="38" t="n">
@@ -6641,7 +6632,7 @@
           <t>height</t>
         </is>
       </c>
-      <c r="D55" s="107" t="inlineStr">
+      <c r="D55" s="106" t="inlineStr">
         <is>
           <t>height</t>
         </is>
@@ -6656,7 +6647,7 @@
           <t>HEIGHT</t>
         </is>
       </c>
-      <c r="G55" s="107" t="inlineStr">
+      <c r="G55" s="106" t="inlineStr">
         <is>
           <t>HEIGHT</t>
         </is>
@@ -6671,7 +6662,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J55" s="107" t="n">
+      <c r="J55" s="106" t="n">
         <v>50</v>
       </c>
       <c r="K55" s="41" t="n">
@@ -6748,7 +6739,7 @@
           <t>weight</t>
         </is>
       </c>
-      <c r="D56" s="107" t="inlineStr">
+      <c r="D56" s="106" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
@@ -6763,7 +6754,7 @@
           <t>WEIGHT</t>
         </is>
       </c>
-      <c r="G56" s="107" t="inlineStr">
+      <c r="G56" s="106" t="inlineStr">
         <is>
           <t>WEIGHT</t>
         </is>
@@ -6778,7 +6769,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J56" s="107" t="n">
+      <c r="J56" s="106" t="n">
         <v>25</v>
       </c>
       <c r="K56" s="41" t="n">
@@ -6855,7 +6846,7 @@
           <t>bmi</t>
         </is>
       </c>
-      <c r="D57" s="107" t="inlineStr">
+      <c r="D57" s="106" t="inlineStr">
         <is>
           <t>bmi</t>
         </is>
@@ -6870,7 +6861,7 @@
           <t>BMI</t>
         </is>
       </c>
-      <c r="G57" s="107" t="inlineStr">
+      <c r="G57" s="106" t="inlineStr">
         <is>
           <t>BMI</t>
         </is>
@@ -6885,7 +6876,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J57" s="107" t="n">
+      <c r="J57" s="106" t="n">
         <v>8</v>
       </c>
       <c r="K57" s="41" t="n">
@@ -6962,7 +6953,7 @@
           <t>wstcir</t>
         </is>
       </c>
-      <c r="D58" s="107" t="inlineStr">
+      <c r="D58" s="106" t="inlineStr">
         <is>
           <t>wstcir</t>
         </is>
@@ -6977,7 +6968,7 @@
           <t>WSTCIR</t>
         </is>
       </c>
-      <c r="G58" s="107" t="inlineStr">
+      <c r="G58" s="106" t="inlineStr">
         <is>
           <t>WSTCIR</t>
         </is>
@@ -6992,7 +6983,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J58" s="107" t="n">
+      <c r="J58" s="106" t="n">
         <v>30</v>
       </c>
       <c r="K58" s="41" t="n">
@@ -7069,7 +7060,7 @@
           <t>sysbpsupine</t>
         </is>
       </c>
-      <c r="D59" s="107" t="inlineStr">
+      <c r="D59" s="106" t="inlineStr">
         <is>
           <t>sysbpsupine</t>
         </is>
@@ -7084,7 +7075,7 @@
           <t>SYSBPSUPINE</t>
         </is>
       </c>
-      <c r="G59" s="107" t="inlineStr">
+      <c r="G59" s="106" t="inlineStr">
         <is>
           <t>SYSBPSUPINE</t>
         </is>
@@ -7099,7 +7090,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J59" s="107" t="n">
+      <c r="J59" s="106" t="n">
         <v>50</v>
       </c>
       <c r="K59" s="41" t="n">
@@ -7176,7 +7167,7 @@
           <t>diabpsupine</t>
         </is>
       </c>
-      <c r="D60" s="107" t="inlineStr">
+      <c r="D60" s="106" t="inlineStr">
         <is>
           <t>diabpsupine</t>
         </is>
@@ -7191,7 +7182,7 @@
           <t>DIABPSUPINE</t>
         </is>
       </c>
-      <c r="G60" s="107" t="inlineStr">
+      <c r="G60" s="106" t="inlineStr">
         <is>
           <t>DIABPSUPINE</t>
         </is>
@@ -7206,7 +7197,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J60" s="107" t="n">
+      <c r="J60" s="106" t="n">
         <v>25</v>
       </c>
       <c r="K60" s="41" t="n">
@@ -7279,7 +7270,7 @@
         </is>
       </c>
       <c r="C61" s="41" t="n"/>
-      <c r="D61" s="107" t="inlineStr">
+      <c r="D61" s="106" t="inlineStr">
         <is>
           <t>hrsupine</t>
         </is>
@@ -7290,7 +7281,7 @@
         </is>
       </c>
       <c r="F61" s="41" t="n"/>
-      <c r="G61" s="107" t="inlineStr">
+      <c r="G61" s="106" t="inlineStr">
         <is>
           <t>HRSUPINE</t>
         </is>
@@ -7305,7 +7296,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J61" s="107" t="n">
+      <c r="J61" s="106" t="n">
         <v>25</v>
       </c>
       <c r="K61" s="41" t="n">
@@ -7378,7 +7369,7 @@
         </is>
       </c>
       <c r="C62" s="41" t="n"/>
-      <c r="D62" s="107" t="inlineStr">
+      <c r="D62" s="106" t="inlineStr">
         <is>
           <t>sysbpstanding</t>
         </is>
@@ -7389,7 +7380,7 @@
         </is>
       </c>
       <c r="F62" s="41" t="n"/>
-      <c r="G62" s="107" t="inlineStr">
+      <c r="G62" s="106" t="inlineStr">
         <is>
           <t>SYSBPSTANDING</t>
         </is>
@@ -7404,7 +7395,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J62" s="107" t="n">
+      <c r="J62" s="106" t="n">
         <v>50</v>
       </c>
       <c r="K62" s="41" t="n">
@@ -7477,7 +7468,7 @@
         </is>
       </c>
       <c r="C63" s="41" t="n"/>
-      <c r="D63" s="107" t="inlineStr">
+      <c r="D63" s="106" t="inlineStr">
         <is>
           <t>diabpstanding</t>
         </is>
@@ -7488,7 +7479,7 @@
         </is>
       </c>
       <c r="F63" s="41" t="n"/>
-      <c r="G63" s="107" t="inlineStr">
+      <c r="G63" s="106" t="inlineStr">
         <is>
           <t>DIABPSTANDING</t>
         </is>
@@ -7503,7 +7494,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J63" s="107" t="n">
+      <c r="J63" s="106" t="n">
         <v>25</v>
       </c>
       <c r="K63" s="41" t="n">
@@ -7576,7 +7567,7 @@
         </is>
       </c>
       <c r="C64" s="41" t="n"/>
-      <c r="D64" s="107" t="inlineStr">
+      <c r="D64" s="106" t="inlineStr">
         <is>
           <t>hrstanding</t>
         </is>
@@ -7587,7 +7578,7 @@
         </is>
       </c>
       <c r="F64" s="41" t="n"/>
-      <c r="G64" s="107" t="inlineStr">
+      <c r="G64" s="106" t="inlineStr">
         <is>
           <t>HRSTANDING</t>
         </is>
@@ -7602,7 +7593,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J64" s="107" t="n">
+      <c r="J64" s="106" t="n">
         <v>25</v>
       </c>
       <c r="K64" s="41" t="n">
@@ -7675,7 +7666,7 @@
         </is>
       </c>
       <c r="C65" s="41" t="n"/>
-      <c r="D65" s="107" t="inlineStr">
+      <c r="D65" s="106" t="inlineStr">
         <is>
           <t>eghrmn</t>
         </is>
@@ -7686,7 +7677,7 @@
         </is>
       </c>
       <c r="F65" s="41" t="n"/>
-      <c r="G65" s="107" t="inlineStr">
+      <c r="G65" s="106" t="inlineStr">
         <is>
           <t>EGHRMN</t>
         </is>
@@ -7701,7 +7692,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J65" s="107" t="n">
+      <c r="J65" s="106" t="n">
         <v>25</v>
       </c>
       <c r="K65" s="41" t="n">
@@ -7774,7 +7765,7 @@
         </is>
       </c>
       <c r="C66" s="41" t="n"/>
-      <c r="D66" s="107" t="inlineStr">
+      <c r="D66" s="106" t="inlineStr">
         <is>
           <t>qt</t>
         </is>
@@ -7785,7 +7776,7 @@
         </is>
       </c>
       <c r="F66" s="41" t="n"/>
-      <c r="G66" s="107" t="inlineStr">
+      <c r="G66" s="106" t="inlineStr">
         <is>
           <t>QT</t>
         </is>
@@ -7800,7 +7791,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J66" s="107" t="n"/>
+      <c r="J66" s="106" t="n"/>
       <c r="K66" s="41" t="n"/>
       <c r="L66" s="41" t="inlineStr">
         <is>
@@ -7869,7 +7860,7 @@
         </is>
       </c>
       <c r="C67" s="41" t="n"/>
-      <c r="D67" s="107" t="inlineStr">
+      <c r="D67" s="106" t="inlineStr">
         <is>
           <t>rr</t>
         </is>
@@ -7880,7 +7871,7 @@
         </is>
       </c>
       <c r="F67" s="41" t="n"/>
-      <c r="G67" s="107" t="inlineStr">
+      <c r="G67" s="106" t="inlineStr">
         <is>
           <t>RR</t>
         </is>
@@ -7895,7 +7886,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J67" s="107" t="n"/>
+      <c r="J67" s="106" t="n"/>
       <c r="K67" s="41" t="n"/>
       <c r="L67" s="41" t="inlineStr">
         <is>
@@ -7968,7 +7959,7 @@
           <t>qtc</t>
         </is>
       </c>
-      <c r="D68" s="108" t="inlineStr">
+      <c r="D68" s="107" t="inlineStr">
         <is>
           <t>qtc</t>
         </is>
@@ -7983,7 +7974,7 @@
           <t>QTC</t>
         </is>
       </c>
-      <c r="G68" s="108" t="inlineStr">
+      <c r="G68" s="107" t="inlineStr">
         <is>
           <t>QTC</t>
         </is>
@@ -7998,7 +7989,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J68" s="108" t="n"/>
+      <c r="J68" s="107" t="n"/>
       <c r="K68" s="46" t="n"/>
       <c r="L68" s="46" t="inlineStr">
         <is>
@@ -8067,7 +8058,7 @@
         </is>
       </c>
       <c r="C69" s="50" t="n"/>
-      <c r="D69" s="109" t="inlineStr">
+      <c r="D69" s="108" t="inlineStr">
         <is>
           <t>sodium</t>
         </is>
@@ -8078,7 +8069,7 @@
         </is>
       </c>
       <c r="F69" s="50" t="n"/>
-      <c r="G69" s="109" t="inlineStr">
+      <c r="G69" s="108" t="inlineStr">
         <is>
           <t>SODIUM</t>
         </is>
@@ -8093,7 +8084,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J69" s="109" t="n">
+      <c r="J69" s="108" t="n">
         <v>100</v>
       </c>
       <c r="K69" s="50" t="n">
@@ -8166,7 +8157,7 @@
         </is>
       </c>
       <c r="C70" s="50" t="n"/>
-      <c r="D70" s="109" t="inlineStr">
+      <c r="D70" s="108" t="inlineStr">
         <is>
           <t>k</t>
         </is>
@@ -8177,7 +8168,7 @@
         </is>
       </c>
       <c r="F70" s="50" t="n"/>
-      <c r="G70" s="109" t="inlineStr">
+      <c r="G70" s="108" t="inlineStr">
         <is>
           <t>K</t>
         </is>
@@ -8192,7 +8183,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J70" s="109" t="n">
+      <c r="J70" s="108" t="n">
         <v>1.5</v>
       </c>
       <c r="K70" s="50" t="n">
@@ -8265,7 +8256,7 @@
         </is>
       </c>
       <c r="C71" s="50" t="n"/>
-      <c r="D71" s="109" t="inlineStr">
+      <c r="D71" s="108" t="inlineStr">
         <is>
           <t>cl</t>
         </is>
@@ -8276,7 +8267,7 @@
         </is>
       </c>
       <c r="F71" s="50" t="n"/>
-      <c r="G71" s="109" t="inlineStr">
+      <c r="G71" s="108" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
@@ -8291,7 +8282,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J71" s="109" t="n">
+      <c r="J71" s="108" t="n">
         <v>70</v>
       </c>
       <c r="K71" s="50" t="n">
@@ -8364,7 +8355,7 @@
         </is>
       </c>
       <c r="C72" s="50" t="n"/>
-      <c r="D72" s="109" t="inlineStr">
+      <c r="D72" s="108" t="inlineStr">
         <is>
           <t>bicarb</t>
         </is>
@@ -8375,7 +8366,7 @@
         </is>
       </c>
       <c r="F72" s="50" t="n"/>
-      <c r="G72" s="109" t="inlineStr">
+      <c r="G72" s="108" t="inlineStr">
         <is>
           <t>BICARB</t>
         </is>
@@ -8390,7 +8381,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J72" s="109" t="n">
+      <c r="J72" s="108" t="n">
         <v>5</v>
       </c>
       <c r="K72" s="50" t="n">
@@ -8463,7 +8454,7 @@
         </is>
       </c>
       <c r="C73" s="50" t="n"/>
-      <c r="D73" s="109" t="inlineStr">
+      <c r="D73" s="108" t="inlineStr">
         <is>
           <t>prot</t>
         </is>
@@ -8474,7 +8465,7 @@
         </is>
       </c>
       <c r="F73" s="50" t="n"/>
-      <c r="G73" s="109" t="inlineStr">
+      <c r="G73" s="108" t="inlineStr">
         <is>
           <t>PROT</t>
         </is>
@@ -8489,7 +8480,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J73" s="109" t="n">
+      <c r="J73" s="108" t="n">
         <v>25</v>
       </c>
       <c r="K73" s="50" t="n">
@@ -8562,7 +8553,7 @@
         </is>
       </c>
       <c r="C74" s="50" t="n"/>
-      <c r="D74" s="109" t="inlineStr">
+      <c r="D74" s="108" t="inlineStr">
         <is>
           <t>alb</t>
         </is>
@@ -8573,7 +8564,7 @@
         </is>
       </c>
       <c r="F74" s="50" t="n"/>
-      <c r="G74" s="109" t="inlineStr">
+      <c r="G74" s="108" t="inlineStr">
         <is>
           <t>ALB</t>
         </is>
@@ -8588,7 +8579,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J74" s="109" t="n">
+      <c r="J74" s="108" t="n">
         <v>10</v>
       </c>
       <c r="K74" s="50" t="n">
@@ -8661,7 +8652,7 @@
         </is>
       </c>
       <c r="C75" s="50" t="n"/>
-      <c r="D75" s="109" t="inlineStr">
+      <c r="D75" s="108" t="inlineStr">
         <is>
           <t>urea</t>
         </is>
@@ -8672,7 +8663,7 @@
         </is>
       </c>
       <c r="F75" s="50" t="n"/>
-      <c r="G75" s="109" t="inlineStr">
+      <c r="G75" s="108" t="inlineStr">
         <is>
           <t>UREA</t>
         </is>
@@ -8687,7 +8678,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J75" s="109" t="n">
+      <c r="J75" s="108" t="n">
         <v>0.5</v>
       </c>
       <c r="K75" s="50" t="n">
@@ -8764,7 +8755,7 @@
           <t>urate</t>
         </is>
       </c>
-      <c r="D76" s="109" t="inlineStr">
+      <c r="D76" s="108" t="inlineStr">
         <is>
           <t>urate</t>
         </is>
@@ -8779,7 +8770,7 @@
           <t>URATE</t>
         </is>
       </c>
-      <c r="G76" s="109" t="inlineStr">
+      <c r="G76" s="108" t="inlineStr">
         <is>
           <t>URATE</t>
         </is>
@@ -8794,7 +8785,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J76" s="109" t="n">
+      <c r="J76" s="108" t="n">
         <v>30</v>
       </c>
       <c r="K76" s="50" t="n">
@@ -8871,7 +8862,7 @@
         </is>
       </c>
       <c r="C77" s="50" t="n"/>
-      <c r="D77" s="109" t="inlineStr">
+      <c r="D77" s="108" t="inlineStr">
         <is>
           <t>creat</t>
         </is>
@@ -8882,7 +8873,7 @@
         </is>
       </c>
       <c r="F77" s="50" t="n"/>
-      <c r="G77" s="109" t="inlineStr">
+      <c r="G77" s="108" t="inlineStr">
         <is>
           <t>CREAT</t>
         </is>
@@ -8897,7 +8888,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J77" s="109" t="n">
+      <c r="J77" s="108" t="n">
         <v>10</v>
       </c>
       <c r="K77" s="50" t="n">
@@ -8970,7 +8961,7 @@
         </is>
       </c>
       <c r="C78" s="50" t="n"/>
-      <c r="D78" s="109" t="inlineStr">
+      <c r="D78" s="108" t="inlineStr">
         <is>
           <t>creatclr</t>
         </is>
@@ -8981,7 +8972,7 @@
         </is>
       </c>
       <c r="F78" s="50" t="n"/>
-      <c r="G78" s="109" t="inlineStr">
+      <c r="G78" s="108" t="inlineStr">
         <is>
           <t>CREATCLR</t>
         </is>
@@ -8996,7 +8987,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J78" s="109" t="n">
+      <c r="J78" s="108" t="n">
         <v>0</v>
       </c>
       <c r="K78" s="50" t="n">
@@ -9069,7 +9060,7 @@
         </is>
       </c>
       <c r="C79" s="50" t="n"/>
-      <c r="D79" s="109" t="inlineStr">
+      <c r="D79" s="108" t="inlineStr">
         <is>
           <t>phos</t>
         </is>
@@ -9080,7 +9071,7 @@
         </is>
       </c>
       <c r="F79" s="50" t="n"/>
-      <c r="G79" s="109" t="inlineStr">
+      <c r="G79" s="108" t="inlineStr">
         <is>
           <t>PHOS</t>
         </is>
@@ -9095,7 +9086,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J79" s="109" t="n">
+      <c r="J79" s="108" t="n">
         <v>0.2</v>
       </c>
       <c r="K79" s="50" t="n">
@@ -9168,7 +9159,7 @@
         </is>
       </c>
       <c r="C80" s="50" t="n"/>
-      <c r="D80" s="109" t="inlineStr">
+      <c r="D80" s="108" t="inlineStr">
         <is>
           <t>iron</t>
         </is>
@@ -9179,7 +9170,7 @@
         </is>
       </c>
       <c r="F80" s="50" t="n"/>
-      <c r="G80" s="109" t="inlineStr">
+      <c r="G80" s="108" t="inlineStr">
         <is>
           <t>IRON</t>
         </is>
@@ -9194,7 +9185,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J80" s="109" t="n">
+      <c r="J80" s="108" t="n">
         <v>1</v>
       </c>
       <c r="K80" s="50" t="n">
@@ -9267,7 +9258,7 @@
         </is>
       </c>
       <c r="C81" s="50" t="n"/>
-      <c r="D81" s="109" t="inlineStr">
+      <c r="D81" s="108" t="inlineStr">
         <is>
           <t>ca</t>
         </is>
@@ -9278,7 +9269,7 @@
         </is>
       </c>
       <c r="F81" s="50" t="n"/>
-      <c r="G81" s="109" t="inlineStr">
+      <c r="G81" s="108" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
@@ -9293,7 +9284,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J81" s="109" t="n">
+      <c r="J81" s="108" t="n">
         <v>1.2</v>
       </c>
       <c r="K81" s="50" t="n">
@@ -9370,7 +9361,7 @@
           <t>crp</t>
         </is>
       </c>
-      <c r="D82" s="109" t="inlineStr">
+      <c r="D82" s="108" t="inlineStr">
         <is>
           <t>crp</t>
         </is>
@@ -9385,7 +9376,7 @@
           <t>CRP</t>
         </is>
       </c>
-      <c r="G82" s="109" t="inlineStr">
+      <c r="G82" s="108" t="inlineStr">
         <is>
           <t>CRP</t>
         </is>
@@ -9400,7 +9391,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J82" s="109" t="n">
+      <c r="J82" s="108" t="n">
         <v>0</v>
       </c>
       <c r="K82" s="50" t="n">
@@ -9481,7 +9472,7 @@
           <t>gluc</t>
         </is>
       </c>
-      <c r="D83" s="109" t="inlineStr">
+      <c r="D83" s="108" t="inlineStr">
         <is>
           <t>gluc</t>
         </is>
@@ -9496,7 +9487,7 @@
           <t>GLUC</t>
         </is>
       </c>
-      <c r="G83" s="109" t="inlineStr">
+      <c r="G83" s="108" t="inlineStr">
         <is>
           <t>GLUC</t>
         </is>
@@ -9511,7 +9502,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J83" s="109" t="n">
+      <c r="J83" s="108" t="n">
         <v>0.5</v>
       </c>
       <c r="K83" s="50" t="n">
@@ -9592,7 +9583,7 @@
           <t>hba1c</t>
         </is>
       </c>
-      <c r="D84" s="109" t="inlineStr">
+      <c r="D84" s="108" t="inlineStr">
         <is>
           <t>hba1c</t>
         </is>
@@ -9607,7 +9598,7 @@
           <t>HBA1C</t>
         </is>
       </c>
-      <c r="G84" s="109" t="inlineStr">
+      <c r="G84" s="108" t="inlineStr">
         <is>
           <t>HBA1C</t>
         </is>
@@ -9622,7 +9613,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J84" s="109" t="n">
+      <c r="J84" s="108" t="n">
         <v>3</v>
       </c>
       <c r="K84" s="50" t="n">
@@ -9703,7 +9694,7 @@
           <t>hdl</t>
         </is>
       </c>
-      <c r="D85" s="109" t="inlineStr">
+      <c r="D85" s="108" t="inlineStr">
         <is>
           <t>hdl</t>
         </is>
@@ -9718,7 +9709,7 @@
           <t>HDL</t>
         </is>
       </c>
-      <c r="G85" s="109" t="inlineStr">
+      <c r="G85" s="108" t="inlineStr">
         <is>
           <t>HDL</t>
         </is>
@@ -9733,7 +9724,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J85" s="109" t="n">
+      <c r="J85" s="108" t="n">
         <v>0.1</v>
       </c>
       <c r="K85" s="50" t="n">
@@ -9814,7 +9805,7 @@
           <t>ldl</t>
         </is>
       </c>
-      <c r="D86" s="109" t="inlineStr">
+      <c r="D86" s="108" t="inlineStr">
         <is>
           <t>ldl</t>
         </is>
@@ -9829,7 +9820,7 @@
           <t>LDL</t>
         </is>
       </c>
-      <c r="G86" s="109" t="inlineStr">
+      <c r="G86" s="108" t="inlineStr">
         <is>
           <t>LDL</t>
         </is>
@@ -9844,7 +9835,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J86" s="109" t="n">
+      <c r="J86" s="108" t="n">
         <v>0.2</v>
       </c>
       <c r="K86" s="50" t="n">
@@ -9925,7 +9916,7 @@
           <t>chol</t>
         </is>
       </c>
-      <c r="D87" s="109" t="inlineStr">
+      <c r="D87" s="108" t="inlineStr">
         <is>
           <t>chol</t>
         </is>
@@ -9940,7 +9931,7 @@
           <t>CHOL</t>
         </is>
       </c>
-      <c r="G87" s="109" t="inlineStr">
+      <c r="G87" s="108" t="inlineStr">
         <is>
           <t>CHOL</t>
         </is>
@@ -9955,7 +9946,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J87" s="109" t="n">
+      <c r="J87" s="108" t="n">
         <v>1</v>
       </c>
       <c r="K87" s="50" t="n">
@@ -10036,7 +10027,7 @@
           <t>cholhdl</t>
         </is>
       </c>
-      <c r="D88" s="109" t="n"/>
+      <c r="D88" s="108" t="n"/>
       <c r="E88" s="50" t="inlineStr">
         <is>
           <t>CHOLHDL_LBSTRESC</t>
@@ -10047,7 +10038,7 @@
           <t>CHOLHDL</t>
         </is>
       </c>
-      <c r="G88" s="109" t="n"/>
+      <c r="G88" s="108" t="n"/>
       <c r="H88" s="50" t="inlineStr">
         <is>
           <t>Rapport Cholestérol Total / HDL</t>
@@ -10058,7 +10049,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J88" s="109" t="n">
+      <c r="J88" s="108" t="n">
         <v>0.5</v>
       </c>
       <c r="K88" s="50" t="n">
@@ -10135,7 +10126,7 @@
           <t>trig</t>
         </is>
       </c>
-      <c r="D89" s="109" t="inlineStr">
+      <c r="D89" s="108" t="inlineStr">
         <is>
           <t>trig</t>
         </is>
@@ -10150,7 +10141,7 @@
           <t>TRIG</t>
         </is>
       </c>
-      <c r="G89" s="109" t="inlineStr">
+      <c r="G89" s="108" t="inlineStr">
         <is>
           <t>TRIG</t>
         </is>
@@ -10165,7 +10156,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J89" s="109" t="n">
+      <c r="J89" s="108" t="n">
         <v>0.1</v>
       </c>
       <c r="K89" s="50" t="n">
@@ -10242,7 +10233,7 @@
         </is>
       </c>
       <c r="C90" s="50" t="n"/>
-      <c r="D90" s="109" t="inlineStr">
+      <c r="D90" s="108" t="inlineStr">
         <is>
           <t>alp</t>
         </is>
@@ -10253,7 +10244,7 @@
         </is>
       </c>
       <c r="F90" s="50" t="n"/>
-      <c r="G90" s="109" t="inlineStr">
+      <c r="G90" s="108" t="inlineStr">
         <is>
           <t>ALP</t>
         </is>
@@ -10268,7 +10259,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J90" s="109" t="n">
+      <c r="J90" s="108" t="n">
         <v>10</v>
       </c>
       <c r="K90" s="50" t="n">
@@ -10341,7 +10332,7 @@
         </is>
       </c>
       <c r="C91" s="50" t="n"/>
-      <c r="D91" s="109" t="inlineStr">
+      <c r="D91" s="108" t="inlineStr">
         <is>
           <t>ast</t>
         </is>
@@ -10352,7 +10343,7 @@
         </is>
       </c>
       <c r="F91" s="50" t="n"/>
-      <c r="G91" s="109" t="inlineStr">
+      <c r="G91" s="108" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
@@ -10367,7 +10358,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J91" s="109" t="n">
+      <c r="J91" s="108" t="n">
         <v>1</v>
       </c>
       <c r="K91" s="50" t="n">
@@ -10440,7 +10431,7 @@
         </is>
       </c>
       <c r="C92" s="50" t="n"/>
-      <c r="D92" s="109" t="inlineStr">
+      <c r="D92" s="108" t="inlineStr">
         <is>
           <t>alt</t>
         </is>
@@ -10451,7 +10442,7 @@
         </is>
       </c>
       <c r="F92" s="50" t="n"/>
-      <c r="G92" s="109" t="inlineStr">
+      <c r="G92" s="108" t="inlineStr">
         <is>
           <t>ALT</t>
         </is>
@@ -10466,7 +10457,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J92" s="109" t="n">
+      <c r="J92" s="108" t="n">
         <v>1</v>
       </c>
       <c r="K92" s="50" t="n">
@@ -10539,7 +10530,7 @@
         </is>
       </c>
       <c r="C93" s="50" t="n"/>
-      <c r="D93" s="109" t="inlineStr">
+      <c r="D93" s="108" t="inlineStr">
         <is>
           <t>bili</t>
         </is>
@@ -10550,7 +10541,7 @@
         </is>
       </c>
       <c r="F93" s="50" t="n"/>
-      <c r="G93" s="109" t="inlineStr">
+      <c r="G93" s="108" t="inlineStr">
         <is>
           <t>BILI</t>
         </is>
@@ -10565,7 +10556,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J93" s="109" t="n">
+      <c r="J93" s="108" t="n">
         <v>1</v>
       </c>
       <c r="K93" s="50" t="n">
@@ -10638,7 +10629,7 @@
         </is>
       </c>
       <c r="C94" s="50" t="n"/>
-      <c r="D94" s="109" t="inlineStr">
+      <c r="D94" s="108" t="inlineStr">
         <is>
           <t>ggt</t>
         </is>
@@ -10649,7 +10640,7 @@
         </is>
       </c>
       <c r="F94" s="50" t="n"/>
-      <c r="G94" s="109" t="inlineStr">
+      <c r="G94" s="108" t="inlineStr">
         <is>
           <t>GGT</t>
         </is>
@@ -10664,7 +10655,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J94" s="109" t="n">
+      <c r="J94" s="108" t="n">
         <v>1</v>
       </c>
       <c r="K94" s="50" t="n">
@@ -10737,7 +10728,7 @@
         </is>
       </c>
       <c r="C95" s="50" t="n"/>
-      <c r="D95" s="109" t="inlineStr">
+      <c r="D95" s="108" t="inlineStr">
         <is>
           <t>tsh</t>
         </is>
@@ -10748,7 +10739,7 @@
         </is>
       </c>
       <c r="F95" s="50" t="n"/>
-      <c r="G95" s="109" t="inlineStr">
+      <c r="G95" s="108" t="inlineStr">
         <is>
           <t>TSH</t>
         </is>
@@ -10763,7 +10754,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J95" s="109" t="n">
+      <c r="J95" s="108" t="n">
         <v>0</v>
       </c>
       <c r="K95" s="50" t="n">
@@ -10836,7 +10827,7 @@
         </is>
       </c>
       <c r="C96" s="50" t="n"/>
-      <c r="D96" s="109" t="inlineStr">
+      <c r="D96" s="108" t="inlineStr">
         <is>
           <t>t3fr</t>
         </is>
@@ -10847,7 +10838,7 @@
         </is>
       </c>
       <c r="F96" s="50" t="n"/>
-      <c r="G96" s="109" t="inlineStr">
+      <c r="G96" s="108" t="inlineStr">
         <is>
           <t>T3FR</t>
         </is>
@@ -10862,7 +10853,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J96" s="109" t="n">
+      <c r="J96" s="108" t="n">
         <v>0.5</v>
       </c>
       <c r="K96" s="50" t="n">
@@ -10935,7 +10926,7 @@
         </is>
       </c>
       <c r="C97" s="50" t="n"/>
-      <c r="D97" s="109" t="inlineStr">
+      <c r="D97" s="108" t="inlineStr">
         <is>
           <t>t4fr</t>
         </is>
@@ -10946,7 +10937,7 @@
         </is>
       </c>
       <c r="F97" s="50" t="n"/>
-      <c r="G97" s="109" t="inlineStr">
+      <c r="G97" s="108" t="inlineStr">
         <is>
           <t>T4FR</t>
         </is>
@@ -10961,7 +10952,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J97" s="109" t="n">
+      <c r="J97" s="108" t="n">
         <v>1</v>
       </c>
       <c r="K97" s="50" t="n">
@@ -11038,7 +11029,7 @@
           <t>wbc</t>
         </is>
       </c>
-      <c r="D98" s="109" t="inlineStr">
+      <c r="D98" s="108" t="inlineStr">
         <is>
           <t>wbc</t>
         </is>
@@ -11053,7 +11044,7 @@
           <t>WBC</t>
         </is>
       </c>
-      <c r="G98" s="109" t="inlineStr">
+      <c r="G98" s="108" t="inlineStr">
         <is>
           <t>WBC</t>
         </is>
@@ -11068,7 +11059,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J98" s="109" t="n">
+      <c r="J98" s="108" t="n">
         <v>0.1</v>
       </c>
       <c r="K98" s="50" t="n">
@@ -11149,7 +11140,7 @@
           <t>rbc</t>
         </is>
       </c>
-      <c r="D99" s="109" t="inlineStr">
+      <c r="D99" s="108" t="inlineStr">
         <is>
           <t>rbc</t>
         </is>
@@ -11164,7 +11155,7 @@
           <t>RBC</t>
         </is>
       </c>
-      <c r="G99" s="109" t="inlineStr">
+      <c r="G99" s="108" t="inlineStr">
         <is>
           <t>RBC</t>
         </is>
@@ -11179,7 +11170,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J99" s="109" t="n">
+      <c r="J99" s="108" t="n">
         <v>1</v>
       </c>
       <c r="K99" s="50" t="n">
@@ -11260,7 +11251,7 @@
           <t>hgb</t>
         </is>
       </c>
-      <c r="D100" s="109" t="inlineStr">
+      <c r="D100" s="108" t="inlineStr">
         <is>
           <t>hgb</t>
         </is>
@@ -11275,7 +11266,7 @@
           <t>HGB</t>
         </is>
       </c>
-      <c r="G100" s="109" t="inlineStr">
+      <c r="G100" s="108" t="inlineStr">
         <is>
           <t>HGB</t>
         </is>
@@ -11290,7 +11281,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J100" s="109" t="n">
+      <c r="J100" s="108" t="n">
         <v>3</v>
       </c>
       <c r="K100" s="50" t="n">
@@ -11367,7 +11358,7 @@
         </is>
       </c>
       <c r="C101" s="50" t="n"/>
-      <c r="D101" s="109" t="inlineStr">
+      <c r="D101" s="108" t="inlineStr">
         <is>
           <t>hct</t>
         </is>
@@ -11378,7 +11369,7 @@
         </is>
       </c>
       <c r="F101" s="50" t="n"/>
-      <c r="G101" s="109" t="inlineStr">
+      <c r="G101" s="108" t="inlineStr">
         <is>
           <t>HCT</t>
         </is>
@@ -11393,7 +11384,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J101" s="109" t="n"/>
+      <c r="J101" s="108" t="n"/>
       <c r="K101" s="50" t="n"/>
       <c r="L101" s="50" t="inlineStr">
         <is>
@@ -11466,7 +11457,7 @@
           <t>neut</t>
         </is>
       </c>
-      <c r="D102" s="109" t="inlineStr">
+      <c r="D102" s="108" t="inlineStr">
         <is>
           <t>neut</t>
         </is>
@@ -11481,7 +11472,7 @@
           <t>NEUT</t>
         </is>
       </c>
-      <c r="G102" s="109" t="inlineStr">
+      <c r="G102" s="108" t="inlineStr">
         <is>
           <t>NEUT</t>
         </is>
@@ -11496,7 +11487,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J102" s="109" t="n">
+      <c r="J102" s="108" t="n">
         <v>0</v>
       </c>
       <c r="K102" s="50" t="n">
@@ -11573,7 +11564,7 @@
         </is>
       </c>
       <c r="C103" s="50" t="n"/>
-      <c r="D103" s="109" t="inlineStr">
+      <c r="D103" s="108" t="inlineStr">
         <is>
           <t>baso</t>
         </is>
@@ -11584,7 +11575,7 @@
         </is>
       </c>
       <c r="F103" s="50" t="n"/>
-      <c r="G103" s="109" t="inlineStr">
+      <c r="G103" s="108" t="inlineStr">
         <is>
           <t>BASO</t>
         </is>
@@ -11599,7 +11590,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J103" s="109" t="n">
+      <c r="J103" s="108" t="n">
         <v>0</v>
       </c>
       <c r="K103" s="50" t="n">
@@ -11676,7 +11667,7 @@
           <t>eos</t>
         </is>
       </c>
-      <c r="D104" s="109" t="inlineStr">
+      <c r="D104" s="108" t="inlineStr">
         <is>
           <t>eos</t>
         </is>
@@ -11691,7 +11682,7 @@
           <t>EOS</t>
         </is>
       </c>
-      <c r="G104" s="109" t="inlineStr">
+      <c r="G104" s="108" t="inlineStr">
         <is>
           <t>EOS</t>
         </is>
@@ -11706,7 +11697,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J104" s="109" t="n">
+      <c r="J104" s="108" t="n">
         <v>0</v>
       </c>
       <c r="K104" s="50" t="n">
@@ -11783,7 +11774,7 @@
         </is>
       </c>
       <c r="C105" s="50" t="n"/>
-      <c r="D105" s="109" t="inlineStr">
+      <c r="D105" s="108" t="inlineStr">
         <is>
           <t>lym</t>
         </is>
@@ -11794,7 +11785,7 @@
         </is>
       </c>
       <c r="F105" s="50" t="n"/>
-      <c r="G105" s="109" t="inlineStr">
+      <c r="G105" s="108" t="inlineStr">
         <is>
           <t>LYM</t>
         </is>
@@ -11809,7 +11800,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J105" s="109" t="n">
+      <c r="J105" s="108" t="n">
         <v>0</v>
       </c>
       <c r="K105" s="50" t="n">
@@ -11882,7 +11873,7 @@
         </is>
       </c>
       <c r="C106" s="50" t="n"/>
-      <c r="D106" s="109" t="inlineStr">
+      <c r="D106" s="108" t="inlineStr">
         <is>
           <t>mono</t>
         </is>
@@ -11893,7 +11884,7 @@
         </is>
       </c>
       <c r="F106" s="50" t="n"/>
-      <c r="G106" s="109" t="inlineStr">
+      <c r="G106" s="108" t="inlineStr">
         <is>
           <t>MONO</t>
         </is>
@@ -11908,7 +11899,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J106" s="109" t="n">
+      <c r="J106" s="108" t="n">
         <v>0</v>
       </c>
       <c r="K106" s="50" t="n">
@@ -11985,7 +11976,7 @@
           <t>mcv</t>
         </is>
       </c>
-      <c r="D107" s="109" t="inlineStr">
+      <c r="D107" s="108" t="inlineStr">
         <is>
           <t>mcv</t>
         </is>
@@ -12000,7 +11991,7 @@
           <t>MCV</t>
         </is>
       </c>
-      <c r="G107" s="109" t="inlineStr">
+      <c r="G107" s="108" t="inlineStr">
         <is>
           <t>MCV</t>
         </is>
@@ -12015,7 +12006,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J107" s="109" t="n">
+      <c r="J107" s="108" t="n">
         <v>50</v>
       </c>
       <c r="K107" s="50" t="n">
@@ -12092,7 +12083,7 @@
         </is>
       </c>
       <c r="C108" s="50" t="n"/>
-      <c r="D108" s="109" t="inlineStr">
+      <c r="D108" s="108" t="inlineStr">
         <is>
           <t>mch</t>
         </is>
@@ -12103,7 +12094,7 @@
         </is>
       </c>
       <c r="F108" s="50" t="n"/>
-      <c r="G108" s="109" t="inlineStr">
+      <c r="G108" s="108" t="inlineStr">
         <is>
           <t>MCH</t>
         </is>
@@ -12118,7 +12109,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J108" s="109" t="n">
+      <c r="J108" s="108" t="n">
         <v>10</v>
       </c>
       <c r="K108" s="50" t="n">
@@ -12191,7 +12182,7 @@
         </is>
       </c>
       <c r="C109" s="50" t="n"/>
-      <c r="D109" s="109" t="inlineStr">
+      <c r="D109" s="108" t="inlineStr">
         <is>
           <t>mchc</t>
         </is>
@@ -12202,7 +12193,7 @@
         </is>
       </c>
       <c r="F109" s="50" t="n"/>
-      <c r="G109" s="109" t="inlineStr">
+      <c r="G109" s="108" t="inlineStr">
         <is>
           <t>MCHC</t>
         </is>
@@ -12217,7 +12208,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J109" s="109" t="n"/>
+      <c r="J109" s="108" t="n"/>
       <c r="K109" s="50" t="n"/>
       <c r="L109" s="50" t="inlineStr">
         <is>
@@ -12290,7 +12281,7 @@
           <t>plat</t>
         </is>
       </c>
-      <c r="D110" s="109" t="inlineStr">
+      <c r="D110" s="108" t="inlineStr">
         <is>
           <t>plat</t>
         </is>
@@ -12305,7 +12296,7 @@
           <t>PLAT</t>
         </is>
       </c>
-      <c r="G110" s="109" t="inlineStr">
+      <c r="G110" s="108" t="inlineStr">
         <is>
           <t>PLAT</t>
         </is>
@@ -12320,7 +12311,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J110" s="109" t="n">
+      <c r="J110" s="108" t="n">
         <v>1</v>
       </c>
       <c r="K110" s="50" t="n">
@@ -12397,7 +12388,7 @@
         </is>
       </c>
       <c r="C111" s="50" t="n"/>
-      <c r="D111" s="109" t="inlineStr">
+      <c r="D111" s="108" t="inlineStr">
         <is>
           <t>hcg</t>
         </is>
@@ -12408,7 +12399,7 @@
         </is>
       </c>
       <c r="F111" s="50" t="n"/>
-      <c r="G111" s="109" t="inlineStr">
+      <c r="G111" s="108" t="inlineStr">
         <is>
           <t>HCG</t>
         </is>
@@ -12423,7 +12414,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J111" s="109" t="n">
+      <c r="J111" s="108" t="n">
         <v>0</v>
       </c>
       <c r="K111" s="50" t="n">
@@ -12500,7 +12491,7 @@
           <t>prolctn</t>
         </is>
       </c>
-      <c r="D112" s="109" t="inlineStr">
+      <c r="D112" s="108" t="inlineStr">
         <is>
           <t>prolctn</t>
         </is>
@@ -12515,7 +12506,7 @@
           <t>PROLCTN</t>
         </is>
       </c>
-      <c r="G112" s="109" t="inlineStr">
+      <c r="G112" s="108" t="inlineStr">
         <is>
           <t>PROLCTN</t>
         </is>
@@ -12530,7 +12521,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J112" s="109" t="n">
+      <c r="J112" s="108" t="n">
         <v>0</v>
       </c>
       <c r="K112" s="50" t="n">
@@ -12607,7 +12598,7 @@
           <t>vitd</t>
         </is>
       </c>
-      <c r="D113" s="109" t="inlineStr">
+      <c r="D113" s="108" t="inlineStr">
         <is>
           <t>vitd</t>
         </is>
@@ -12618,7 +12609,7 @@
           <t>VITD</t>
         </is>
       </c>
-      <c r="G113" s="109" t="inlineStr">
+      <c r="G113" s="108" t="inlineStr">
         <is>
           <t>VITD</t>
         </is>
@@ -12633,7 +12624,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J113" s="109" t="n">
+      <c r="J113" s="108" t="n">
         <v>0</v>
       </c>
       <c r="K113" s="50" t="n">
@@ -12710,7 +12701,7 @@
           <t>clozapin</t>
         </is>
       </c>
-      <c r="D114" s="109" t="n"/>
+      <c r="D114" s="108" t="n"/>
       <c r="E114" s="50" t="inlineStr">
         <is>
           <t>CLOZAPIN</t>
@@ -12721,7 +12712,7 @@
           <t>CLOZAPIN</t>
         </is>
       </c>
-      <c r="G114" s="109" t="n"/>
+      <c r="G114" s="108" t="n"/>
       <c r="H114" s="50" t="inlineStr">
         <is>
           <t>Dosage plasmatique de clozapine (µg/L)</t>
@@ -12732,7 +12723,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J114" s="109" t="n">
+      <c r="J114" s="108" t="n">
         <v>0</v>
       </c>
       <c r="K114" s="50" t="n">
@@ -12805,7 +12796,7 @@
         </is>
       </c>
       <c r="C115" s="57" t="n"/>
-      <c r="D115" s="110" t="inlineStr">
+      <c r="D115" s="109" t="inlineStr">
         <is>
           <t>oxcarbaz</t>
         </is>
@@ -12816,7 +12807,7 @@
         </is>
       </c>
       <c r="F115" s="57" t="n"/>
-      <c r="G115" s="110" t="inlineStr">
+      <c r="G115" s="109" t="inlineStr">
         <is>
           <t>OXCARBAZ</t>
         </is>
@@ -12831,7 +12822,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J115" s="110" t="n">
+      <c r="J115" s="109" t="n">
         <v>0</v>
       </c>
       <c r="K115" s="57" t="n">
@@ -12908,7 +12899,7 @@
           <t>agemere</t>
         </is>
       </c>
-      <c r="D116" s="107" t="inlineStr">
+      <c r="D116" s="106" t="inlineStr">
         <is>
           <t>agemere</t>
         </is>
@@ -12923,7 +12914,7 @@
           <t>AGEMERE</t>
         </is>
       </c>
-      <c r="G116" s="107" t="inlineStr">
+      <c r="G116" s="106" t="inlineStr">
         <is>
           <t>AGEMERE</t>
         </is>
@@ -12938,7 +12929,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J116" s="107" t="n">
+      <c r="J116" s="106" t="n">
         <v>12</v>
       </c>
       <c r="K116" s="41" t="n">
@@ -13027,7 +13018,7 @@
           <t>agepere</t>
         </is>
       </c>
-      <c r="D117" s="107" t="inlineStr">
+      <c r="D117" s="106" t="inlineStr">
         <is>
           <t>agepere</t>
         </is>
@@ -13042,7 +13033,7 @@
           <t>AGEPERE</t>
         </is>
       </c>
-      <c r="G117" s="107" t="inlineStr">
+      <c r="G117" s="106" t="inlineStr">
         <is>
           <t>AGEPERE</t>
         </is>
@@ -13057,7 +13048,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J117" s="107" t="n">
+      <c r="J117" s="106" t="n">
         <v>12</v>
       </c>
       <c r="K117" s="41" t="n">
@@ -13146,7 +13137,7 @@
           <t>prembrth</t>
         </is>
       </c>
-      <c r="D118" s="107" t="inlineStr">
+      <c r="D118" s="106" t="inlineStr">
         <is>
           <t>prembrth</t>
         </is>
@@ -13161,7 +13152,7 @@
           <t>PREMBRTH</t>
         </is>
       </c>
-      <c r="G118" s="107" t="inlineStr">
+      <c r="G118" s="106" t="inlineStr">
         <is>
           <t>PREMBRTH</t>
         </is>
@@ -13176,7 +13167,7 @@
           <t>1=prématurité; 2=à terme; 3=post-maturité; 0=ne sais pas</t>
         </is>
       </c>
-      <c r="J118" s="107" t="n"/>
+      <c r="J118" s="106" t="n"/>
       <c r="K118" s="41" t="n"/>
       <c r="L118" s="41" t="inlineStr">
         <is>
@@ -13261,7 +13252,7 @@
           <t>gstabrth</t>
         </is>
       </c>
-      <c r="D119" s="107" t="inlineStr">
+      <c r="D119" s="106" t="inlineStr">
         <is>
           <t>gstabrth</t>
         </is>
@@ -13276,7 +13267,7 @@
           <t>GSTABRTH</t>
         </is>
       </c>
-      <c r="G119" s="107" t="inlineStr">
+      <c r="G119" s="106" t="inlineStr">
         <is>
           <t>GSTABRTH</t>
         </is>
@@ -13291,7 +13282,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J119" s="107" t="n">
+      <c r="J119" s="106" t="n">
         <v>20</v>
       </c>
       <c r="K119" s="41" t="n">
@@ -13380,7 +13371,7 @@
           <t>naisstyp</t>
         </is>
       </c>
-      <c r="D120" s="107" t="inlineStr">
+      <c r="D120" s="106" t="inlineStr">
         <is>
           <t>naisstyp</t>
         </is>
@@ -13395,7 +13386,7 @@
           <t>NAISSTYP</t>
         </is>
       </c>
-      <c r="G120" s="107" t="inlineStr">
+      <c r="G120" s="106" t="inlineStr">
         <is>
           <t>NAISSTYP</t>
         </is>
@@ -13410,7 +13401,7 @@
           <t>1=voie basse; 2=césarienne; 0=ne sais pas</t>
         </is>
       </c>
-      <c r="J120" s="107" t="n"/>
+      <c r="J120" s="106" t="n"/>
       <c r="K120" s="41" t="n"/>
       <c r="L120" s="41" t="inlineStr">
         <is>
@@ -13495,7 +13486,7 @@
           <t>honeonat</t>
         </is>
       </c>
-      <c r="D121" s="107" t="inlineStr">
+      <c r="D121" s="106" t="inlineStr">
         <is>
           <t>honeonat</t>
         </is>
@@ -13510,7 +13501,7 @@
           <t>HONEONAT</t>
         </is>
       </c>
-      <c r="G121" s="107" t="inlineStr">
+      <c r="G121" s="106" t="inlineStr">
         <is>
           <t>HONEONAT</t>
         </is>
@@ -13525,7 +13516,7 @@
           <t>1=Oui; 0=Non</t>
         </is>
       </c>
-      <c r="J121" s="107" t="n"/>
+      <c r="J121" s="106" t="n"/>
       <c r="K121" s="41" t="n"/>
       <c r="L121" s="41" t="inlineStr">
         <is>
@@ -13606,7 +13597,7 @@
         </is>
       </c>
       <c r="C122" s="41" t="n"/>
-      <c r="D122" s="107" t="inlineStr">
+      <c r="D122" s="106" t="inlineStr">
         <is>
           <t>brthht</t>
         </is>
@@ -13617,7 +13608,7 @@
         </is>
       </c>
       <c r="F122" s="41" t="n"/>
-      <c r="G122" s="107" t="inlineStr">
+      <c r="G122" s="106" t="inlineStr">
         <is>
           <t>BRTHHT</t>
         </is>
@@ -13632,7 +13623,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J122" s="107" t="n">
+      <c r="J122" s="106" t="n">
         <v>20</v>
       </c>
       <c r="K122" s="41" t="n">
@@ -13701,7 +13692,7 @@
         </is>
       </c>
       <c r="C123" s="41" t="n"/>
-      <c r="D123" s="107" t="inlineStr">
+      <c r="D123" s="106" t="inlineStr">
         <is>
           <t>brthcirc</t>
         </is>
@@ -13712,7 +13703,7 @@
         </is>
       </c>
       <c r="F123" s="41" t="n"/>
-      <c r="G123" s="107" t="inlineStr">
+      <c r="G123" s="106" t="inlineStr">
         <is>
           <t>BRTHCIRC</t>
         </is>
@@ -13727,7 +13718,7 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="J123" s="107" t="n">
+      <c r="J123" s="106" t="n">
         <v>20</v>
       </c>
       <c r="K123" s="41" t="n">
@@ -13796,7 +13787,7 @@
         </is>
       </c>
       <c r="C124" s="10" t="n"/>
-      <c r="D124" s="101" t="inlineStr">
+      <c r="D124" s="100" t="inlineStr">
         <is>
           <t>apgr0106_1min</t>
         </is>
@@ -13807,7 +13798,7 @@
         </is>
       </c>
       <c r="F124" s="10" t="n"/>
-      <c r="G124" s="101" t="inlineStr">
+      <c r="G124" s="100" t="inlineStr">
         <is>
           <t>APGR0106_1min</t>
         </is>
@@ -13822,7 +13813,7 @@
           <t>NUM (0–10)</t>
         </is>
       </c>
-      <c r="J124" s="101" t="n">
+      <c r="J124" s="100" t="n">
         <v>0</v>
       </c>
       <c r="K124" s="10" t="n">
@@ -13863,7 +13854,7 @@
           <t>test score (see Codage)</t>
         </is>
       </c>
-      <c r="W124" s="126" t="inlineStr">
+      <c r="W124" s="125" t="inlineStr">
         <is>
           <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
         </is>
@@ -13880,90 +13871,90 @@
       </c>
     </row>
     <row r="125" ht="23" customFormat="1" customHeight="1" s="43">
-      <c r="A125" s="127" t="inlineStr">
+      <c r="A125" s="126" t="inlineStr">
         <is>
           <t>PERINATALITE</t>
         </is>
       </c>
-      <c r="B125" s="127" t="inlineStr">
+      <c r="B125" s="126" t="inlineStr">
         <is>
           <t>apgr0106_5min</t>
         </is>
       </c>
-      <c r="C125" s="127" t="n"/>
-      <c r="D125" s="128" t="inlineStr">
+      <c r="C125" s="126" t="n"/>
+      <c r="D125" s="127" t="inlineStr">
         <is>
           <t>apgr0106_5min</t>
         </is>
       </c>
-      <c r="E125" s="127" t="inlineStr">
+      <c r="E125" s="126" t="inlineStr">
         <is>
           <t>APGR0106_5min</t>
         </is>
       </c>
-      <c r="F125" s="127" t="n"/>
-      <c r="G125" s="128" t="inlineStr">
+      <c r="F125" s="126" t="n"/>
+      <c r="G125" s="127" t="inlineStr">
         <is>
           <t>APGR0106_5min</t>
         </is>
       </c>
-      <c r="H125" s="127" t="inlineStr">
+      <c r="H125" s="126" t="inlineStr">
         <is>
           <t>Score d'Apgar à 5 minutes</t>
         </is>
       </c>
-      <c r="I125" s="127" t="inlineStr">
+      <c r="I125" s="126" t="inlineStr">
         <is>
           <t>NUM (0–10)</t>
         </is>
       </c>
-      <c r="J125" s="128" t="n">
+      <c r="J125" s="127" t="n">
         <v>0</v>
       </c>
-      <c r="K125" s="127" t="n">
+      <c r="K125" s="126" t="n">
         <v>10</v>
       </c>
-      <c r="L125" s="127" t="inlineStr">
+      <c r="L125" s="126" t="inlineStr">
         <is>
           <t>5-minute Apgar score : the more prognostic of the two Apgar measurements, with low values robustly linked to cerebral palsy, intellectual disability and increased risk of later psychiatric disorders.</t>
         </is>
       </c>
-      <c r="M125" s="127" t="n"/>
-      <c r="N125" s="127" t="n"/>
-      <c r="O125" s="127" t="inlineStr">
+      <c r="M125" s="126" t="n"/>
+      <c r="N125" s="126" t="n"/>
+      <c r="O125" s="126" t="inlineStr">
         <is>
           <t>apgr0106_5min</t>
         </is>
       </c>
-      <c r="P125" s="127" t="n"/>
-      <c r="Q125" s="127" t="n"/>
-      <c r="R125" s="127" t="n"/>
-      <c r="S125" s="127" t="inlineStr">
+      <c r="P125" s="126" t="n"/>
+      <c r="Q125" s="126" t="n"/>
+      <c r="R125" s="126" t="n"/>
+      <c r="S125" s="126" t="inlineStr">
         <is>
           <t>apgr0106_5min</t>
         </is>
       </c>
-      <c r="T125" s="127" t="inlineStr">
+      <c r="T125" s="126" t="inlineStr">
         <is>
           <t>num</t>
         </is>
       </c>
-      <c r="U125" s="127" t="inlineStr">
+      <c r="U125" s="126" t="inlineStr">
         <is>
           <t>int8 categorical</t>
         </is>
       </c>
-      <c r="V125" s="127" t="inlineStr">
+      <c r="V125" s="126" t="inlineStr">
         <is>
           <t>{0, 4, 5, 6, 7, 8, 9, 10}</t>
         </is>
       </c>
-      <c r="W125" s="129" t="inlineStr">
+      <c r="W125" s="128" t="inlineStr">
         <is>
           <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
         </is>
       </c>
-      <c r="X125" s="127" t="inlineStr">
+      <c r="X125" s="126" t="inlineStr">
         <is>
           <t>apgr0106_5min</t>
         </is>
@@ -13990,7 +13981,7 @@
           <t>isf01</t>
         </is>
       </c>
-      <c r="D126" s="111" t="inlineStr">
+      <c r="D126" s="110" t="inlineStr">
         <is>
           <t>isf01</t>
         </is>
@@ -14005,7 +13996,7 @@
           <t>ISF01</t>
         </is>
       </c>
-      <c r="G126" s="111" t="inlineStr">
+      <c r="G126" s="110" t="inlineStr">
         <is>
           <t>ISF01</t>
         </is>
@@ -14020,7 +14011,7 @@
           <t>Y=Oui ; N=Non (BP/SZ) ; 1=Oui ; 0=Non (DR)</t>
         </is>
       </c>
-      <c r="J126" s="111" t="n"/>
+      <c r="J126" s="110" t="n"/>
       <c r="K126" s="25" t="n"/>
       <c r="L126" s="25" t="inlineStr">
         <is>
@@ -14094,7 +14085,7 @@
       </c>
     </row>
     <row r="127" ht="23" customFormat="1" customHeight="1" s="43">
-      <c r="A127" s="131" t="inlineStr">
+      <c r="A127" s="130" t="inlineStr">
         <is>
           <t>SUICIDE</t>
         </is>
@@ -14109,7 +14100,7 @@
           <t>isf01a</t>
         </is>
       </c>
-      <c r="D127" s="101" t="inlineStr">
+      <c r="D127" s="100" t="inlineStr">
         <is>
           <t>isf01a</t>
         </is>
@@ -14124,7 +14115,7 @@
           <t>ISF01A</t>
         </is>
       </c>
-      <c r="G127" s="101" t="inlineStr">
+      <c r="G127" s="100" t="inlineStr">
         <is>
           <t>ISF01A</t>
         </is>
@@ -14139,7 +14130,7 @@
           <t>0=la semaine dernière; 1=il y a entre deux semaines et douze mois; 2=il y a entre un et cinq ans; 3=il y a plus de cinq ans</t>
         </is>
       </c>
-      <c r="J127" s="101" t="n"/>
+      <c r="J127" s="100" t="n"/>
       <c r="K127" s="10" t="n"/>
       <c r="L127" s="10" t="inlineStr">
         <is>
@@ -14228,7 +14219,7 @@
           <t>isf02</t>
         </is>
       </c>
-      <c r="D128" s="111" t="inlineStr">
+      <c r="D128" s="110" t="inlineStr">
         <is>
           <t>isf02</t>
         </is>
@@ -14243,7 +14234,7 @@
           <t>ISF02</t>
         </is>
       </c>
-      <c r="G128" s="111" t="inlineStr">
+      <c r="G128" s="110" t="inlineStr">
         <is>
           <t>ISF02</t>
         </is>
@@ -14258,7 +14249,7 @@
           <t>Y=Oui ; N=Non (BP/SZ) ; 1=Oui ; 0=Non (DR)</t>
         </is>
       </c>
-      <c r="J128" s="111" t="n"/>
+      <c r="J128" s="110" t="n"/>
       <c r="K128" s="25" t="n"/>
       <c r="L128" s="25" t="inlineStr">
         <is>
@@ -14332,7 +14323,7 @@
       </c>
     </row>
     <row r="129" ht="23" customFormat="1" customHeight="1" s="43">
-      <c r="A129" s="131" t="inlineStr">
+      <c r="A129" s="130" t="inlineStr">
         <is>
           <t>SUICIDE</t>
         </is>
@@ -14347,7 +14338,7 @@
           <t>isf02a</t>
         </is>
       </c>
-      <c r="D129" s="101" t="inlineStr">
+      <c r="D129" s="100" t="inlineStr">
         <is>
           <t>isf02a</t>
         </is>
@@ -14362,7 +14353,7 @@
           <t>ISF02A</t>
         </is>
       </c>
-      <c r="G129" s="101" t="inlineStr">
+      <c r="G129" s="100" t="inlineStr">
         <is>
           <t>ISF02A</t>
         </is>
@@ -14377,7 +14368,7 @@
           <t>0=la semaine dernière; 1=il y a entre deux semaines et douze mois; 2=il y a entre un et cinq ans; 3=il y a plus de cinq ans</t>
         </is>
       </c>
-      <c r="J129" s="101" t="n"/>
+      <c r="J129" s="100" t="n"/>
       <c r="K129" s="10" t="n"/>
       <c r="L129" s="10" t="inlineStr">
         <is>
@@ -14466,7 +14457,7 @@
           <t>isf03</t>
         </is>
       </c>
-      <c r="D130" s="111" t="inlineStr">
+      <c r="D130" s="110" t="inlineStr">
         <is>
           <t>isf03</t>
         </is>
@@ -14481,7 +14472,7 @@
           <t>ISF03</t>
         </is>
       </c>
-      <c r="G130" s="111" t="inlineStr">
+      <c r="G130" s="110" t="inlineStr">
         <is>
           <t>ISF03</t>
         </is>
@@ -14496,7 +14487,7 @@
           <t>Y=Oui ; N=Non (BP/SZ) ; 1=Oui ; 0=Non (DR)</t>
         </is>
       </c>
-      <c r="J130" s="111" t="n"/>
+      <c r="J130" s="110" t="n"/>
       <c r="K130" s="25" t="n"/>
       <c r="L130" s="25" t="inlineStr">
         <is>
@@ -14569,8 +14560,8 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="23" customFormat="1" customHeight="1" s="130">
-      <c r="A131" s="131" t="inlineStr">
+    <row r="131" ht="23" customFormat="1" customHeight="1" s="129">
+      <c r="A131" s="130" t="inlineStr">
         <is>
           <t>SUICIDE</t>
         </is>
@@ -14585,7 +14576,7 @@
           <t>isf03a</t>
         </is>
       </c>
-      <c r="D131" s="101" t="inlineStr">
+      <c r="D131" s="100" t="inlineStr">
         <is>
           <t>isf03a</t>
         </is>
@@ -14600,7 +14591,7 @@
           <t>ISF03A</t>
         </is>
       </c>
-      <c r="G131" s="101" t="inlineStr">
+      <c r="G131" s="100" t="inlineStr">
         <is>
           <t>ISF03A</t>
         </is>
@@ -14615,7 +14606,7 @@
           <t>0=la semaine dernière; 1=il y a entre deux semaines et douze mois; 2=il y a entre un et cinq ans; 3=il y a plus de cinq ans</t>
         </is>
       </c>
-      <c r="J131" s="101" t="n"/>
+      <c r="J131" s="100" t="n"/>
       <c r="K131" s="10" t="n"/>
       <c r="L131" s="10" t="inlineStr">
         <is>
@@ -14704,7 +14695,7 @@
           <t>isf04</t>
         </is>
       </c>
-      <c r="D132" s="111" t="inlineStr">
+      <c r="D132" s="110" t="inlineStr">
         <is>
           <t>isf04</t>
         </is>
@@ -14719,7 +14710,7 @@
           <t>ISF04</t>
         </is>
       </c>
-      <c r="G132" s="111" t="inlineStr">
+      <c r="G132" s="110" t="inlineStr">
         <is>
           <t>ISF04</t>
         </is>
@@ -14734,7 +14725,7 @@
           <t>Y=Oui ; N=Non (BP/SZ) ; 1=Oui ; 0=Non (DR)</t>
         </is>
       </c>
-      <c r="J132" s="111" t="n"/>
+      <c r="J132" s="110" t="n"/>
       <c r="K132" s="25" t="n"/>
       <c r="L132" s="25" t="inlineStr">
         <is>
@@ -14808,7 +14799,7 @@
       </c>
     </row>
     <row r="133" ht="21" customFormat="1" customHeight="1" s="14">
-      <c r="A133" s="131" t="inlineStr">
+      <c r="A133" s="130" t="inlineStr">
         <is>
           <t>SUICIDE</t>
         </is>
@@ -14823,7 +14814,7 @@
           <t>isf04a</t>
         </is>
       </c>
-      <c r="D133" s="101" t="inlineStr">
+      <c r="D133" s="100" t="inlineStr">
         <is>
           <t>isf04a</t>
         </is>
@@ -14838,7 +14829,7 @@
           <t>ISF04A</t>
         </is>
       </c>
-      <c r="G133" s="101" t="inlineStr">
+      <c r="G133" s="100" t="inlineStr">
         <is>
           <t>ISF04A</t>
         </is>
@@ -14853,7 +14844,7 @@
           <t>0=la semaine dernière; 1=il y a entre deux semaines et douze mois; 2=il y a entre un et cinq ans; 3=il y a plus de cinq ans</t>
         </is>
       </c>
-      <c r="J133" s="101" t="n"/>
+      <c r="J133" s="100" t="n"/>
       <c r="K133" s="10" t="n"/>
       <c r="L133" s="10" t="inlineStr">
         <is>
@@ -14942,7 +14933,7 @@
           <t>isf05</t>
         </is>
       </c>
-      <c r="D134" s="111" t="inlineStr">
+      <c r="D134" s="110" t="inlineStr">
         <is>
           <t>isf05</t>
         </is>
@@ -14957,7 +14948,7 @@
           <t>ISF05</t>
         </is>
       </c>
-      <c r="G134" s="111" t="inlineStr">
+      <c r="G134" s="110" t="inlineStr">
         <is>
           <t>ISF05</t>
         </is>
@@ -14972,7 +14963,7 @@
           <t>Y=Oui ; N=Non (BP/SZ) ; 1=Oui ; 0=Non (DR)</t>
         </is>
       </c>
-      <c r="J134" s="111" t="n"/>
+      <c r="J134" s="110" t="n"/>
       <c r="K134" s="25" t="n"/>
       <c r="L134" s="25" t="inlineStr">
         <is>
@@ -15046,7 +15037,7 @@
       </c>
     </row>
     <row r="135" ht="21" customFormat="1" customHeight="1" s="14">
-      <c r="A135" s="131" t="inlineStr">
+      <c r="A135" s="130" t="inlineStr">
         <is>
           <t>SUICIDE</t>
         </is>
@@ -15061,7 +15052,7 @@
           <t>isf05a</t>
         </is>
       </c>
-      <c r="D135" s="101" t="inlineStr">
+      <c r="D135" s="100" t="inlineStr">
         <is>
           <t>isf05a</t>
         </is>
@@ -15076,7 +15067,7 @@
           <t>ISF05A</t>
         </is>
       </c>
-      <c r="G135" s="101" t="inlineStr">
+      <c r="G135" s="100" t="inlineStr">
         <is>
           <t>ISF05A</t>
         </is>
@@ -15091,7 +15082,7 @@
           <t>0=la semaine dernière; 1=il y a entre deux semaines et douze mois; 2=il y a entre un et cinq ans; 3=il y a plus de cinq ans</t>
         </is>
       </c>
-      <c r="J135" s="101" t="n"/>
+      <c r="J135" s="100" t="n"/>
       <c r="K135" s="10" t="n"/>
       <c r="L135" s="10" t="inlineStr">
         <is>
@@ -15180,7 +15171,7 @@
           <t>isf07</t>
         </is>
       </c>
-      <c r="D136" s="111" t="inlineStr">
+      <c r="D136" s="110" t="inlineStr">
         <is>
           <t>isf07</t>
         </is>
@@ -15195,7 +15186,7 @@
           <t>ISF07</t>
         </is>
       </c>
-      <c r="G136" s="111" t="inlineStr">
+      <c r="G136" s="110" t="inlineStr">
         <is>
           <t>ISF07</t>
         </is>
@@ -15210,7 +15201,7 @@
           <t>NUM (count)</t>
         </is>
       </c>
-      <c r="J136" s="111" t="n">
+      <c r="J136" s="110" t="n">
         <v>0</v>
       </c>
       <c r="K136" s="25" t="n">
@@ -15291,7 +15282,7 @@
           <t>isf08</t>
         </is>
       </c>
-      <c r="D137" s="111" t="inlineStr">
+      <c r="D137" s="110" t="inlineStr">
         <is>
           <t>isf08</t>
         </is>
@@ -15306,7 +15297,7 @@
           <t>ISF08</t>
         </is>
       </c>
-      <c r="G137" s="111" t="inlineStr">
+      <c r="G137" s="110" t="inlineStr">
         <is>
           <t>ISF08</t>
         </is>
@@ -15321,7 +15312,7 @@
           <t>Y=Oui ; N=Non (BP/SZ) ; 1=Oui ; 0=Non (DR) ; 2=Ne sais pas (SZ/DR)</t>
         </is>
       </c>
-      <c r="J137" s="111" t="n"/>
+      <c r="J137" s="110" t="n"/>
       <c r="K137" s="25" t="n"/>
       <c r="L137" s="25" t="inlineStr">
         <is>
@@ -15410,7 +15401,7 @@
           <t>isf08a</t>
         </is>
       </c>
-      <c r="D138" s="111" t="inlineStr">
+      <c r="D138" s="110" t="inlineStr">
         <is>
           <t>isf08a</t>
         </is>
@@ -15425,7 +15416,7 @@
           <t>ISF08A</t>
         </is>
       </c>
-      <c r="G138" s="111" t="inlineStr">
+      <c r="G138" s="110" t="inlineStr">
         <is>
           <t>ISF08A</t>
         </is>
@@ -15440,7 +15431,7 @@
           <t>NUM (count)</t>
         </is>
       </c>
-      <c r="J138" s="111" t="n">
+      <c r="J138" s="110" t="n">
         <v>0</v>
       </c>
       <c r="K138" s="25" t="n">
@@ -15521,7 +15512,7 @@
           <t>isf09</t>
         </is>
       </c>
-      <c r="D139" s="111" t="inlineStr">
+      <c r="D139" s="110" t="inlineStr">
         <is>
           <t>isf09</t>
         </is>
@@ -15536,7 +15527,7 @@
           <t>ISF09</t>
         </is>
       </c>
-      <c r="G139" s="111" t="inlineStr">
+      <c r="G139" s="110" t="inlineStr">
         <is>
           <t>ISF09</t>
         </is>
@@ -15551,7 +15542,7 @@
           <t>Y=Oui ; N=Non (BP/SZ) ; 1=Oui ; 0=Non (DR) ; 2=Ne sais pas (SZ/DR)</t>
         </is>
       </c>
-      <c r="J139" s="111" t="n"/>
+      <c r="J139" s="110" t="n"/>
       <c r="K139" s="25" t="n"/>
       <c r="L139" s="25" t="inlineStr">
         <is>
@@ -15640,7 +15631,7 @@
           <t>isf09a</t>
         </is>
       </c>
-      <c r="D140" s="111" t="inlineStr">
+      <c r="D140" s="110" t="inlineStr">
         <is>
           <t>isf09a</t>
         </is>
@@ -15655,7 +15646,7 @@
           <t>ISF09A</t>
         </is>
       </c>
-      <c r="G140" s="111" t="inlineStr">
+      <c r="G140" s="110" t="inlineStr">
         <is>
           <t>ISF09A</t>
         </is>
@@ -15670,7 +15661,7 @@
           <t>NUM (count)</t>
         </is>
       </c>
-      <c r="J140" s="111" t="n">
+      <c r="J140" s="110" t="n">
         <v>0</v>
       </c>
       <c r="K140" s="25" t="n">
@@ -15747,7 +15738,7 @@
         </is>
       </c>
       <c r="C141" s="25" t="n"/>
-      <c r="D141" s="111" t="inlineStr">
+      <c r="D141" s="110" t="inlineStr">
         <is>
           <t>ltsv01</t>
         </is>
@@ -15758,7 +15749,7 @@
         </is>
       </c>
       <c r="F141" s="25" t="n"/>
-      <c r="G141" s="111" t="inlineStr">
+      <c r="G141" s="110" t="inlineStr">
         <is>
           <t>LTSV01</t>
         </is>
@@ -15773,7 +15764,7 @@
           <t>Categorical</t>
         </is>
       </c>
-      <c r="J141" s="111" t="n"/>
+      <c r="J141" s="110" t="n"/>
       <c r="K141" s="25" t="n"/>
       <c r="L141" s="25" t="inlineStr">
         <is>
@@ -15842,7 +15833,7 @@
         </is>
       </c>
       <c r="C142" s="25" t="n"/>
-      <c r="D142" s="111" t="inlineStr">
+      <c r="D142" s="110" t="inlineStr">
         <is>
           <t>ltsv02</t>
         </is>
@@ -15853,7 +15844,7 @@
         </is>
       </c>
       <c r="F142" s="25" t="n"/>
-      <c r="G142" s="111" t="inlineStr">
+      <c r="G142" s="110" t="inlineStr">
         <is>
           <t>LTSV02</t>
         </is>
@@ -15868,7 +15859,7 @@
           <t>NUM (mètres)</t>
         </is>
       </c>
-      <c r="J142" s="111" t="n"/>
+      <c r="J142" s="110" t="n"/>
       <c r="K142" s="25" t="n"/>
       <c r="L142" s="25" t="inlineStr">
         <is>
@@ -15937,7 +15928,7 @@
         </is>
       </c>
       <c r="C143" s="25" t="n"/>
-      <c r="D143" s="111" t="inlineStr">
+      <c r="D143" s="110" t="inlineStr">
         <is>
           <t>ltsv03</t>
         </is>
@@ -15948,7 +15939,7 @@
         </is>
       </c>
       <c r="F143" s="25" t="n"/>
-      <c r="G143" s="111" t="inlineStr">
+      <c r="G143" s="110" t="inlineStr">
         <is>
           <t>LTSV03</t>
         </is>
@@ -15963,7 +15954,7 @@
           <t>Categorical (Columbia lethality)</t>
         </is>
       </c>
-      <c r="J143" s="111" t="n"/>
+      <c r="J143" s="110" t="n"/>
       <c r="K143" s="25" t="n"/>
       <c r="L143" s="25" t="inlineStr">
         <is>
@@ -16032,7 +16023,7 @@
         </is>
       </c>
       <c r="C144" s="25" t="n"/>
-      <c r="D144" s="111" t="inlineStr">
+      <c r="D144" s="110" t="inlineStr">
         <is>
           <t>ltsv04</t>
         </is>
@@ -16043,7 +16034,7 @@
         </is>
       </c>
       <c r="F144" s="25" t="n"/>
-      <c r="G144" s="111" t="inlineStr">
+      <c r="G144" s="110" t="inlineStr">
         <is>
           <t>LTSV04</t>
         </is>
@@ -16058,7 +16049,7 @@
           <t>Categorical (Columbia lethality)</t>
         </is>
       </c>
-      <c r="J144" s="111" t="n"/>
+      <c r="J144" s="110" t="n"/>
       <c r="K144" s="25" t="n"/>
       <c r="L144" s="25" t="inlineStr">
         <is>
@@ -16127,7 +16118,7 @@
         </is>
       </c>
       <c r="C145" s="25" t="n"/>
-      <c r="D145" s="111" t="inlineStr">
+      <c r="D145" s="110" t="inlineStr">
         <is>
           <t>ltsv05</t>
         </is>
@@ -16138,7 +16129,7 @@
         </is>
       </c>
       <c r="F145" s="25" t="n"/>
-      <c r="G145" s="111" t="inlineStr">
+      <c r="G145" s="110" t="inlineStr">
         <is>
           <t>LTSV05</t>
         </is>
@@ -16153,7 +16144,7 @@
           <t>Categorical (Columbia lethality)</t>
         </is>
       </c>
-      <c r="J145" s="111" t="n"/>
+      <c r="J145" s="110" t="n"/>
       <c r="K145" s="25" t="n"/>
       <c r="L145" s="25" t="inlineStr">
         <is>
@@ -16222,7 +16213,7 @@
         </is>
       </c>
       <c r="C146" s="25" t="n"/>
-      <c r="D146" s="111" t="inlineStr">
+      <c r="D146" s="110" t="inlineStr">
         <is>
           <t>ltsv06</t>
         </is>
@@ -16233,7 +16224,7 @@
         </is>
       </c>
       <c r="F146" s="25" t="n"/>
-      <c r="G146" s="111" t="inlineStr">
+      <c r="G146" s="110" t="inlineStr">
         <is>
           <t>LTSV06</t>
         </is>
@@ -16248,7 +16239,7 @@
           <t>Categorical (Columbia lethality)</t>
         </is>
       </c>
-      <c r="J146" s="111" t="n"/>
+      <c r="J146" s="110" t="n"/>
       <c r="K146" s="25" t="n"/>
       <c r="L146" s="25" t="inlineStr">
         <is>
@@ -16317,7 +16308,7 @@
         </is>
       </c>
       <c r="C147" s="25" t="n"/>
-      <c r="D147" s="111" t="inlineStr">
+      <c r="D147" s="110" t="inlineStr">
         <is>
           <t>ltsv07</t>
         </is>
@@ -16328,7 +16319,7 @@
         </is>
       </c>
       <c r="F147" s="25" t="n"/>
-      <c r="G147" s="111" t="inlineStr">
+      <c r="G147" s="110" t="inlineStr">
         <is>
           <t>LTSV07</t>
         </is>
@@ -16343,7 +16334,7 @@
           <t>Categorical (Columbia lethality)</t>
         </is>
       </c>
-      <c r="J147" s="111" t="n"/>
+      <c r="J147" s="110" t="n"/>
       <c r="K147" s="25" t="n"/>
       <c r="L147" s="25" t="inlineStr">
         <is>
@@ -16412,7 +16403,7 @@
         </is>
       </c>
       <c r="C148" s="25" t="n"/>
-      <c r="D148" s="111" t="inlineStr">
+      <c r="D148" s="110" t="inlineStr">
         <is>
           <t>ltsv09</t>
         </is>
@@ -16423,7 +16414,7 @@
         </is>
       </c>
       <c r="F148" s="25" t="n"/>
-      <c r="G148" s="111" t="inlineStr">
+      <c r="G148" s="110" t="inlineStr">
         <is>
           <t>LTSV09</t>
         </is>
@@ -16438,7 +16429,7 @@
           <t>Y=Oui ; N=Non (BP) ; 1=Oui ; 0=Non ; 2=Ne sais pas (DR)</t>
         </is>
       </c>
-      <c r="J148" s="111" t="n"/>
+      <c r="J148" s="110" t="n"/>
       <c r="K148" s="25" t="n"/>
       <c r="L148" s="25" t="inlineStr">
         <is>
@@ -16515,7 +16506,7 @@
         </is>
       </c>
       <c r="C149" s="25" t="n"/>
-      <c r="D149" s="111" t="inlineStr">
+      <c r="D149" s="110" t="inlineStr">
         <is>
           <t>ltsg01</t>
         </is>
@@ -16526,7 +16517,7 @@
         </is>
       </c>
       <c r="F149" s="25" t="n"/>
-      <c r="G149" s="111" t="inlineStr">
+      <c r="G149" s="110" t="inlineStr">
         <is>
           <t>LTSG01</t>
         </is>
@@ -16541,7 +16532,7 @@
           <t>Categorical</t>
         </is>
       </c>
-      <c r="J149" s="111" t="n"/>
+      <c r="J149" s="110" t="n"/>
       <c r="K149" s="25" t="n"/>
       <c r="L149" s="25" t="inlineStr">
         <is>
@@ -16610,7 +16601,7 @@
         </is>
       </c>
       <c r="C150" s="25" t="n"/>
-      <c r="D150" s="111" t="inlineStr">
+      <c r="D150" s="110" t="inlineStr">
         <is>
           <t>ltsg02</t>
         </is>
@@ -16621,7 +16612,7 @@
         </is>
       </c>
       <c r="F150" s="25" t="n"/>
-      <c r="G150" s="111" t="inlineStr">
+      <c r="G150" s="110" t="inlineStr">
         <is>
           <t>LTSG02</t>
         </is>
@@ -16636,7 +16627,7 @@
           <t>Categorical</t>
         </is>
       </c>
-      <c r="J150" s="111" t="n"/>
+      <c r="J150" s="110" t="n"/>
       <c r="K150" s="25" t="n"/>
       <c r="L150" s="25" t="inlineStr">
         <is>
@@ -16705,7 +16696,7 @@
         </is>
       </c>
       <c r="C151" s="25" t="n"/>
-      <c r="D151" s="111" t="inlineStr">
+      <c r="D151" s="110" t="inlineStr">
         <is>
           <t>ltsg03</t>
         </is>
@@ -16716,7 +16707,7 @@
         </is>
       </c>
       <c r="F151" s="25" t="n"/>
-      <c r="G151" s="111" t="inlineStr">
+      <c r="G151" s="110" t="inlineStr">
         <is>
           <t>LTSG03</t>
         </is>
@@ -16731,7 +16722,7 @@
           <t>Categorical</t>
         </is>
       </c>
-      <c r="J151" s="111" t="n"/>
+      <c r="J151" s="110" t="n"/>
       <c r="K151" s="25" t="n"/>
       <c r="L151" s="25" t="inlineStr">
         <is>
@@ -16800,7 +16791,7 @@
         </is>
       </c>
       <c r="C152" s="25" t="n"/>
-      <c r="D152" s="111" t="inlineStr">
+      <c r="D152" s="110" t="inlineStr">
         <is>
           <t>ltsg04</t>
         </is>
@@ -16811,7 +16802,7 @@
         </is>
       </c>
       <c r="F152" s="25" t="n"/>
-      <c r="G152" s="111" t="inlineStr">
+      <c r="G152" s="110" t="inlineStr">
         <is>
           <t>LTSG04</t>
         </is>
@@ -16826,7 +16817,7 @@
           <t>Categorical (Columbia lethality)</t>
         </is>
       </c>
-      <c r="J152" s="111" t="n"/>
+      <c r="J152" s="110" t="n"/>
       <c r="K152" s="25" t="n"/>
       <c r="L152" s="25" t="inlineStr">
         <is>
@@ -16895,7 +16886,7 @@
         </is>
       </c>
       <c r="C153" s="25" t="n"/>
-      <c r="D153" s="111" t="inlineStr">
+      <c r="D153" s="110" t="inlineStr">
         <is>
           <t>ltsg05</t>
         </is>
@@ -16906,7 +16897,7 @@
         </is>
       </c>
       <c r="F153" s="25" t="n"/>
-      <c r="G153" s="111" t="inlineStr">
+      <c r="G153" s="110" t="inlineStr">
         <is>
           <t>LTSG05</t>
         </is>
@@ -16921,7 +16912,7 @@
           <t>Categorical (Columbia lethality)</t>
         </is>
       </c>
-      <c r="J153" s="111" t="n"/>
+      <c r="J153" s="110" t="n"/>
       <c r="K153" s="25" t="n"/>
       <c r="L153" s="25" t="inlineStr">
         <is>
@@ -16990,7 +16981,7 @@
         </is>
       </c>
       <c r="C154" s="25" t="n"/>
-      <c r="D154" s="111" t="inlineStr">
+      <c r="D154" s="110" t="inlineStr">
         <is>
           <t>ltsg06</t>
         </is>
@@ -17001,7 +16992,7 @@
         </is>
       </c>
       <c r="F154" s="25" t="n"/>
-      <c r="G154" s="111" t="inlineStr">
+      <c r="G154" s="110" t="inlineStr">
         <is>
           <t>LTSG06</t>
         </is>
@@ -17016,7 +17007,7 @@
           <t>Categorical (Columbia lethality)</t>
         </is>
       </c>
-      <c r="J154" s="111" t="n"/>
+      <c r="J154" s="110" t="n"/>
       <c r="K154" s="25" t="n"/>
       <c r="L154" s="25" t="inlineStr">
         <is>
@@ -17074,7 +17065,7 @@
       </c>
     </row>
     <row r="155" ht="21" customFormat="1" customHeight="1" s="27">
-      <c r="A155" s="131" t="inlineStr">
+      <c r="A155" s="130" t="inlineStr">
         <is>
           <t>SUICIDE</t>
         </is>
@@ -17085,7 +17076,7 @@
         </is>
       </c>
       <c r="C155" s="10" t="n"/>
-      <c r="D155" s="101" t="inlineStr">
+      <c r="D155" s="100" t="inlineStr">
         <is>
           <t>ltsg07</t>
         </is>
@@ -17096,7 +17087,7 @@
         </is>
       </c>
       <c r="F155" s="10" t="n"/>
-      <c r="G155" s="101" t="inlineStr">
+      <c r="G155" s="100" t="inlineStr">
         <is>
           <t>LTSG07</t>
         </is>
@@ -17111,7 +17102,7 @@
           <t>Y=Oui ; N=Non (BP) ; 1=Oui ; 0=Non ; 2=Ne sais pas (DR)</t>
         </is>
       </c>
-      <c r="J155" s="101" t="n"/>
+      <c r="J155" s="100" t="n"/>
       <c r="K155" s="10" t="n"/>
       <c r="L155" s="10" t="inlineStr">
         <is>
@@ -17160,7 +17151,7 @@
           <t>{0=No/Non, 1=Yes/Oui, NA=Unknown}</t>
         </is>
       </c>
-      <c r="W155" s="126" t="inlineStr">
+      <c r="W155" s="125" t="inlineStr">
         <is>
           <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
         </is>
@@ -17188,7 +17179,7 @@
         </is>
       </c>
       <c r="C156" s="25" t="n"/>
-      <c r="D156" s="111" t="inlineStr">
+      <c r="D156" s="110" t="inlineStr">
         <is>
           <t>cssrs01</t>
         </is>
@@ -17199,7 +17190,7 @@
         </is>
       </c>
       <c r="F156" s="25" t="n"/>
-      <c r="G156" s="111" t="inlineStr">
+      <c r="G156" s="110" t="inlineStr">
         <is>
           <t>CSSRS01</t>
         </is>
@@ -17214,7 +17205,7 @@
           <t>Y=Oui ; N=Non (BP) ; 1=Oui ; 0=Non (DR)</t>
         </is>
       </c>
-      <c r="J156" s="111" t="n"/>
+      <c r="J156" s="110" t="n"/>
       <c r="K156" s="25" t="n"/>
       <c r="L156" s="25" t="inlineStr">
         <is>
@@ -17291,7 +17282,7 @@
         </is>
       </c>
       <c r="C157" s="25" t="n"/>
-      <c r="D157" s="111" t="inlineStr">
+      <c r="D157" s="110" t="inlineStr">
         <is>
           <t>cssrs02</t>
         </is>
@@ -17302,7 +17293,7 @@
         </is>
       </c>
       <c r="F157" s="25" t="n"/>
-      <c r="G157" s="111" t="inlineStr">
+      <c r="G157" s="110" t="inlineStr">
         <is>
           <t>CSSRS02</t>
         </is>
@@ -17317,7 +17308,7 @@
           <t>Y=Oui ; N=Non (BP) ; 1=Oui ; 0=Non (DR)</t>
         </is>
       </c>
-      <c r="J157" s="111" t="n"/>
+      <c r="J157" s="110" t="n"/>
       <c r="K157" s="25" t="n"/>
       <c r="L157" s="25" t="inlineStr">
         <is>
@@ -17394,7 +17385,7 @@
         </is>
       </c>
       <c r="C158" s="25" t="n"/>
-      <c r="D158" s="111" t="inlineStr">
+      <c r="D158" s="110" t="inlineStr">
         <is>
           <t>cssrs03</t>
         </is>
@@ -17405,7 +17396,7 @@
         </is>
       </c>
       <c r="F158" s="25" t="n"/>
-      <c r="G158" s="111" t="inlineStr">
+      <c r="G158" s="110" t="inlineStr">
         <is>
           <t>CSSRS03</t>
         </is>
@@ -17420,7 +17411,7 @@
           <t>Y=Oui ; N=Non (BP) ; 1=Oui ; 0=Non (DR)</t>
         </is>
       </c>
-      <c r="J158" s="111" t="n"/>
+      <c r="J158" s="110" t="n"/>
       <c r="K158" s="25" t="n"/>
       <c r="L158" s="25" t="inlineStr">
         <is>
@@ -17497,7 +17488,7 @@
         </is>
       </c>
       <c r="C159" s="25" t="n"/>
-      <c r="D159" s="111" t="inlineStr">
+      <c r="D159" s="110" t="inlineStr">
         <is>
           <t>cssrs04</t>
         </is>
@@ -17508,7 +17499,7 @@
         </is>
       </c>
       <c r="F159" s="25" t="n"/>
-      <c r="G159" s="111" t="inlineStr">
+      <c r="G159" s="110" t="inlineStr">
         <is>
           <t>CSSRS04</t>
         </is>
@@ -17523,7 +17514,7 @@
           <t>Y=Oui ; N=Non (BP) ; 1=Oui ; 0=Non (DR)</t>
         </is>
       </c>
-      <c r="J159" s="111" t="n"/>
+      <c r="J159" s="110" t="n"/>
       <c r="K159" s="25" t="n"/>
       <c r="L159" s="25" t="inlineStr">
         <is>
@@ -17600,7 +17591,7 @@
         </is>
       </c>
       <c r="C160" s="25" t="n"/>
-      <c r="D160" s="111" t="inlineStr">
+      <c r="D160" s="110" t="inlineStr">
         <is>
           <t>cssrs05</t>
         </is>
@@ -17611,7 +17602,7 @@
         </is>
       </c>
       <c r="F160" s="25" t="n"/>
-      <c r="G160" s="111" t="inlineStr">
+      <c r="G160" s="110" t="inlineStr">
         <is>
           <t>CSSRS05</t>
         </is>
@@ -17626,7 +17617,7 @@
           <t>Y=Oui ; N=Non (BP) ; 1=Oui ; 0=Non (DR)</t>
         </is>
       </c>
-      <c r="J160" s="111" t="n"/>
+      <c r="J160" s="110" t="n"/>
       <c r="K160" s="25" t="n"/>
       <c r="L160" s="25" t="inlineStr">
         <is>
@@ -17703,7 +17694,7 @@
         </is>
       </c>
       <c r="C161" s="25" t="n"/>
-      <c r="D161" s="111" t="inlineStr">
+      <c r="D161" s="110" t="inlineStr">
         <is>
           <t>cssrs06</t>
         </is>
@@ -17714,7 +17705,7 @@
         </is>
       </c>
       <c r="F161" s="25" t="n"/>
-      <c r="G161" s="111" t="inlineStr">
+      <c r="G161" s="110" t="inlineStr">
         <is>
           <t>CSSRS06</t>
         </is>
@@ -17729,7 +17720,7 @@
           <t>1=moins grave ; 5=plus grave</t>
         </is>
       </c>
-      <c r="J161" s="111" t="n">
+      <c r="J161" s="110" t="n">
         <v>1</v>
       </c>
       <c r="K161" s="25" t="n">
@@ -17810,7 +17801,7 @@
         </is>
       </c>
       <c r="C162" s="25" t="n"/>
-      <c r="D162" s="111" t="inlineStr">
+      <c r="D162" s="110" t="inlineStr">
         <is>
           <t>cssrs08</t>
         </is>
@@ -17821,7 +17812,7 @@
         </is>
       </c>
       <c r="F162" s="25" t="n"/>
-      <c r="G162" s="111" t="inlineStr">
+      <c r="G162" s="110" t="inlineStr">
         <is>
           <t>CSSRS08</t>
         </is>
@@ -17836,7 +17827,7 @@
           <t>1=moins d'une fois/semaine ... 5=plusieurs fois/jour</t>
         </is>
       </c>
-      <c r="J162" s="111" t="n">
+      <c r="J162" s="110" t="n">
         <v>1</v>
       </c>
       <c r="K162" s="25" t="n">
@@ -17917,7 +17908,7 @@
         </is>
       </c>
       <c r="C163" s="25" t="n"/>
-      <c r="D163" s="111" t="inlineStr">
+      <c r="D163" s="110" t="inlineStr">
         <is>
           <t>cssrs09</t>
         </is>
@@ -17928,7 +17919,7 @@
         </is>
       </c>
       <c r="F163" s="25" t="n"/>
-      <c r="G163" s="111" t="inlineStr">
+      <c r="G163" s="110" t="inlineStr">
         <is>
           <t>CSSRS09</t>
         </is>
@@ -17943,7 +17934,7 @@
           <t>1=quelques instants ... 5=continues/quasi-continues</t>
         </is>
       </c>
-      <c r="J163" s="111" t="n">
+      <c r="J163" s="110" t="n">
         <v>1</v>
       </c>
       <c r="K163" s="25" t="n">
@@ -18024,7 +18015,7 @@
         </is>
       </c>
       <c r="C164" s="25" t="n"/>
-      <c r="D164" s="111" t="inlineStr">
+      <c r="D164" s="110" t="inlineStr">
         <is>
           <t>cssrs10</t>
         </is>
@@ -18035,7 +18026,7 @@
         </is>
       </c>
       <c r="F164" s="25" t="n"/>
-      <c r="G164" s="111" t="inlineStr">
+      <c r="G164" s="110" t="inlineStr">
         <is>
           <t>CSSRS10</t>
         </is>
@@ -18050,7 +18041,7 @@
           <t>0=n'essaie pas ; 1=maîtrise facile ... 5=impossibilité totale</t>
         </is>
       </c>
-      <c r="J164" s="111" t="n">
+      <c r="J164" s="110" t="n">
         <v>0</v>
       </c>
       <c r="K164" s="25" t="n">
@@ -18131,7 +18122,7 @@
         </is>
       </c>
       <c r="C165" s="25" t="n"/>
-      <c r="D165" s="111" t="inlineStr">
+      <c r="D165" s="110" t="inlineStr">
         <is>
           <t>cssrs11</t>
         </is>
@@ -18142,7 +18133,7 @@
         </is>
       </c>
       <c r="F165" s="25" t="n"/>
-      <c r="G165" s="111" t="inlineStr">
+      <c r="G165" s="110" t="inlineStr">
         <is>
           <t>CSSRS11</t>
         </is>
@@ -18157,7 +18148,7 @@
           <t>0=sans objet ... 5=aucun élément dissuasif</t>
         </is>
       </c>
-      <c r="J165" s="111" t="n">
+      <c r="J165" s="110" t="n">
         <v>0</v>
       </c>
       <c r="K165" s="25" t="n">
@@ -18238,7 +18229,7 @@
         </is>
       </c>
       <c r="C166" s="65" t="n"/>
-      <c r="D166" s="112" t="inlineStr">
+      <c r="D166" s="111" t="inlineStr">
         <is>
           <t>cssrs12</t>
         </is>
@@ -18249,7 +18240,7 @@
         </is>
       </c>
       <c r="F166" s="65" t="n"/>
-      <c r="G166" s="112" t="inlineStr">
+      <c r="G166" s="111" t="inlineStr">
         <is>
           <t>CSSRS12</t>
         </is>
@@ -18264,7 +18255,7 @@
           <t>0=sans objet ... 5=mettre fin à la souffrance/escape</t>
         </is>
       </c>
-      <c r="J166" s="112" t="n">
+      <c r="J166" s="111" t="n">
         <v>0</v>
       </c>
       <c r="K166" s="65" t="n">
@@ -18349,7 +18340,7 @@
           <t>suncf_cigarettes_lt</t>
         </is>
       </c>
-      <c r="D167" s="101" t="inlineStr">
+      <c r="D167" s="100" t="inlineStr">
         <is>
           <t>suncf_cigarettes_lt</t>
         </is>
@@ -18364,7 +18355,7 @@
           <t>SUNCF_CIGARETTES_LT</t>
         </is>
       </c>
-      <c r="G167" s="101" t="inlineStr">
+      <c r="G167" s="100" t="inlineStr">
         <is>
           <t>SUNCF_CIGARETTES_LT</t>
         </is>
@@ -18379,7 +18370,7 @@
           <t>DR : 1=Non fumeur, 2=Ex-fumeur, 3=Fumeur actuel ; BP/SZ : codage libre déclaratif</t>
         </is>
       </c>
-      <c r="J167" s="101" t="n"/>
+      <c r="J167" s="100" t="n"/>
       <c r="K167" s="10" t="n"/>
       <c r="L167" s="10" t="inlineStr">
         <is>
@@ -18452,7 +18443,7 @@
           <t>sudose_cigarettes_lt</t>
         </is>
       </c>
-      <c r="D168" s="113" t="inlineStr">
+      <c r="D168" s="112" t="inlineStr">
         <is>
           <t>sudose_cigarettes_lt</t>
         </is>
@@ -18467,7 +18458,7 @@
           <t>SUDOSE_CIGARETTES_LT</t>
         </is>
       </c>
-      <c r="G168" s="113" t="inlineStr">
+      <c r="G168" s="112" t="inlineStr">
         <is>
           <t>SUDOSE_CIGARETTES_LT</t>
         </is>
@@ -18482,7 +18473,7 @@
           <t>Numérique (paquets-année)</t>
         </is>
       </c>
-      <c r="J168" s="113" t="n">
+      <c r="J168" s="112" t="n">
         <v>0</v>
       </c>
       <c r="K168" s="68" t="n">
@@ -18563,7 +18554,7 @@
           <t>agedebut_cigarettes_lt</t>
         </is>
       </c>
-      <c r="D169" s="113" t="inlineStr">
+      <c r="D169" s="112" t="inlineStr">
         <is>
           <t>agedebut_cigarettes_lt</t>
         </is>
@@ -18578,7 +18569,7 @@
           <t>AGEDEBUT_CIGARETTES_LT</t>
         </is>
       </c>
-      <c r="G169" s="113" t="inlineStr">
+      <c r="G169" s="112" t="inlineStr">
         <is>
           <t>AGEDEBUT_CIGARETTES_LT</t>
         </is>
@@ -18593,7 +18584,7 @@
           <t>Numérique (années)</t>
         </is>
       </c>
-      <c r="J169" s="113" t="n">
+      <c r="J169" s="112" t="n">
         <v>5</v>
       </c>
       <c r="K169" s="68" t="n">
@@ -18674,7 +18665,7 @@
           <t>agefin_cigarettes_lt</t>
         </is>
       </c>
-      <c r="D170" s="114" t="inlineStr">
+      <c r="D170" s="113" t="inlineStr">
         <is>
           <t>agefin_cigarettes_lt</t>
         </is>
@@ -18689,7 +18680,7 @@
           <t>AGEFIN_CIGARETTES_LT</t>
         </is>
       </c>
-      <c r="G170" s="114" t="inlineStr">
+      <c r="G170" s="113" t="inlineStr">
         <is>
           <t>AGEFIN_CIGARETTES_LT</t>
         </is>
@@ -18704,7 +18695,7 @@
           <t>Numérique (années) — NA si fumeur actuel ou jamais fumeur</t>
         </is>
       </c>
-      <c r="J170" s="114" t="n">
+      <c r="J170" s="113" t="n">
         <v>10</v>
       </c>
       <c r="K170" s="73" t="n">
@@ -18770,110 +18761,110 @@
       </c>
     </row>
     <row r="171" ht="21" customFormat="1" customHeight="1" s="27">
-      <c r="A171" s="121" t="inlineStr">
+      <c r="A171" s="120" t="inlineStr">
         <is>
           <t>NEUROPSYCHOLOGIE</t>
         </is>
       </c>
-      <c r="B171" s="121" t="inlineStr">
+      <c r="B171" s="120" t="inlineStr">
         <is>
           <t>cclin01_</t>
         </is>
       </c>
-      <c r="C171" s="121" t="inlineStr">
+      <c r="C171" s="120" t="inlineStr">
         <is>
           <t>cclin01_</t>
         </is>
       </c>
-      <c r="D171" s="122" t="inlineStr">
+      <c r="D171" s="121" t="inlineStr">
         <is>
           <t>cclin01</t>
         </is>
       </c>
-      <c r="E171" s="121" t="inlineStr">
+      <c r="E171" s="120" t="inlineStr">
         <is>
           <t>CCLIN01_</t>
         </is>
       </c>
-      <c r="F171" s="121" t="inlineStr">
+      <c r="F171" s="120" t="inlineStr">
         <is>
           <t>CCLIN01</t>
         </is>
       </c>
-      <c r="G171" s="122" t="inlineStr">
+      <c r="G171" s="121" t="inlineStr">
         <is>
           <t>CCLIN01</t>
         </is>
       </c>
-      <c r="H171" s="121" t="inlineStr">
+      <c r="H171" s="120" t="inlineStr">
         <is>
           <t>Âge du patient (au moment de l'évaluation cognitive)</t>
         </is>
       </c>
-      <c r="I171" s="121" t="inlineStr">
+      <c r="I171" s="120" t="inlineStr">
         <is>
           <t>Numérique (années)</t>
         </is>
       </c>
-      <c r="J171" s="122" t="n">
+      <c r="J171" s="121" t="n">
         <v>16</v>
       </c>
-      <c r="K171" s="121" t="n">
+      <c r="K171" s="120" t="n">
         <v>90</v>
       </c>
-      <c r="L171" s="121" t="inlineStr">
+      <c r="L171" s="120" t="inlineStr">
         <is>
           <t>COVARIATE (not a feature). Age at testing is the single largest determinant of neuropsychological performance, and raw timed scores (TMT) are strongly age-dependent. The cohorts differ markedly in age (DR median 52 vs BP 39 vs SZ 32), so age is retained to residualize the cognitive features and prevent cohort age imbalance from masquerading as a trans-diagnostic cognitive difference.</t>
         </is>
       </c>
-      <c r="M171" s="121" t="inlineStr">
+      <c r="M171" s="120" t="inlineStr">
         <is>
           <t>NUM, comparable all 3 cohorts</t>
         </is>
       </c>
-      <c r="N171" s="121" t="inlineStr">
+      <c r="N171" s="120" t="inlineStr">
         <is>
           <t>Use as covariate (TMT raw times not age-normed); not a feature. QC [16,90].</t>
         </is>
       </c>
-      <c r="O171" s="121" t="inlineStr">
+      <c r="O171" s="120" t="inlineStr">
         <is>
           <t>cclin01_</t>
         </is>
       </c>
-      <c r="P171" s="121" t="n"/>
-      <c r="Q171" s="121" t="inlineStr">
+      <c r="P171" s="120" t="n"/>
+      <c r="Q171" s="120" t="inlineStr">
         <is>
           <t>cclin01_</t>
         </is>
       </c>
-      <c r="R171" s="121" t="inlineStr">
+      <c r="R171" s="120" t="inlineStr">
         <is>
           <t>NUM</t>
         </is>
       </c>
-      <c r="S171" s="121" t="inlineStr">
+      <c r="S171" s="120" t="inlineStr">
         <is>
           <t>cclin01</t>
         </is>
       </c>
-      <c r="T171" s="121" t="n"/>
-      <c r="U171" s="121" t="inlineStr">
+      <c r="T171" s="120" t="n"/>
+      <c r="U171" s="120" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="V171" s="121" t="inlineStr">
+      <c r="V171" s="120" t="inlineStr">
         <is>
           <t>free text (NLP required)</t>
         </is>
       </c>
-      <c r="W171" s="124" t="inlineStr">
+      <c r="W171" s="123" t="inlineStr">
         <is>
           <t>READY — Comparable in 3 cohorts (Tier A); data present in 3 CSVs (DR neuropsych recovered 2026-05)</t>
         </is>
       </c>
-      <c r="X171" s="121" t="inlineStr">
+      <c r="X171" s="120" t="inlineStr">
         <is>
           <t>cclin01</t>
         </is>
@@ -18900,7 +18891,7 @@
           <t>cclin08_</t>
         </is>
       </c>
-      <c r="D172" s="103" t="inlineStr">
+      <c r="D172" s="102" t="inlineStr">
         <is>
           <t>cclin08</t>
         </is>
@@ -18915,7 +18906,7 @@
           <t>CCLIN08</t>
         </is>
       </c>
-      <c r="G172" s="103" t="inlineStr">
+      <c r="G172" s="102" t="inlineStr">
         <is>
           <t>CCLIN08</t>
         </is>
@@ -18930,7 +18921,7 @@
           <t>Numérique (années)</t>
         </is>
       </c>
-      <c r="J172" s="103" t="n">
+      <c r="J172" s="102" t="n">
         <v>0</v>
       </c>
       <c r="K172" s="15" t="n">
@@ -19016,7 +19007,7 @@
           <t>tmt0101_</t>
         </is>
       </c>
-      <c r="D173" s="103" t="inlineStr">
+      <c r="D173" s="102" t="inlineStr">
         <is>
           <t>tmta01</t>
         </is>
@@ -19031,7 +19022,7 @@
           <t>TMT0101</t>
         </is>
       </c>
-      <c r="G173" s="103" t="inlineStr">
+      <c r="G173" s="102" t="inlineStr">
         <is>
           <t>TMTA01</t>
         </is>
@@ -19046,7 +19037,7 @@
           <t>Numérique (s) ; codes diffèrent (SZ TMT0101 vs BP/DR TMTA01)</t>
         </is>
       </c>
-      <c r="J173" s="103" t="n">
+      <c r="J173" s="102" t="n">
         <v>5</v>
       </c>
       <c r="K173" s="15" t="n">
@@ -19131,7 +19122,7 @@
           <t>tmt0102_</t>
         </is>
       </c>
-      <c r="D174" s="103" t="inlineStr">
+      <c r="D174" s="102" t="inlineStr">
         <is>
           <t>tmtb01</t>
         </is>
@@ -19146,7 +19137,7 @@
           <t>TMT0102</t>
         </is>
       </c>
-      <c r="G174" s="103" t="inlineStr">
+      <c r="G174" s="102" t="inlineStr">
         <is>
           <t>TMTB01</t>
         </is>
@@ -19161,7 +19152,7 @@
           <t>Numérique (s)</t>
         </is>
       </c>
-      <c r="J174" s="103" t="n">
+      <c r="J174" s="102" t="n">
         <v>10</v>
       </c>
       <c r="K174" s="15" t="n">
@@ -19246,7 +19237,7 @@
           <t>tmtba01_</t>
         </is>
       </c>
-      <c r="D175" s="103" t="inlineStr">
+      <c r="D175" s="102" t="inlineStr">
         <is>
           <t>tmtba01</t>
         </is>
@@ -19261,7 +19252,7 @@
           <t>TMTBA01</t>
         </is>
       </c>
-      <c r="G175" s="103" t="inlineStr">
+      <c r="G175" s="102" t="inlineStr">
         <is>
           <t>TMTBA01</t>
         </is>
@@ -19276,7 +19267,7 @@
           <t>Numérique (s)</t>
         </is>
       </c>
-      <c r="J175" s="103" t="n">
+      <c r="J175" s="102" t="n">
         <v>-100</v>
       </c>
       <c r="K175" s="15" t="n">
@@ -19361,7 +19352,7 @@
           <t>similstd_w</t>
         </is>
       </c>
-      <c r="D176" s="103" t="inlineStr">
+      <c r="D176" s="102" t="inlineStr">
         <is>
           <t>similstd</t>
         </is>
@@ -19376,7 +19367,7 @@
           <t>WAIS4_SIMILSTD</t>
         </is>
       </c>
-      <c r="G176" s="103" t="inlineStr">
+      <c r="G176" s="102" t="inlineStr">
         <is>
           <t>SIMILSTD</t>
         </is>
@@ -19391,7 +19382,7 @@
           <t>Numérique (note standard)</t>
         </is>
       </c>
-      <c r="J176" s="103" t="n">
+      <c r="J176" s="102" t="n">
         <v>1</v>
       </c>
       <c r="K176" s="15" t="n">
@@ -19460,7 +19451,7 @@
         </is>
       </c>
     </row>
-    <row r="177" ht="21" customFormat="1" customHeight="1" s="123">
+    <row r="177" ht="21" customFormat="1" customHeight="1" s="122">
       <c r="A177" s="15" t="inlineStr">
         <is>
           <t>NEUROPSYCHOLOGIE</t>
@@ -19476,7 +19467,7 @@
           <t>mat_std_w</t>
         </is>
       </c>
-      <c r="D177" s="103" t="n"/>
+      <c r="D177" s="102" t="n"/>
       <c r="E177" s="15" t="inlineStr">
         <is>
           <t>MAT_STD_w</t>
@@ -19487,7 +19478,7 @@
           <t>WAIS4_MAT_STD</t>
         </is>
       </c>
-      <c r="G177" s="103" t="n"/>
+      <c r="G177" s="102" t="n"/>
       <c r="H177" s="15" t="inlineStr">
         <is>
           <t>WAIS-IV Matrices — Note standard</t>
@@ -19498,7 +19489,7 @@
           <t>Numérique (note standard)</t>
         </is>
       </c>
-      <c r="J177" s="103" t="n">
+      <c r="J177" s="102" t="n">
         <v>1</v>
       </c>
       <c r="K177" s="15" t="n">
@@ -19575,7 +19566,7 @@
           <t>nstand_w</t>
         </is>
       </c>
-      <c r="D178" s="103" t="inlineStr">
+      <c r="D178" s="102" t="inlineStr">
         <is>
           <t>nstand</t>
         </is>
@@ -19590,7 +19581,7 @@
           <t>WAIS4_NSTAND</t>
         </is>
       </c>
-      <c r="G178" s="103" t="inlineStr">
+      <c r="G178" s="102" t="inlineStr">
         <is>
           <t>NSTAND</t>
         </is>
@@ -19605,7 +19596,7 @@
           <t>Numérique (note standard)</t>
         </is>
       </c>
-      <c r="J178" s="103" t="n">
+      <c r="J178" s="102" t="n">
         <v>1</v>
       </c>
       <c r="K178" s="15" t="n">
@@ -19682,7 +19673,7 @@
           <t>arithstd_w</t>
         </is>
       </c>
-      <c r="D179" s="103" t="inlineStr">
+      <c r="D179" s="102" t="inlineStr">
         <is>
           <t>arithstd</t>
         </is>
@@ -19693,7 +19684,7 @@
           <t>WAIS4_ARITHSTD</t>
         </is>
       </c>
-      <c r="G179" s="103" t="inlineStr">
+      <c r="G179" s="102" t="inlineStr">
         <is>
           <t>ARITHSTD</t>
         </is>
@@ -19708,7 +19699,7 @@
           <t>Numérique ; SZ+DR seulement</t>
         </is>
       </c>
-      <c r="J179" s="103" t="n">
+      <c r="J179" s="102" t="n">
         <v>1</v>
       </c>
       <c r="K179" s="15" t="n">
@@ -19785,7 +19776,7 @@
           <t>sdmt0101_w</t>
         </is>
       </c>
-      <c r="D180" s="103" t="inlineStr">
+      <c r="D180" s="102" t="inlineStr">
         <is>
           <t>code04</t>
         </is>
@@ -19800,7 +19791,7 @@
           <t>WAIS4_SDMT0101</t>
         </is>
       </c>
-      <c r="G180" s="103" t="inlineStr">
+      <c r="G180" s="102" t="inlineStr">
         <is>
           <t>CODE04</t>
         </is>
@@ -19815,7 +19806,7 @@
           <t>Numérique (note standard)</t>
         </is>
       </c>
-      <c r="J180" s="103" t="n">
+      <c r="J180" s="102" t="n">
         <v>1</v>
       </c>
       <c r="K180" s="15" t="n">
@@ -19892,7 +19883,7 @@
         </is>
       </c>
       <c r="C181" s="15" t="n"/>
-      <c r="D181" s="103" t="inlineStr">
+      <c r="D181" s="102" t="inlineStr">
         <is>
           <t>symbol04</t>
         </is>
@@ -19903,7 +19894,7 @@
         </is>
       </c>
       <c r="F181" s="15" t="n"/>
-      <c r="G181" s="103" t="inlineStr">
+      <c r="G181" s="102" t="inlineStr">
         <is>
           <t>SYMBOL04</t>
         </is>
@@ -19918,7 +19909,7 @@
           <t>Numérique (note standard) ; BP+DR seulement</t>
         </is>
       </c>
-      <c r="J181" s="103" t="n">
+      <c r="J181" s="102" t="n">
         <v>1</v>
       </c>
       <c r="K181" s="15" t="n">
@@ -19995,7 +19986,7 @@
           <t>agetrt</t>
         </is>
       </c>
-      <c r="D182" s="115" t="inlineStr">
+      <c r="D182" s="114" t="inlineStr">
         <is>
           <t>agetrt</t>
         </is>
@@ -20010,7 +20001,7 @@
           <t>AGETRT</t>
         </is>
       </c>
-      <c r="G182" s="115" t="inlineStr">
+      <c r="G182" s="114" t="inlineStr">
         <is>
           <t>AGETRT</t>
         </is>
@@ -20025,7 +20016,7 @@
           <t>Numérique (années) ; BP=psychotrope, SZ=antipsychotique, DR=psychotrope (libellés diffèrent)</t>
         </is>
       </c>
-      <c r="J182" s="115" t="n">
+      <c r="J182" s="114" t="n">
         <v>5</v>
       </c>
       <c r="K182" s="77" t="n">
@@ -20106,7 +20097,7 @@
           <t>agepisod</t>
         </is>
       </c>
-      <c r="D183" s="115" t="inlineStr">
+      <c r="D183" s="114" t="inlineStr">
         <is>
           <t>agedebutpremier_episode</t>
         </is>
@@ -20121,7 +20112,7 @@
           <t>AGEPISOD</t>
         </is>
       </c>
-      <c r="G183" s="115" t="inlineStr">
+      <c r="G183" s="114" t="inlineStr">
         <is>
           <t>AGEDEBUTPremier_episode</t>
         </is>
@@ -20136,7 +20127,7 @@
           <t>Numérique (années) ; BP/DR=premier épisode thymique (EDM/manie/hypomanie/mixte), SZ=premier épisode psychotique caractérisé</t>
         </is>
       </c>
-      <c r="J183" s="115" t="n">
+      <c r="J183" s="114" t="n">
         <v>5</v>
       </c>
       <c r="K183" s="77" t="n">
@@ -20221,7 +20212,7 @@
           <t>migraine_mhoccur</t>
         </is>
       </c>
-      <c r="D184" s="100" t="inlineStr">
+      <c r="D184" s="99" t="inlineStr">
         <is>
           <t>migraine_mhoccur</t>
         </is>
@@ -20236,7 +20227,7 @@
           <t>migraine_MHOCCUR</t>
         </is>
       </c>
-      <c r="G184" s="100" t="inlineStr">
+      <c r="G184" s="99" t="inlineStr">
         <is>
           <t>migraine_MHOCCUR</t>
         </is>
@@ -20251,7 +20242,7 @@
           <t>Y/N/U (BP/SZ) ; codages similaires en DR</t>
         </is>
       </c>
-      <c r="J184" s="100" t="n">
+      <c r="J184" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K184" s="2" t="n">
@@ -20332,7 +20323,7 @@
           <t>sep_mhoccur</t>
         </is>
       </c>
-      <c r="D185" s="100" t="inlineStr">
+      <c r="D185" s="99" t="inlineStr">
         <is>
           <t>sep_mhoccur</t>
         </is>
@@ -20347,7 +20338,7 @@
           <t>sep_MHOCCUR</t>
         </is>
       </c>
-      <c r="G185" s="100" t="inlineStr">
+      <c r="G185" s="99" t="inlineStr">
         <is>
           <t>sep_MHOCCUR</t>
         </is>
@@ -20362,7 +20353,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J185" s="100" t="n">
+      <c r="J185" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K185" s="2" t="n">
@@ -20443,7 +20434,7 @@
           <t>epilepsie_mhoccur</t>
         </is>
       </c>
-      <c r="D186" s="100" t="inlineStr">
+      <c r="D186" s="99" t="inlineStr">
         <is>
           <t>epilepsie_mhoccur</t>
         </is>
@@ -20458,7 +20449,7 @@
           <t>epilepsie_MHOCCUR</t>
         </is>
       </c>
-      <c r="G186" s="100" t="inlineStr">
+      <c r="G186" s="99" t="inlineStr">
         <is>
           <t>epilepsie_MHOCCUR</t>
         </is>
@@ -20473,7 +20464,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J186" s="100" t="n">
+      <c r="J186" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K186" s="2" t="n">
@@ -20554,7 +20545,7 @@
           <t>traumacra_mhoccur</t>
         </is>
       </c>
-      <c r="D187" s="100" t="inlineStr">
+      <c r="D187" s="99" t="inlineStr">
         <is>
           <t>traumacra_mhoccur</t>
         </is>
@@ -20569,7 +20560,7 @@
           <t>traumacra_MHOCCUR</t>
         </is>
       </c>
-      <c r="G187" s="100" t="inlineStr">
+      <c r="G187" s="99" t="inlineStr">
         <is>
           <t>traumacra_MHOCCUR</t>
         </is>
@@ -20584,7 +20575,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J187" s="100" t="n">
+      <c r="J187" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K187" s="2" t="n">
@@ -20661,7 +20652,7 @@
           <t>avc_mhoccur</t>
         </is>
       </c>
-      <c r="D188" s="100" t="inlineStr">
+      <c r="D188" s="99" t="inlineStr">
         <is>
           <t>avc_mhoccur</t>
         </is>
@@ -20676,7 +20667,7 @@
           <t>avc_MHOCCUR</t>
         </is>
       </c>
-      <c r="G188" s="100" t="inlineStr">
+      <c r="G188" s="99" t="inlineStr">
         <is>
           <t>avc_MHOCCUR</t>
         </is>
@@ -20691,7 +20682,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J188" s="100" t="n">
+      <c r="J188" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K188" s="2" t="n">
@@ -20772,7 +20763,7 @@
           <t>autneuro_mhoccur</t>
         </is>
       </c>
-      <c r="D189" s="100" t="inlineStr">
+      <c r="D189" s="99" t="inlineStr">
         <is>
           <t>autneuro_mhoccur</t>
         </is>
@@ -20787,7 +20778,7 @@
           <t>autneuro_MHOCCUR</t>
         </is>
       </c>
-      <c r="G189" s="100" t="inlineStr">
+      <c r="G189" s="99" t="inlineStr">
         <is>
           <t>autneuro_MHOCCUR</t>
         </is>
@@ -20802,7 +20793,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J189" s="100" t="n">
+      <c r="J189" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K189" s="2" t="n">
@@ -20883,7 +20874,7 @@
           <t>hta_mhoccur</t>
         </is>
       </c>
-      <c r="D190" s="100" t="inlineStr">
+      <c r="D190" s="99" t="inlineStr">
         <is>
           <t>hta_mhoccur</t>
         </is>
@@ -20898,7 +20889,7 @@
           <t>hta_MHOCCUR</t>
         </is>
       </c>
-      <c r="G190" s="100" t="inlineStr">
+      <c r="G190" s="99" t="inlineStr">
         <is>
           <t>hta_MHOCCUR</t>
         </is>
@@ -20913,7 +20904,7 @@
           <t>Y/N/U ; libellé DR='HTA'</t>
         </is>
       </c>
-      <c r="J190" s="100" t="n">
+      <c r="J190" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K190" s="2" t="n">
@@ -20994,7 +20985,7 @@
           <t>coronar_mhoccur</t>
         </is>
       </c>
-      <c r="D191" s="100" t="inlineStr">
+      <c r="D191" s="99" t="inlineStr">
         <is>
           <t>coronar_mhoccur</t>
         </is>
@@ -21009,7 +21000,7 @@
           <t>coronar_MHOCCUR</t>
         </is>
       </c>
-      <c r="G191" s="100" t="inlineStr">
+      <c r="G191" s="99" t="inlineStr">
         <is>
           <t>coronar_MHOCCUR</t>
         </is>
@@ -21024,7 +21015,7 @@
           <t>Y/N/U ; DR précise 'hors IDM' dans le libellé</t>
         </is>
       </c>
-      <c r="J191" s="100" t="n">
+      <c r="J191" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K191" s="2" t="n">
@@ -21105,7 +21096,7 @@
           <t>infarctus_mhoccur</t>
         </is>
       </c>
-      <c r="D192" s="100" t="inlineStr">
+      <c r="D192" s="99" t="inlineStr">
         <is>
           <t>infarctus_mhoccur</t>
         </is>
@@ -21120,7 +21111,7 @@
           <t>infarctus_MHOCCUR</t>
         </is>
       </c>
-      <c r="G192" s="100" t="inlineStr">
+      <c r="G192" s="99" t="inlineStr">
         <is>
           <t>infarctus_MHOCCUR</t>
         </is>
@@ -21135,7 +21126,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J192" s="100" t="n">
+      <c r="J192" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K192" s="2" t="n">
@@ -21216,7 +21207,7 @@
           <t>trbrycard_mhoccur</t>
         </is>
       </c>
-      <c r="D193" s="100" t="inlineStr">
+      <c r="D193" s="99" t="inlineStr">
         <is>
           <t>trbrycard_mhoccur</t>
         </is>
@@ -21231,7 +21222,7 @@
           <t>trbrycard_MHOCCUR</t>
         </is>
       </c>
-      <c r="G193" s="100" t="inlineStr">
+      <c r="G193" s="99" t="inlineStr">
         <is>
           <t>trbrycard_MHOCCUR</t>
         </is>
@@ -21246,7 +21237,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J193" s="100" t="n">
+      <c r="J193" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K193" s="2" t="n">
@@ -21327,7 +21318,7 @@
           <t>autcardv_mhoccur</t>
         </is>
       </c>
-      <c r="D194" s="100" t="inlineStr">
+      <c r="D194" s="99" t="inlineStr">
         <is>
           <t>autcardv_mhoccur</t>
         </is>
@@ -21342,7 +21333,7 @@
           <t>autcardv_MHOCCUR</t>
         </is>
       </c>
-      <c r="G194" s="100" t="inlineStr">
+      <c r="G194" s="99" t="inlineStr">
         <is>
           <t>autcardv_MHOCCUR</t>
         </is>
@@ -21357,7 +21348,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J194" s="100" t="n">
+      <c r="J194" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K194" s="2" t="n">
@@ -21438,7 +21429,7 @@
           <t>autendoc_mhoccur</t>
         </is>
       </c>
-      <c r="D195" s="100" t="inlineStr">
+      <c r="D195" s="99" t="inlineStr">
         <is>
           <t>autendoc_mhoccur</t>
         </is>
@@ -21453,7 +21444,7 @@
           <t>autendoc_MHOCCUR</t>
         </is>
       </c>
-      <c r="G195" s="100" t="inlineStr">
+      <c r="G195" s="99" t="inlineStr">
         <is>
           <t>autendoc_MHOCCUR</t>
         </is>
@@ -21468,7 +21459,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J195" s="100" t="n">
+      <c r="J195" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K195" s="2" t="n">
@@ -21549,7 +21540,7 @@
           <t>acne_mhoccur</t>
         </is>
       </c>
-      <c r="D196" s="100" t="inlineStr">
+      <c r="D196" s="99" t="inlineStr">
         <is>
           <t>acne_mhoccur</t>
         </is>
@@ -21564,7 +21555,7 @@
           <t>acne_MHOCCUR</t>
         </is>
       </c>
-      <c r="G196" s="100" t="inlineStr">
+      <c r="G196" s="99" t="inlineStr">
         <is>
           <t>acne_MHOCCUR</t>
         </is>
@@ -21579,7 +21570,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J196" s="100" t="n">
+      <c r="J196" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K196" s="2" t="n">
@@ -21660,7 +21651,7 @@
           <t>eczema_mhoccur</t>
         </is>
       </c>
-      <c r="D197" s="100" t="inlineStr">
+      <c r="D197" s="99" t="inlineStr">
         <is>
           <t>eczema_mhoccur</t>
         </is>
@@ -21675,7 +21666,7 @@
           <t>eczema_MHOCCUR</t>
         </is>
       </c>
-      <c r="G197" s="100" t="inlineStr">
+      <c r="G197" s="99" t="inlineStr">
         <is>
           <t>eczema_MHOCCUR</t>
         </is>
@@ -21690,7 +21681,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J197" s="100" t="n">
+      <c r="J197" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K197" s="2" t="n">
@@ -21771,7 +21762,7 @@
           <t>toxidermi_mhoccur</t>
         </is>
       </c>
-      <c r="D198" s="100" t="inlineStr">
+      <c r="D198" s="99" t="inlineStr">
         <is>
           <t>toxidermi_mhoccur</t>
         </is>
@@ -21786,7 +21777,7 @@
           <t>toxidermi_MHOCCUR</t>
         </is>
       </c>
-      <c r="G198" s="100" t="inlineStr">
+      <c r="G198" s="99" t="inlineStr">
         <is>
           <t>toxidermi_MHOCCUR</t>
         </is>
@@ -21801,7 +21792,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J198" s="100" t="n">
+      <c r="J198" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K198" s="2" t="n">
@@ -21882,7 +21873,7 @@
           <t>cheveux_mhoccur</t>
         </is>
       </c>
-      <c r="D199" s="100" t="inlineStr">
+      <c r="D199" s="99" t="inlineStr">
         <is>
           <t>cheveux_mhoccur</t>
         </is>
@@ -21897,7 +21888,7 @@
           <t>cheveux_MHOCCUR</t>
         </is>
       </c>
-      <c r="G199" s="100" t="inlineStr">
+      <c r="G199" s="99" t="inlineStr">
         <is>
           <t>cheveux_MHOCCUR</t>
         </is>
@@ -21912,7 +21903,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J199" s="100" t="n">
+      <c r="J199" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K199" s="2" t="n">
@@ -21993,7 +21984,7 @@
           <t>psoriasis_mhoccur</t>
         </is>
       </c>
-      <c r="D200" s="100" t="inlineStr">
+      <c r="D200" s="99" t="inlineStr">
         <is>
           <t>psoriasis_mhoccur</t>
         </is>
@@ -22008,7 +21999,7 @@
           <t>psoriasis_MHOCCUR</t>
         </is>
       </c>
-      <c r="G200" s="100" t="inlineStr">
+      <c r="G200" s="99" t="inlineStr">
         <is>
           <t>psoriasis_MHOCCUR</t>
         </is>
@@ -22023,7 +22014,7 @@
           <t>Y/N/U ; SZ classe psoriasis dans pathologies auto-immunes</t>
         </is>
       </c>
-      <c r="J200" s="100" t="n">
+      <c r="J200" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K200" s="2" t="n">
@@ -22104,7 +22095,7 @@
           <t>somat_all</t>
         </is>
       </c>
-      <c r="D201" s="100" t="inlineStr">
+      <c r="D201" s="99" t="inlineStr">
         <is>
           <t>somat_all</t>
         </is>
@@ -22119,7 +22110,7 @@
           <t>somat_all</t>
         </is>
       </c>
-      <c r="G201" s="100" t="inlineStr">
+      <c r="G201" s="99" t="inlineStr">
         <is>
           <t>somat_all</t>
         </is>
@@ -22134,7 +22125,7 @@
           <t>Y/N (drapeau)</t>
         </is>
       </c>
-      <c r="J201" s="100" t="n">
+      <c r="J201" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K201" s="2" t="n">
@@ -22211,7 +22202,7 @@
           <t>inflachro_mhoccur</t>
         </is>
       </c>
-      <c r="D202" s="100" t="inlineStr">
+      <c r="D202" s="99" t="inlineStr">
         <is>
           <t>inflachro_mhoccur</t>
         </is>
@@ -22226,7 +22217,7 @@
           <t>inflachro_MHOCCUR</t>
         </is>
       </c>
-      <c r="G202" s="100" t="inlineStr">
+      <c r="G202" s="99" t="inlineStr">
         <is>
           <t>inflachro_MHOCCUR</t>
         </is>
@@ -22241,7 +22232,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J202" s="100" t="n">
+      <c r="J202" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K202" s="2" t="n">
@@ -22322,7 +22313,7 @@
           <t>cirrhose_mhoccur</t>
         </is>
       </c>
-      <c r="D203" s="100" t="inlineStr">
+      <c r="D203" s="99" t="inlineStr">
         <is>
           <t>cirrhose_mhoccur</t>
         </is>
@@ -22337,7 +22328,7 @@
           <t>cirrhose_MHOCCUR</t>
         </is>
       </c>
-      <c r="G203" s="100" t="inlineStr">
+      <c r="G203" s="99" t="inlineStr">
         <is>
           <t>cirrhose_MHOCCUR</t>
         </is>
@@ -22352,7 +22343,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J203" s="100" t="n">
+      <c r="J203" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K203" s="2" t="n">
@@ -22433,7 +22424,7 @@
           <t>ulcgasduo_mhoccur</t>
         </is>
       </c>
-      <c r="D204" s="100" t="inlineStr">
+      <c r="D204" s="99" t="inlineStr">
         <is>
           <t>ulcgasduo_mhoccur</t>
         </is>
@@ -22448,7 +22439,7 @@
           <t>ulcgasduo_MHOCCUR</t>
         </is>
       </c>
-      <c r="G204" s="100" t="inlineStr">
+      <c r="G204" s="99" t="inlineStr">
         <is>
           <t>ulcgasduo_MHOCCUR</t>
         </is>
@@ -22463,7 +22454,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J204" s="100" t="n">
+      <c r="J204" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K204" s="2" t="n">
@@ -22544,7 +22535,7 @@
           <t>hepmedic_mhoccur</t>
         </is>
       </c>
-      <c r="D205" s="100" t="inlineStr">
+      <c r="D205" s="99" t="inlineStr">
         <is>
           <t>hepmedic_mhoccur</t>
         </is>
@@ -22559,7 +22550,7 @@
           <t>hepmedic_MHOCCUR</t>
         </is>
       </c>
-      <c r="G205" s="100" t="inlineStr">
+      <c r="G205" s="99" t="inlineStr">
         <is>
           <t>hepmedic_MHOCCUR</t>
         </is>
@@ -22574,7 +22565,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J205" s="100" t="n">
+      <c r="J205" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K205" s="2" t="n">
@@ -22655,7 +22646,7 @@
           <t>vih_mhoccur</t>
         </is>
       </c>
-      <c r="D206" s="100" t="inlineStr">
+      <c r="D206" s="99" t="inlineStr">
         <is>
           <t>vih_mhoccur</t>
         </is>
@@ -22670,7 +22661,7 @@
           <t>vih_MHOCCUR</t>
         </is>
       </c>
-      <c r="G206" s="100" t="inlineStr">
+      <c r="G206" s="99" t="inlineStr">
         <is>
           <t>vih_MHOCCUR</t>
         </is>
@@ -22685,7 +22676,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J206" s="100" t="n">
+      <c r="J206" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K206" s="2" t="n">
@@ -22766,7 +22757,7 @@
           <t>hvc_mhoccur</t>
         </is>
       </c>
-      <c r="D207" s="100" t="inlineStr">
+      <c r="D207" s="99" t="inlineStr">
         <is>
           <t>hvc_mhoccur</t>
         </is>
@@ -22781,7 +22772,7 @@
           <t>hvc_MHOCCUR</t>
         </is>
       </c>
-      <c r="G207" s="100" t="inlineStr">
+      <c r="G207" s="99" t="inlineStr">
         <is>
           <t>hvc_MHOCCUR</t>
         </is>
@@ -22796,7 +22787,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J207" s="100" t="n">
+      <c r="J207" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K207" s="2" t="n">
@@ -22877,7 +22868,7 @@
           <t>genetique_mhoccur</t>
         </is>
       </c>
-      <c r="D208" s="100" t="inlineStr">
+      <c r="D208" s="99" t="inlineStr">
         <is>
           <t>genetique_mhoccur</t>
         </is>
@@ -22892,7 +22883,7 @@
           <t>genetique_MHOCCUR</t>
         </is>
       </c>
-      <c r="G208" s="100" t="inlineStr">
+      <c r="G208" s="99" t="inlineStr">
         <is>
           <t>genetique_MHOCCUR</t>
         </is>
@@ -22907,7 +22898,7 @@
           <t>Y/N/U</t>
         </is>
       </c>
-      <c r="J208" s="100" t="n">
+      <c r="J208" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K208" s="2" t="n">
@@ -22988,7 +22979,7 @@
           <t>pregnn_rporres</t>
         </is>
       </c>
-      <c r="D209" s="100" t="inlineStr">
+      <c r="D209" s="99" t="inlineStr">
         <is>
           <t>pregnn_rporres</t>
         </is>
@@ -23003,7 +22994,7 @@
           <t>PREGNN_RPORRES</t>
         </is>
       </c>
-      <c r="G209" s="100" t="inlineStr">
+      <c r="G209" s="99" t="inlineStr">
         <is>
           <t>PREGNN_RPORRES</t>
         </is>
@@ -23018,7 +23009,7 @@
           <t>Numérique</t>
         </is>
       </c>
-      <c r="J209" s="100" t="n">
+      <c r="J209" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K209" s="2" t="n">
@@ -23095,7 +23086,7 @@
           <t>menostat_rporres</t>
         </is>
       </c>
-      <c r="D210" s="100" t="inlineStr">
+      <c r="D210" s="99" t="inlineStr">
         <is>
           <t>menostat_rporres</t>
         </is>
@@ -23110,7 +23101,7 @@
           <t>MENOSTAT_RPORRES</t>
         </is>
       </c>
-      <c r="G210" s="100" t="inlineStr">
+      <c r="G210" s="99" t="inlineStr">
         <is>
           <t>MENOSTAT_RPORRES</t>
         </is>
@@ -23125,7 +23116,7 @@
           <t>Y/N (ménopausée oui/non)</t>
         </is>
       </c>
-      <c r="J210" s="100" t="n">
+      <c r="J210" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K210" s="2" t="n">
@@ -23206,7 +23197,7 @@
           <t>hormonal_rporres</t>
         </is>
       </c>
-      <c r="D211" s="100" t="inlineStr">
+      <c r="D211" s="99" t="inlineStr">
         <is>
           <t>hormonal_rporres</t>
         </is>
@@ -23221,7 +23212,7 @@
           <t>HORMONAL_RPORRES</t>
         </is>
       </c>
-      <c r="G211" s="100" t="inlineStr">
+      <c r="G211" s="99" t="inlineStr">
         <is>
           <t>HORMONAL_RPORRES</t>
         </is>
@@ -23236,7 +23227,7 @@
           <t>Y/N</t>
         </is>
       </c>
-      <c r="J211" s="100" t="n">
+      <c r="J211" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K211" s="2" t="n">
@@ -23317,7 +23308,7 @@
           <t>mere_structure</t>
         </is>
       </c>
-      <c r="D212" s="100" t="inlineStr">
+      <c r="D212" s="99" t="inlineStr">
         <is>
           <t>mere_structure</t>
         </is>
@@ -23332,7 +23323,7 @@
           <t>mere_structure</t>
         </is>
       </c>
-      <c r="G212" s="100" t="inlineStr">
+      <c r="G212" s="99" t="inlineStr">
         <is>
           <t>mere_structure</t>
         </is>
@@ -23347,7 +23338,7 @@
           <t>Y/N/U (BP/SZ) ; 0=Non/1=Oui/2=NSP (DR) — la mère présente-t-elle un trouble psychiatrique</t>
         </is>
       </c>
-      <c r="J212" s="100" t="n">
+      <c r="J212" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K212" s="2" t="n">
@@ -23432,7 +23423,7 @@
           <t>mere_suicide</t>
         </is>
       </c>
-      <c r="D213" s="100" t="inlineStr">
+      <c r="D213" s="99" t="inlineStr">
         <is>
           <t>mere_suicide</t>
         </is>
@@ -23447,7 +23438,7 @@
           <t>mere_suicide</t>
         </is>
       </c>
-      <c r="G213" s="100" t="inlineStr">
+      <c r="G213" s="99" t="inlineStr">
         <is>
           <t>mere_suicide</t>
         </is>
@@ -23462,7 +23453,7 @@
           <t>Aucun/Tentative de suicide/Suicide abouti/NSP (BP/SZ) ; 0/1/2/3 (DR)</t>
         </is>
       </c>
-      <c r="J213" s="100" t="n">
+      <c r="J213" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K213" s="2" t="n">
@@ -23551,7 +23542,7 @@
           <t>pere_structure</t>
         </is>
       </c>
-      <c r="D214" s="100" t="inlineStr">
+      <c r="D214" s="99" t="inlineStr">
         <is>
           <t>pere_structure</t>
         </is>
@@ -23566,7 +23557,7 @@
           <t>pere_structure</t>
         </is>
       </c>
-      <c r="G214" s="100" t="inlineStr">
+      <c r="G214" s="99" t="inlineStr">
         <is>
           <t>pere_structure</t>
         </is>
@@ -23581,7 +23572,7 @@
           <t>Y/N/U (BP/SZ) ; 0=Non/1=Oui/2=NSP (DR) — le père présente-t-il un trouble psychiatrique</t>
         </is>
       </c>
-      <c r="J214" s="100" t="n">
+      <c r="J214" s="99" t="n">
         <v>0</v>
       </c>
       <c r="K214" s="2" t="n">
@@ -23666,7 +23657,7 @@
           <t>pere_suicide</t>
         </is>
       </c>
-      <c r="D215" s="102" t="inlineStr">
+      <c r="D215" s="101" t="inlineStr">
         <is>
           <t>pere_suicide</t>
         </is>
@@ -23681,7 +23672,7 @@
           <t>pere_suicide</t>
         </is>
       </c>
-      <c r="G215" s="102" t="inlineStr">
+      <c r="G215" s="101" t="inlineStr">
         <is>
           <t>pere_suicide</t>
         </is>
@@ -23696,7 +23687,7 @@
           <t>Aucun/Tentative de suicide/Suicide abouti/NSP (BP/SZ) ; 0/1/2/3 (DR)</t>
         </is>
       </c>
-      <c r="J215" s="102" t="n">
+      <c r="J215" s="101" t="n">
         <v>0</v>
       </c>
       <c r="K215" s="7" t="n">
@@ -23777,7 +23768,7 @@
           <t>agedebut_hospitalisation_first</t>
         </is>
       </c>
-      <c r="D216" s="116" t="inlineStr">
+      <c r="D216" s="115" t="inlineStr">
         <is>
           <t>agedebut_hospitalisation_lt</t>
         </is>
@@ -23792,7 +23783,7 @@
           <t>AGEDEBUT_hospitalisation_FIRST</t>
         </is>
       </c>
-      <c r="G216" s="116" t="inlineStr">
+      <c r="G216" s="115" t="inlineStr">
         <is>
           <t>AGEDEBUT_hospitalisation_LT</t>
         </is>
@@ -23807,7 +23798,7 @@
           <t>Numérique (années) ; codes diffèrent : BP=non-suffixé, SZ=`_FIRST` (libellé : 'pour trouble psychotique'), DR=`_LT`</t>
         </is>
       </c>
-      <c r="J216" s="116" t="n">
+      <c r="J216" s="115" t="n">
         <v>5</v>
       </c>
       <c r="K216" s="82" t="n">
@@ -23888,7 +23879,7 @@
           <t>nboccur_hospitalisation_lt</t>
         </is>
       </c>
-      <c r="D217" s="116" t="inlineStr">
+      <c r="D217" s="115" t="inlineStr">
         <is>
           <t>nboccur_hospitalisation_lt</t>
         </is>
@@ -23903,7 +23894,7 @@
           <t>NBOCCUR_hospitalisation_LT</t>
         </is>
       </c>
-      <c r="G217" s="116" t="inlineStr">
+      <c r="G217" s="115" t="inlineStr">
         <is>
           <t>NBOCCUR_hospitalisation_LT</t>
         </is>
@@ -23918,7 +23909,7 @@
           <t>Numérique ; BP non-suffixé, SZ+DR ont le suffixe `_LT`</t>
         </is>
       </c>
-      <c r="J217" s="116" t="n">
+      <c r="J217" s="115" t="n">
         <v>0</v>
       </c>
       <c r="K217" s="82" t="n">
@@ -23999,7 +23990,7 @@
           <t>hodur_hospitalisation_lt</t>
         </is>
       </c>
-      <c r="D218" s="116" t="inlineStr">
+      <c r="D218" s="115" t="inlineStr">
         <is>
           <t>hodur_hospitalisation_lt</t>
         </is>
@@ -24014,7 +24005,7 @@
           <t>HODUR_hospitalisation_LT</t>
         </is>
       </c>
-      <c r="G218" s="116" t="inlineStr">
+      <c r="G218" s="115" t="inlineStr">
         <is>
           <t>HODUR_hospitalisation_LT</t>
         </is>
@@ -24029,7 +24020,7 @@
           <t>Numérique (mois) ; BP non-suffixé, SZ+DR ont le suffixe `_LT`</t>
         </is>
       </c>
-      <c r="J218" s="116" t="n">
+      <c r="J218" s="115" t="n">
         <v>0</v>
       </c>
       <c r="K218" s="82" t="n">
@@ -24110,7 +24101,7 @@
           <t>hooccur_arret_travail_actuel</t>
         </is>
       </c>
-      <c r="D219" s="116" t="inlineStr">
+      <c r="D219" s="115" t="inlineStr">
         <is>
           <t>hooccur_arret_travail_actuel</t>
         </is>
@@ -24125,7 +24116,7 @@
           <t>HOOCCUR_arret_travail_actuel</t>
         </is>
       </c>
-      <c r="G219" s="116" t="inlineStr">
+      <c r="G219" s="115" t="inlineStr">
         <is>
           <t>HOOCCUR_arret_travail_actuel</t>
         </is>
@@ -24140,7 +24131,7 @@
           <t>Y/N (BP/SZ) ; Y/N/NA (DR) — verbatim Tier A</t>
         </is>
       </c>
-      <c r="J219" s="116" t="n">
+      <c r="J219" s="115" t="n">
         <v>0</v>
       </c>
       <c r="K219" s="82" t="n">
@@ -24229,7 +24220,7 @@
         </is>
       </c>
       <c r="C220" s="88" t="n"/>
-      <c r="D220" s="117" t="inlineStr">
+      <c r="D220" s="116" t="inlineStr">
         <is>
           <t>hodur_arret_travail_actuel</t>
         </is>
@@ -24240,7 +24231,7 @@
         </is>
       </c>
       <c r="F220" s="88" t="n"/>
-      <c r="G220" s="117" t="inlineStr">
+      <c r="G220" s="116" t="inlineStr">
         <is>
           <t>HODUR_arret_travail_actuel</t>
         </is>
@@ -24255,7 +24246,7 @@
           <t>Y/N (BP) ; Y/N (DR libellé '&gt;Longue durée?') ; BP+DR seulement</t>
         </is>
       </c>
-      <c r="J220" s="117" t="n">
+      <c r="J220" s="116" t="n">
         <v>0</v>
       </c>
       <c r="K220" s="88" t="n">
@@ -24332,7 +24323,7 @@
           <t>edulevel</t>
         </is>
       </c>
-      <c r="D221" s="118" t="inlineStr">
+      <c r="D221" s="117" t="inlineStr">
         <is>
           <t>edulevel</t>
         </is>
@@ -24347,7 +24338,7 @@
           <t>EDULEVEL</t>
         </is>
       </c>
-      <c r="G221" s="118" t="inlineStr">
+      <c r="G221" s="117" t="inlineStr">
         <is>
           <t>EDULEVEL</t>
         </is>
@@ -24362,7 +24353,7 @@
           <t>BP+DR : codage uniforme (CP-CM2=1-5, collège=6-9, lycée=10-12, CAP=13, BEP=14, BAC+1 à BAC+5=15-19, Doctorat=20) ; SZ : TEXTE libre</t>
         </is>
       </c>
-      <c r="J221" s="118" t="n">
+      <c r="J221" s="117" t="n">
         <v>1</v>
       </c>
       <c r="K221" s="91" t="n">
@@ -24455,7 +24446,7 @@
           <t>stprof</t>
         </is>
       </c>
-      <c r="D222" s="118" t="inlineStr">
+      <c r="D222" s="117" t="inlineStr">
         <is>
           <t>stprof</t>
         </is>
@@ -24470,7 +24461,7 @@
           <t>STPROF</t>
         </is>
       </c>
-      <c r="G222" s="118" t="inlineStr">
+      <c r="G222" s="117" t="inlineStr">
         <is>
           <t>STPROF</t>
         </is>
@@ -24485,7 +24476,7 @@
           <t>Catégoriel ; BP+DR : 0=sans emploi, 1=actif, 2=retraité, 3=étudiant, 4=pension, 5=au foyer, 6=autres ; SZ : même grille mais 3=étudiant/lycéen, 7=au foyer (réordonné)</t>
         </is>
       </c>
-      <c r="J222" s="118" t="n">
+      <c r="J222" s="117" t="n">
         <v>0</v>
       </c>
       <c r="K222" s="91" t="n">
@@ -24578,7 +24569,7 @@
           <t>jobclas</t>
         </is>
       </c>
-      <c r="D223" s="118" t="inlineStr">
+      <c r="D223" s="117" t="inlineStr">
         <is>
           <t>jobclas</t>
         </is>
@@ -24593,7 +24584,7 @@
           <t>JOBCLAS</t>
         </is>
       </c>
-      <c r="G223" s="118" t="inlineStr">
+      <c r="G223" s="117" t="inlineStr">
         <is>
           <t>JOBCLAS</t>
         </is>
@@ -24608,7 +24599,7 @@
           <t>Oui/Non (BP/SZ) ; 0/1 (DR) — emploi à temps plein</t>
         </is>
       </c>
-      <c r="J223" s="118" t="n">
+      <c r="J223" s="117" t="n">
         <v>0</v>
       </c>
       <c r="K223" s="91" t="n">
@@ -24674,118 +24665,118 @@
       </c>
     </row>
     <row r="224" ht="21" customFormat="1" customHeight="1" s="17">
-      <c r="A224" s="96" t="inlineStr">
+      <c r="A224" s="95" t="inlineStr">
         <is>
           <t>SOCIAL</t>
         </is>
       </c>
-      <c r="B224" s="97" t="inlineStr">
+      <c r="B224" s="96" t="inlineStr">
         <is>
           <t>lvsbjind</t>
         </is>
       </c>
-      <c r="C224" s="97" t="inlineStr">
+      <c r="C224" s="96" t="inlineStr">
         <is>
           <t>vie</t>
         </is>
       </c>
-      <c r="D224" s="119" t="inlineStr">
+      <c r="D224" s="118" t="inlineStr">
         <is>
           <t>lvsbjind</t>
         </is>
       </c>
-      <c r="E224" s="97" t="inlineStr">
+      <c r="E224" s="96" t="inlineStr">
         <is>
           <t>LVSBJIND</t>
         </is>
       </c>
-      <c r="F224" s="97" t="inlineStr">
+      <c r="F224" s="96" t="inlineStr">
         <is>
           <t>VIE</t>
         </is>
       </c>
-      <c r="G224" s="119" t="inlineStr">
+      <c r="G224" s="118" t="inlineStr">
         <is>
           <t>LVSBJIND</t>
         </is>
       </c>
-      <c r="H224" s="97" t="inlineStr">
+      <c r="H224" s="96" t="inlineStr">
         <is>
           <t>Mode de vie (avec qui le sujet vit / type de logement)</t>
         </is>
       </c>
-      <c r="I224" s="97" t="inlineStr">
+      <c r="I224" s="96" t="inlineStr">
         <is>
           <t>Catégoriel ; codes diffèrent (BP+DR=LVSBJIND, SZ=VIE) ; mêmes catégories 1-8 : seul / chez parents / propre foyer familial / chez enfants / chez famille / colocation / collectivité / autres</t>
         </is>
       </c>
-      <c r="J224" s="119" t="n">
+      <c r="J224" s="118" t="n">
         <v>1</v>
       </c>
-      <c r="K224" s="97" t="n">
+      <c r="K224" s="96" t="n">
         <v>8</v>
       </c>
-      <c r="L224" s="97" t="inlineStr">
+      <c r="L224" s="96" t="inlineStr">
         <is>
           <t>Living arrangement : core social/functional autonomy marker. Living alone vs with parents vs in own family unit vs collective housing differentiates major recovery and dependency phenotypes. Same construct across all three thesauri with same coded categories — only the variable name differs (semantic Tier A). Critical clustering variable for autonomy-trajectory phenotypes.</t>
         </is>
       </c>
-      <c r="M224" s="97" t="inlineStr">
+      <c r="M224" s="96" t="inlineStr">
         <is>
           <t>BP/DR numeric codes 1-8; SZ stores TEXT in 'vie' col -&gt; encode SZ text to the 1-8 scheme. Bound [1,8].</t>
         </is>
       </c>
-      <c r="N224" s="97" t="inlineStr">
+      <c r="N224" s="96" t="inlineStr">
         <is>
           <t>Verify SZ data is stored as either text labels OR integers 1-8. If text labels, recode to BP/DR's 1-8 integer convention before pooling. Construct is fully comparable; only the variable name and codage display differ.</t>
         </is>
       </c>
-      <c r="O224" s="97" t="inlineStr">
+      <c r="O224" s="96" t="inlineStr">
         <is>
           <t>lvsbjind</t>
         </is>
       </c>
-      <c r="P224" s="97" t="inlineStr">
+      <c r="P224" s="96" t="inlineStr">
         <is>
           <t>1: seul, 2: chez ses parents, 3: dans son propre foyer familial, 4: chez les enfants, 5: chez de la famille, 6: colocation, 7: collectivité, 8: autres</t>
         </is>
       </c>
-      <c r="Q224" s="97" t="inlineStr">
+      <c r="Q224" s="96" t="inlineStr">
         <is>
           <t>vie</t>
         </is>
       </c>
-      <c r="R224" s="97" t="inlineStr">
+      <c r="R224" s="96" t="inlineStr">
         <is>
           <t>Seul/ Chez ses parents / Dans son propre foyer familial / Chez les enfants / Chez de la famille / Colocation / Collectivité / Autres</t>
         </is>
       </c>
-      <c r="S224" s="97" t="inlineStr">
+      <c r="S224" s="96" t="inlineStr">
         <is>
           <t>lvsbjind</t>
         </is>
       </c>
-      <c r="T224" s="97" t="inlineStr">
+      <c r="T224" s="96" t="inlineStr">
         <is>
           <t>1: seul, 2: chez ses parents, 3: dans son propre foyer familial, 4: chez les enfants, 5: chez de la famille, 6: colocation, 7: collectivité, 8: autres</t>
         </is>
       </c>
-      <c r="U224" s="97" t="inlineStr">
+      <c r="U224" s="96" t="inlineStr">
         <is>
           <t>int8 categorical</t>
         </is>
       </c>
-      <c r="V224" s="97" t="inlineStr">
+      <c r="V224" s="96" t="inlineStr">
         <is>
           <t>{1, 2, 3, 4, 5, 6, 7, 8}</t>
         </is>
       </c>
-      <c r="W224" s="98" t="inlineStr">
+      <c r="W224" s="97" t="inlineStr">
         <is>
           <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
-      <c r="X224" s="97" t="inlineStr">
+      <c r="X224" s="96" t="inlineStr">
         <is>
           <t>lvsbjind</t>
         </is>
@@ -24796,39 +24787,6 @@
         </is>
       </c>
     </row>
-    <row r="225" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="226" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="227" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="228" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="229" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="230" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="231" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="232" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="233" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="234" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="235" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="236" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="237" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="238" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="239" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="240" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="241" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="242" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="243" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="244" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="245" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="246" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="247" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="248" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="249" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="250" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="251" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="252" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="253" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="254" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="255" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="256" ht="21" customFormat="1" customHeight="1" s="17"/>
-    <row r="257" ht="21" customFormat="1" customHeight="1" s="17"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/face-common-vars-v2.xlsx
+++ b/data/face-common-vars-v2.xlsx
@@ -5493,8 +5493,12 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="G65" s="96" t="n"/>
-      <c r="H65" s="123" t="n"/>
+      <c r="G65" s="96" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H65" s="123" t="n">
+        <v>0.7</v>
+      </c>
       <c r="I65" s="36" t="inlineStr">
         <is>
           <t>Raw QT interval : precursor to QTc; needed when re-deriving Bazett, Fridericia or Framingham corrections under different assumptions.</t>
@@ -5563,8 +5567,12 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="G66" s="96" t="n"/>
-      <c r="H66" s="123" t="n"/>
+      <c r="G66" s="96" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H66" s="123" t="n">
+        <v>2</v>
+      </c>
       <c r="I66" s="36" t="inlineStr">
         <is>
           <t>RR interval : cardiac cycle length used to compute corrected QT and to characterise basal heart-rate variability.</t>
@@ -5637,8 +5645,12 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="G67" s="97" t="n"/>
-      <c r="H67" s="124" t="n"/>
+      <c r="G67" s="97" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H67" s="124" t="n">
+        <v>0.7</v>
+      </c>
       <c r="I67" s="41" t="inlineStr">
         <is>
           <t>Corrected QT interval : critical pharmacovigilance variable for many psychotropics (haloperidol, ziprasidone, citalopram, methadone, lithium combinations) ; thresholds (&gt;450 ms men / &gt;460 ms women / &gt;500 ms absolute) drive treatment decisions.</t>
@@ -13400,7 +13412,7 @@
       </c>
       <c r="J172" s="11" t="inlineStr">
         <is>
-          <t>[verify]</t>
+          <t>int8 ordinal</t>
         </is>
       </c>
       <c r="K172" s="11" t="inlineStr">

--- a/data/face-common-vars-v2.xlsx
+++ b/data/face-common-vars-v2.xlsx
@@ -1587,7 +1587,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Derive canonical site from fondacode leading digits; map to city via data/site_lookup.csv. Use as ComBat batch / site confound.</t>
+          <t>Derive canonical site from fondacode leading digits; map to city via data/site_lookup.csv. Use as ComBat batch / site confound. | Implemented in rules.py::derive_siteid_city (fondacode leading digits + data/site_lookup.csv).</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Verify units: mmHg for BP, msec for QT/QTc, bpm for HR, kg for weight, cm for height. Convert if any source uses different.</t>
+          <t>Verify units: mmHg for BP, msec for QT/QTc, bpm for HR, kg for weight, cm for height. Convert if any source uses different. | Implemented in rules.py::qt (ms→s: value&gt;5 ⇒ /1000), v2-gated. Bound in seconds.</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Verify units: mmHg for BP, msec for QT/QTc, bpm for HR, kg for weight, cm for height. Convert if any source uses different.</t>
+          <t>Verify units: mmHg for BP, msec for QT/QTc, bpm for HR, kg for weight, cm for height. Convert if any source uses different. | Implemented in rules.py::rr (ms→s: value&gt;5 ⇒ /1000), v2-gated. Bound in seconds.</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -5679,6 +5679,11 @@
       <c r="N67" s="22" t="inlineStr">
         <is>
           <t>3 (BP/SZ/DR)</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Implemented in rules.py::qtc (ms→s: value&gt;5 ⇒ /1000), v2-gated. Bound in seconds.</t>
         </is>
       </c>
     </row>
@@ -10774,11 +10779,15 @@
       </c>
       <c r="F136" s="20" t="inlineStr">
         <is>
-          <t>NUM (mètres)</t>
-        </is>
-      </c>
-      <c r="G136" s="100" t="n"/>
-      <c r="H136" s="129" t="n"/>
+          <t>Ordinal jump height: 1=Hauteur d'homme, 2=Hauteur modérée, 3=D'un endroit élevé.</t>
+        </is>
+      </c>
+      <c r="G136" s="100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" s="129" t="n">
+        <v>3</v>
+      </c>
       <c r="I136" s="20" t="inlineStr">
         <is>
           <t>Jump height : objective lethality marker when the method is jumping; correlates with lethal intent and injury severity.</t>
@@ -10811,12 +10820,12 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Recode all to {1=Oui, 0=Non, NA=missing}. BP/SZ: 'Oui'→1, 'Non'→0. DR: already numeric, no change needed.</t>
+          <t>rules.py::ltsv02 — BP text → ordinal 1-3; DR codes pass through; SZ absent.</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>✓ CONFIRMED in data: BP and SZ store as text {'Oui','Non'}; DR stores as numeric {0,1}. ~30%-72% missing depending on pathology.</t>
+          <t>Jump height (LTSV02). BP stores French text, DR is pre-numericized, SZ does not collect it. Encoded in rules.py (v2-gated; v1 unchanged). Verified by scripts/qa_harmonization.py.</t>
         </is>
       </c>
     </row>
@@ -10914,11 +10923,15 @@
       </c>
       <c r="F138" s="20" t="inlineStr">
         <is>
-          <t>Categorical (Columbia lethality)</t>
-        </is>
-      </c>
-      <c r="G138" s="100" t="n"/>
-      <c r="H138" s="129" t="n"/>
+          <t>Firearm lethality (Columbia): 0=Pas de dommage, 2=extrémité, 5=abdomen/thorax.</t>
+        </is>
+      </c>
+      <c r="G138" s="100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" s="129" t="n">
+        <v>6</v>
+      </c>
       <c r="I138" s="20" t="inlineStr">
         <is>
           <t>Lethality grading for firearm : the highest case-fatality method; lethality grade refines the severity of the violent-method phenotype.</t>
@@ -10951,12 +10964,12 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Reclassify as PARTIAL. Pool BP+DR; SZ NA.</t>
+          <t>rules.py::ltsv04 — BP text → Beck/Columbia medical-lethality ordinal (0=no damage → higher=more severe → death). DR codes pass through; SZ absent.</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>LTSV04 (Létalité si méthode = Arme à feu). Same situation as R150.</t>
+          <t>Firearm lethality (LTSV04). BP stores French text, DR is pre-numericized, SZ does not collect it. Encoded in rules.py (v2-gated; v1 unchanged). Verified by scripts/qa_harmonization.py.</t>
         </is>
       </c>
     </row>
@@ -10984,11 +10997,15 @@
       </c>
       <c r="F139" s="20" t="inlineStr">
         <is>
-          <t>Categorical (Columbia lethality)</t>
-        </is>
-      </c>
-      <c r="G139" s="100" t="n"/>
-      <c r="H139" s="129" t="n"/>
+          <t>Self-immolation lethality (Columbia): 0=no damage, 1=1st°, 2=2nd°, 4=3rd° burns.</t>
+        </is>
+      </c>
+      <c r="G139" s="100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="129" t="n">
+        <v>6</v>
+      </c>
       <c r="I139" s="20" t="inlineStr">
         <is>
           <t>Lethality grading for immolation : rare but high-lethality method, often associated with severe psychotic features or extreme distress.</t>
@@ -10996,7 +11013,7 @@
       </c>
       <c r="J139" s="20" t="inlineStr">
         <is>
-          <t>int8 categorical</t>
+          <t>int8 ordinal</t>
         </is>
       </c>
       <c r="K139" s="20" t="inlineStr">
@@ -11021,12 +11038,12 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Map BP/SZ text → numeric: {'La semaine dernière'→0, 'Il y a entre une semaine et la dernière visite'→0 (collapse to la semaine dernière, OR keep as 0.5 if you want to preserve granularity for BP/SZ-only sub-analyses), 'Il y a entre deux semaines et douze mois'→1, 'Il y a plus d''un an'→2}. DR is already 0/1/2 — no change. Document the BP/SZ 4-to-3 collapse choice.</t>
+          <t>rules.py::ltsv05 — BP text → Beck/Columbia medical-lethality ordinal (0=no damage → higher=more severe → death). DR codes pass through; SZ absent.</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>⚠ REVISED finding: data shows BP and SZ have 4 timing categories — 'La semaine dernière', 'Il y a entre une semaine et la dernière visite' (extra visit-context category), 'Il y a entre deux semaines et douze mois', 'Il y a plus d''un an'. DR has only 3 categories (0/1/2 = la semaine dernière / 2 sem-12 mois / &gt;1 an), MISSING the 'Il y a entre une semaine et la dernière visite' category. The thesaurus's off-by-one suspicion was wrong; the real issue is category granularity.</t>
+          <t>Immolation lethality (LTSV05). BP stores French text, DR is pre-numericized, SZ does not collect it. Encoded in rules.py (v2-gated; v1 unchanged). Verified by scripts/qa_harmonization.py.</t>
         </is>
       </c>
     </row>
@@ -11054,11 +11071,15 @@
       </c>
       <c r="F140" s="20" t="inlineStr">
         <is>
-          <t>Categorical (Columbia lethality)</t>
-        </is>
-      </c>
-      <c r="G140" s="100" t="n"/>
-      <c r="H140" s="129" t="n"/>
+          <t>Drowning lethality (Columbia): 0=no damage, 2=conscious/mild, 4=unconscious.</t>
+        </is>
+      </c>
+      <c r="G140" s="100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="129" t="n">
+        <v>6</v>
+      </c>
       <c r="I140" s="20" t="inlineStr">
         <is>
           <t>Lethality grading for drowning : method-specific severity refinement complementing the categorical method variable.</t>
@@ -11091,12 +11112,12 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Recode all to {1=Oui, 0=Non, NA=missing}. BP/SZ: 'Oui'→1, 'Non'→0. DR: already numeric, no change needed.</t>
+          <t>rules.py::ltsv06 — BP text → Beck/Columbia medical-lethality ordinal (0=no damage → higher=more severe → death). DR codes pass through; SZ absent.</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>✓ CONFIRMED in data: BP and SZ store as text {'Oui','Non'}; DR stores as numeric {0,1}. ~30%-72% missing depending on pathology.</t>
+          <t>Drowning lethality (LTSV06). BP stores French text, DR is pre-numericized, SZ does not collect it. Encoded in rules.py (v2-gated; v1 unchanged). Verified by scripts/qa_harmonization.py.</t>
         </is>
       </c>
     </row>
@@ -11404,11 +11425,15 @@
       </c>
       <c r="F145" s="20" t="inlineStr">
         <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="G145" s="100" t="n"/>
-      <c r="H145" s="129" t="n"/>
+          <t>Non-sedative drug type: 1=OTC, 2=non-psychotrope Rx, 3=other ingested, 5=lithium; Inconnu→NA.</t>
+        </is>
+      </c>
+      <c r="G145" s="100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" s="129" t="n">
+        <v>8</v>
+      </c>
       <c r="I145" s="20" t="inlineStr">
         <is>
           <t>Non-sedative drug class used : complements the sedative-class variable for full pharmacologic characterisation of the overdose.</t>
@@ -11441,12 +11466,12 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Map BP/SZ text → numeric: {'La semaine dernière'→0, 'Il y a entre une semaine et la dernière visite'→0 (collapse to la semaine dernière, OR keep as 0.5 if you want to preserve granularity for BP/SZ-only sub-analyses), 'Il y a entre deux semaines et douze mois'→1, 'Il y a plus d''un an'→2}. DR is already 0/1/2 — no change. Document the BP/SZ 4-to-3 collapse choice.</t>
+          <t>rules.py::ltsg03 — BP text → category code; DR codes pass through; SZ absent.</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>⚠ REVISED finding: data shows BP and SZ have 4 timing categories — 'La semaine dernière', 'Il y a entre une semaine et la dernière visite' (extra visit-context category), 'Il y a entre deux semaines et douze mois', 'Il y a plus d''un an'. DR has only 3 categories (0/1/2 = la semaine dernière / 2 sem-12 mois / &gt;1 an), MISSING the 'Il y a entre une semaine et la dernière visite' category. The thesaurus's off-by-one suspicion was wrong; the real issue is category granularity.</t>
+          <t>Non-sedative drug type in overdose (LTSG03). BP stores French text, DR is pre-numericized, SZ does not collect it. Encoded in rules.py (v2-gated; v1 unchanged). Verified by scripts/qa_harmonization.py.</t>
         </is>
       </c>
     </row>
@@ -11544,11 +11569,15 @@
       </c>
       <c r="F147" s="20" t="inlineStr">
         <is>
-          <t>Categorical (Columbia lethality)</t>
-        </is>
-      </c>
-      <c r="G147" s="100" t="n"/>
-      <c r="H147" s="129" t="n"/>
+          <t>Medication-overdose lethality (Columbia): 0=none/minimal … 4=major systemic, 6=Mort.</t>
+        </is>
+      </c>
+      <c r="G147" s="100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" s="129" t="n">
+        <v>6</v>
+      </c>
       <c r="I147" s="20" t="inlineStr">
         <is>
           <t>Lethality grading for non-sedative medication overdose : complements LTSG04 for full toxicological lethality phenotype.</t>
@@ -11556,7 +11585,7 @@
       </c>
       <c r="J147" s="20" t="inlineStr">
         <is>
-          <t>int8 categorical</t>
+          <t>int8 ordinal</t>
         </is>
       </c>
       <c r="K147" s="20" t="inlineStr">
@@ -11581,12 +11610,12 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Map BP/SZ text → numeric: {'La semaine dernière'→0, 'Il y a entre une semaine et la dernière visite'→0 (collapse to la semaine dernière, OR keep as 0.5 if you want to preserve granularity for BP/SZ-only sub-analyses), 'Il y a entre deux semaines et douze mois'→1, 'Il y a plus d''un an'→2}. DR is already 0/1/2 — no change. Document the BP/SZ 4-to-3 collapse choice.</t>
+          <t>rules.py::ltsg05 — BP text → Beck/Columbia medical-lethality ordinal (0=no damage → higher=more severe → death). DR codes pass through; SZ absent.</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>⚠ REVISED finding: data shows BP and SZ have 4 timing categories — 'La semaine dernière', 'Il y a entre une semaine et la dernière visite' (extra visit-context category), 'Il y a entre deux semaines et douze mois', 'Il y a plus d''un an'. DR has only 3 categories (0/1/2 = la semaine dernière / 2 sem-12 mois / &gt;1 an), MISSING the 'Il y a entre une semaine et la dernière visite' category. The thesaurus's off-by-one suspicion was wrong; the real issue is category granularity.</t>
+          <t>Overdose lethality (LTSG05). BP stores French text, DR is pre-numericized, SZ does not collect it. Encoded in rules.py (v2-gated; v1 unchanged). Verified by scripts/qa_harmonization.py.</t>
         </is>
       </c>
     </row>
@@ -11614,11 +11643,15 @@
       </c>
       <c r="F148" s="20" t="inlineStr">
         <is>
-          <t>Categorical (Columbia lethality)</t>
-        </is>
-      </c>
-      <c r="G148" s="100" t="n"/>
-      <c r="H148" s="129" t="n"/>
+          <t>Phlebotomy (cutting) lethality (Columbia): 1=scratches … 4=major blood loss/transfusion.</t>
+        </is>
+      </c>
+      <c r="G148" s="100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" s="129" t="n">
+        <v>6</v>
+      </c>
       <c r="I148" s="20" t="inlineStr">
         <is>
           <t>Lethality grading for self-cutting : separates non-suicidal self-injury from genuine suicidal phlebotomy on medical severity grounds.</t>
@@ -11626,7 +11659,7 @@
       </c>
       <c r="J148" s="20" t="inlineStr">
         <is>
-          <t>int8 categorical</t>
+          <t>int8 ordinal</t>
         </is>
       </c>
       <c r="K148" s="20" t="inlineStr">
@@ -11651,12 +11684,12 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Recode all to {1=Oui, 0=Non, NA=missing}. BP/SZ: 'Oui'→1, 'Non'→0. DR: already numeric, no change needed.</t>
+          <t>rules.py::ltsg06 — BP text → Beck/Columbia medical-lethality ordinal (0=no damage → higher=more severe → death). DR codes pass through; SZ absent.</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>✓ CONFIRMED in data: BP and SZ store as text {'Oui','Non'}; DR stores as numeric {0,1}. ~30%-72% missing depending on pathology.</t>
+          <t>Phlebotomy lethality (LTSG06). BP stores French text, DR is pre-numericized, SZ does not collect it. Encoded in rules.py (v2-gated; v1 unchanged). Verified by scripts/qa_harmonization.py.</t>
         </is>
       </c>
     </row>
@@ -16415,7 +16448,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>Recode both BP and SZ: 'BAC' → 12 (baccalauréat = end of lycée, after 12 years of schooling); other numeric strings → cast to int. Verify other rare strings ('BEP', 'CAP', etc.) per-cohort and apply the thesaurus mapping (CP-CM2=1-5, collège=6-9, lycée=10-12, CAP=13, BEP=14, BAC+1 to BAC+5=15-19, Doctorat=20). DR is ready to pool directly.</t>
+          <t>Recode both BP and SZ: 'BAC' → 12 (baccalauréat = end of lycée, after 12 years of schooling); other numeric strings → cast to int. Verify other rare strings ('BEP', 'CAP', etc.) per-cohort and apply the thesaurus mapping (CP-CM2=1-5, collège=6-9, lycée=10-12, CAP=13, BEP=14, BAC+1 to BAC+5=15-19, Doctorat=20). DR is ready to pool directly. | Implemented in rules.py::edulevel (SZ text tokens BAC/CAP/Doctorat→ordinal), v2-gated.</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
